--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -541,6 +541,18 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>UPSON INTERNATIONAL CORP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2nd floor SM Cyberzone SM City Sta. Rosa, Tagapo, City Of Santa Rosa, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-03-03-0771</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1174-419</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -551,6 +563,33 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1146-031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
@@ -4034,7 +4073,7 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>172</x:v>
@@ -4052,19 +4091,19 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I6" s="32">
-        <x:v>46084</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>83</x:v>
@@ -4075,7 +4114,7 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>176</x:v>
@@ -4093,85 +4132,243 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I7" s="32">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="N7" s="7" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I8" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I9" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L11" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="20" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="22" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>170</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5147,14 +5344,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -551,6 +551,45 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1174-419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06698-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
@@ -4114,13 +4153,13 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>176</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>177</x:v>
@@ -4132,34 +4171,34 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46084</x:v>
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>180</x:v>
@@ -4171,33 +4210,33 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I8" s="19">
-        <x:v>46104</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
         <x:v>183</x:v>
@@ -4209,33 +4248,33 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I9" s="19">
-        <x:v>46097</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
         <x:v>186</x:v>
@@ -4247,27 +4286,27 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46098</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
         <x:v>189</x:v>
@@ -4285,95 +4324,253 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I11" s="19">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L15" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="20" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
         <x:v>170</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5344,15 +5541,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -539,6 +539,18 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERALD BEBIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94 Magsaysay, Poblacion, Cavinti, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03009-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1189-403</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -4112,14 +4124,12 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
+      <x:c r="D6" s="11" t="s"/>
       <x:c r="E6" s="11" t="s">
         <x:v>173</x:v>
       </x:c>
@@ -4130,19 +4140,19 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
-        <x:v>46095</x:v>
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>83</x:v>
@@ -4153,13 +4163,13 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>176</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>177</x:v>
@@ -4171,22 +4181,22 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
@@ -4195,34 +4205,34 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>23</x:v>
@@ -4233,25 +4243,25 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
         <x:v>1507966</x:v>
@@ -4260,7 +4270,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>23</x:v>
@@ -4271,34 +4281,34 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>23</x:v>
@@ -4306,13 +4316,13 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>189</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
         <x:v>190</x:v>
@@ -4324,22 +4334,22 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46084</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -4347,34 +4357,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>83</x:v>
@@ -4385,34 +4395,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>83</x:v>
@@ -4423,34 +4433,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>83</x:v>
@@ -4458,10 +4468,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>202</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>52</x:v>
@@ -4476,103 +4486,150 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="H15" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="I16" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L16" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="20" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="22" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="23" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="s">
         <x:v>170</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
       <x:c r="E21" s="27" t="s"/>
       <x:c r="F21" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>92</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="26" t="s">
-        <x:v>142</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C23" s="27" t="s"/>
       <x:c r="D23" s="27" t="s"/>
       <x:c r="E23" s="27" t="s"/>
       <x:c r="F23" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5541,16 +5598,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -551,6 +551,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1189-403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAKE C. PASILAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103, Banlic, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03010-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -973,7 +985,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1044,11 +1056,8 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1165,10 +1174,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -4163,14 +4168,12 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
+      <x:c r="D7" s="11" t="s"/>
       <x:c r="E7" s="11" t="s">
         <x:v>177</x:v>
       </x:c>
@@ -4181,19 +4184,19 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46095</x:v>
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>83</x:v>
@@ -4202,13 +4205,13 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>180</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>181</x:v>
@@ -4220,22 +4223,22 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I8" s="19">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -4243,34 +4246,34 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>23</x:v>
@@ -4281,25 +4284,25 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
         <x:v>1507966</x:v>
@@ -4308,7 +4311,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>23</x:v>
@@ -4319,34 +4322,34 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>23</x:v>
@@ -4354,13 +4357,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
         <x:v>194</x:v>
@@ -4372,22 +4375,22 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46084</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
@@ -4395,34 +4398,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>83</x:v>
@@ -4433,34 +4436,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>83</x:v>
@@ -4471,34 +4474,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>83</x:v>
@@ -4506,10 +4509,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>206</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>52</x:v>
@@ -4524,82 +4527,109 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H16" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="I17" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L16" s="18">
+      <x:c r="L17" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="20" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="20" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="22" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="23" t="s">
+      <x:c r="C20" s="21" t="s"/>
+      <x:c r="D20" s="21" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="22" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="23" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="s">
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="s">
         <x:v>170</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C23" s="27" t="s"/>
       <x:c r="D23" s="27" t="s"/>
       <x:c r="E23" s="27" t="s"/>
       <x:c r="F23" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="26" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C24" s="27" t="s"/>
       <x:c r="D24" s="27" t="s"/>
@@ -4610,27 +4640,37 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="26" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C25" s="27" t="s"/>
       <x:c r="D25" s="27" t="s"/>
       <x:c r="E25" s="27" t="s"/>
       <x:c r="F25" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="29" t="s">
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C26" s="30" t="s"/>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="30" t="s"/>
-      <x:c r="F26" s="31" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5601,14 +5641,14 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -565,6 +565,78 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL ANGLE MARKETING INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>X-DOT CONNECTION INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3 UNIT 103, BATONG MALAKE, Los Baños, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06900-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1177-099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -616,6 +688,18 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
+    <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#95 CZ 28 3RD, FLOOR SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-16-05-1938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1162-745</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -653,6 +737,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>257-G SM City Molino Molino Road, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1194-347</x:t>
   </x:si>
   <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
@@ -4205,13 +4301,13 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>180</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>181</x:v>
@@ -4223,247 +4319,247 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I8" s="19">
-        <x:v>46095</x:v>
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46090.2109953704</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46090.2110069444</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511204</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46084</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>201</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>202</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46104</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>83</x:v>
@@ -4471,215 +4567,521 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>205</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>206</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46097</x:v>
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>207</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>209</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46098</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>211</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>212</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46084</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46083.1543634259</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="20" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
+      <x:c r="C28" s="21" t="s"/>
+      <x:c r="D28" s="21" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="22" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="23" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
+      <x:c r="C29" s="24" t="s"/>
+      <x:c r="D29" s="24" t="s"/>
+      <x:c r="E29" s="24" t="s"/>
+      <x:c r="F29" s="25" t="s">
         <x:v>170</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B36" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C36" s="30" t="s"/>
+      <x:c r="D36" s="30" t="s"/>
+      <x:c r="E36" s="30" t="s"/>
+      <x:c r="F36" s="31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5638,17 +6040,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:F28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -154,6 +154,18 @@
     <x:t>NEW</x:t>
   </x:si>
   <x:si>
+    <x:t>2F 2106 SM CITY LIPA JP LAUREL, San Antonio, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-26-02-0981</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1080-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deniel Puyo</x:t>
+  </x:si>
+  <x:si>
     <x:t>LOWER GROUND LEVEL SPACE 41 AYALA MALL SERIN, SILANG JUNCTION NORTH, Tagaytay City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -163,18 +175,6 @@
     <x:t>43A-2-2026-1105-857</x:t>
   </x:si>
   <x:si>
-    <x:t>Deniel Puyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2F 2106 SM CITY LIPA JP LAUREL, San Antonio, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-26-02-0981</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1080-857</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -607,6 +607,15 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -616,15 +625,6 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -652,6 +652,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06698-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1169-102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -670,24 +688,6 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-06698-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1169-102</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -712,6 +712,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -719,24 +737,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -1860,10 +1860,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46072.3184259259</x:v>
+        <x:v>46067.3600231481</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46072.3184375</x:v>
+        <x:v>46067.3600462963</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
         <x:v>1505803</x:v>
@@ -1872,7 +1872,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46079.2696990741</x:v>
+        <x:v>46079.2730092593</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>46</x:v>
@@ -1898,10 +1898,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46067.3600231481</x:v>
+        <x:v>46072.3184259259</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46067.3600462963</x:v>
+        <x:v>46072.3184375</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
         <x:v>1505803</x:v>
@@ -1910,7 +1910,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46079.2730092593</x:v>
+        <x:v>46079.2696990741</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>46</x:v>
@@ -4433,19 +4433,19 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46144</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>184</x:v>
@@ -4471,19 +4471,19 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>184</x:v>
@@ -4585,19 +4585,19 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>23</x:v>
@@ -4623,10 +4623,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
         <x:v>1507966</x:v>
@@ -4635,7 +4635,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>23</x:v>
@@ -4661,19 +4661,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
@@ -4699,19 +4699,19 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J18" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>23</x:v>
@@ -4813,19 +4813,19 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46104</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>83</x:v>
@@ -4889,19 +4889,19 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46098</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>83</x:v>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -635,6 +635,15 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0775 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -4532,75 +4541,75 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
       <x:c r="H14" s="16">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46095</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
       <x:c r="H15" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -4608,7 +4617,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>42</x:v>
@@ -4623,19 +4632,19 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>23</x:v>
@@ -4646,7 +4655,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>42</x:v>
@@ -4661,19 +4670,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
@@ -4684,7 +4693,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>42</x:v>
@@ -4699,19 +4708,19 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J18" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>23</x:v>
@@ -4719,40 +4728,40 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
       <x:c r="H19" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46145</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J19" s="15" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -4760,37 +4769,37 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
       <x:c r="H20" s="16">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>46084</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J20" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -4798,7 +4807,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>52</x:v>
@@ -4813,19 +4822,19 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>83</x:v>
@@ -4836,7 +4845,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>52</x:v>
@@ -4851,19 +4860,19 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46097</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J22" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>83</x:v>
@@ -4874,7 +4883,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>52</x:v>
@@ -4889,19 +4898,19 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>83</x:v>
@@ -4909,40 +4918,40 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>238</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
       <x:c r="H24" s="16">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46094</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J24" s="15" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46093.3109375</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -4950,75 +4959,102 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
       <x:c r="H25" s="16">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J25" s="15" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L25" s="18">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
+      <x:c r="M26" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="20" t="s">
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="20" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C28" s="21" t="s"/>
-      <x:c r="D28" s="21" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="22" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="23" t="s">
+      <x:c r="C29" s="21" t="s"/>
+      <x:c r="D29" s="21" t="s"/>
+      <x:c r="E29" s="22" t="s"/>
+      <x:c r="F29" s="22" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B30" s="23" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C29" s="24" t="s"/>
-      <x:c r="D29" s="24" t="s"/>
-      <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="25" t="s">
+      <x:c r="C30" s="24" t="s"/>
+      <x:c r="D30" s="24" t="s"/>
+      <x:c r="E30" s="24" t="s"/>
+      <x:c r="F30" s="25" t="s">
         <x:v>170</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="26" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C31" s="27" t="s"/>
       <x:c r="D31" s="27" t="s"/>
@@ -5029,60 +5065,70 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="26" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="27" t="s"/>
       <x:c r="D32" s="27" t="s"/>
       <x:c r="E32" s="27" t="s"/>
       <x:c r="F32" s="28" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C33" s="27" t="s"/>
       <x:c r="D33" s="27" t="s"/>
       <x:c r="E33" s="27" t="s"/>
       <x:c r="F33" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="26" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C34" s="27" t="s"/>
       <x:c r="D34" s="27" t="s"/>
       <x:c r="E34" s="27" t="s"/>
       <x:c r="F34" s="28" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="26" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C35" s="27" t="s"/>
       <x:c r="D35" s="27" t="s"/>
       <x:c r="E35" s="27" t="s"/>
       <x:c r="F35" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="29" t="s">
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C36" s="30" t="s"/>
-      <x:c r="D36" s="30" t="s"/>
-      <x:c r="E36" s="30" t="s"/>
-      <x:c r="F36" s="31" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C37" s="30" t="s"/>
+      <x:c r="D37" s="30" t="s"/>
+      <x:c r="E37" s="30" t="s"/>
+      <x:c r="F37" s="31" t="n">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6043,8 +6089,7 @@
   <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B28:F28"/>
-    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B29:F29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
@@ -6052,6 +6097,7 @@
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -10,58 +10,22 @@
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -568,6 +532,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06919-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1179-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -577,9 +553,6 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -592,6 +565,60 @@
     <x:t>43A-3-2026-1177-099</x:t>
   </x:si>
   <x:si>
+    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0781 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1144-933</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELL EVER MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 424 Cyberzone 4th flr., SM City Bacoor, Habay II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-456b-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1154-964</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBLITZ MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 23- 019R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1095-163</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
@@ -604,9 +631,27 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -625,9 +670,87 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLIXTEC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/F BLDG. D DAANG HARI ROAD, PASONG BUAYA I, Imus City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-456R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1086-471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTO GADGETS TOO INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 440 SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0773 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1152-831</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0778 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1153-796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3 03714 ROBINSONS PLACE DASMARIÑAS, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-018R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1094-777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-468R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1161-717</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-471R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1108-762</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -670,6 +793,24 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -679,24 +820,6 @@
     <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -709,6 +832,15 @@
     <x:t>43A-3-2026-1162-745</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-21-03-2265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1157-256</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -721,6 +853,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -728,24 +878,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1173-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -779,7 +911,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -806,12 +938,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -819,6 +945,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -833,13 +980,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -884,6 +1024,17 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
@@ -898,17 +1049,6 @@
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -1090,7 +1230,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1101,73 +1241,82 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
@@ -1175,109 +1324,118 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1541,1577 +1699,1553 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="F7" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="G7" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="H7" s="17">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="D8" s="19" t="s"/>
+      <x:c r="E8" s="19" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="F8" s="19" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="G8" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="H8" s="20">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="19" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="F9" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I9" s="20">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="L9" s="20">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D10" s="12" t="s"/>
+      <x:c r="E10" s="11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F10" s="11" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="G10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="L10" s="15">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D11" s="12" t="s"/>
+      <x:c r="E11" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="H11" s="13">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I11" s="13">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="L11" s="15">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="C12" s="11" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="D12" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="E12" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="F12" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I12" s="13">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I13" s="13">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I14" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="15">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s"/>
+      <x:c r="E19" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I19" s="13">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I20" s="13">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L20" s="15">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I21" s="13">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="15">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I22" s="13">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="15">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M22" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I23" s="22">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J23" s="12" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L23" s="15">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M23" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H24" s="13">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="15">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M24" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H25" s="13">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J25" s="12" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="15">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M25" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H26" s="13">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I26" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="15">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M26" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H27" s="13">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I27" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="12" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="15">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M27" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H28" s="13">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I28" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="12" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="15">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M28" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H29" s="13">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I29" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K29" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="15">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M29" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H30" s="13">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I30" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="15">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M30" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H31" s="13">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I31" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="15">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M31" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H32" s="13">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I32" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="12" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K32" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="15">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M32" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H33" s="13">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I33" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="12" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K33" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="15">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M33" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H34" s="13">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I34" s="22">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J34" s="12" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="15">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M34" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H35" s="13">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I35" s="13">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J35" s="12" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K35" s="14" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L35" s="15">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M35" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="11" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="C36" s="11" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G36" s="11" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H36" s="13">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I36" s="22">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J36" s="12" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K36" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L36" s="15">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M36" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="11" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="C37" s="11" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H37" s="13">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I37" s="22">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J37" s="12" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K37" s="14" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L37" s="15">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M37" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="11" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="C38" s="11" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="E38" s="11" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H38" s="13">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I38" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J38" s="12" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K38" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L38" s="15">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M38" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s"/>
-      <x:c r="E19" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="E39" s="11" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H39" s="13">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I39" s="22">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J39" s="12" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K39" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L39" s="15">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M39" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="11" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="s"/>
+      <x:c r="E40" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I31" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I32" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I33" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I34" s="19">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I35" s="16">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I36" s="19">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
+      <x:c r="G40" s="11" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H40" s="13">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I40" s="13">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J40" s="12" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K40" s="14" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L40" s="15">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M40" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="11" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I37" s="19">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
+      <x:c r="C41" s="11" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F38" s="14" t="s">
+      <x:c r="D41" s="12" t="s"/>
+      <x:c r="E41" s="11" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G38" s="14" t="s">
+      <x:c r="F41" s="11" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I38" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
+      <x:c r="G41" s="11" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I39" s="19">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s"/>
-      <x:c r="E40" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I40" s="16">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K40" s="17" t="n">
+      <x:c r="H41" s="13">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I41" s="13">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J41" s="12" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K41" s="14" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L40" s="18">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D41" s="15" t="s"/>
-      <x:c r="E41" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G41" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I41" s="16">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K41" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L41" s="18">
+      <x:c r="L41" s="15">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M41" s="14" t="s">
-        <x:v>23</x:v>
+      <x:c r="M41" s="11" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="20" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C44" s="21" t="s"/>
-      <x:c r="D44" s="21" t="s"/>
-      <x:c r="E44" s="22" t="s"/>
-      <x:c r="F44" s="22" t="s"/>
+      <x:c r="B44" s="23" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C44" s="24" t="s"/>
+      <x:c r="D44" s="24" t="s"/>
+      <x:c r="E44" s="25" t="s"/>
+      <x:c r="F44" s="25" t="s"/>
     </x:row>
     <x:row r="45" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B45" s="23" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C45" s="24" t="s"/>
-      <x:c r="D45" s="24" t="s"/>
-      <x:c r="E45" s="24" t="s"/>
-      <x:c r="F45" s="25" t="s">
-        <x:v>170</x:v>
+      <x:c r="B45" s="26" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C45" s="27" t="s"/>
+      <x:c r="D45" s="27" t="s"/>
+      <x:c r="E45" s="27" t="s"/>
+      <x:c r="F45" s="28" t="s">
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C46" s="27" t="s"/>
-      <x:c r="D46" s="27" t="s"/>
-      <x:c r="E46" s="27" t="s"/>
-      <x:c r="F46" s="28" t="n">
+      <x:c r="B46" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C46" s="30" t="s"/>
+      <x:c r="D46" s="30" t="s"/>
+      <x:c r="E46" s="30" t="s"/>
+      <x:c r="F46" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C47" s="27" t="s"/>
-      <x:c r="D47" s="27" t="s"/>
-      <x:c r="E47" s="27" t="s"/>
-      <x:c r="F47" s="28" t="n">
+      <x:c r="B47" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s"/>
+      <x:c r="D47" s="30" t="s"/>
+      <x:c r="E47" s="30" t="s"/>
+      <x:c r="F47" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C48" s="27" t="s"/>
-      <x:c r="D48" s="27" t="s"/>
-      <x:c r="E48" s="27" t="s"/>
-      <x:c r="F48" s="28" t="n">
+      <x:c r="B48" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s"/>
+      <x:c r="D48" s="30" t="s"/>
+      <x:c r="E48" s="30" t="s"/>
+      <x:c r="F48" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
+      <x:c r="B49" s="29" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s"/>
+      <x:c r="D49" s="30" t="s"/>
+      <x:c r="E49" s="30" t="s"/>
+      <x:c r="F49" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
+      <x:c r="B50" s="29" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="30" t="s"/>
+      <x:c r="F50" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="26" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C51" s="27" t="s"/>
-      <x:c r="D51" s="27" t="s"/>
-      <x:c r="E51" s="27" t="s"/>
-      <x:c r="F51" s="28" t="n">
+      <x:c r="B51" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s"/>
+      <x:c r="D51" s="30" t="s"/>
+      <x:c r="E51" s="30" t="s"/>
+      <x:c r="F51" s="31" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
+      <x:c r="B52" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s"/>
+      <x:c r="D52" s="30" t="s"/>
+      <x:c r="E52" s="30" t="s"/>
+      <x:c r="F52" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="26" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C53" s="27" t="s"/>
-      <x:c r="D53" s="27" t="s"/>
-      <x:c r="E53" s="27" t="s"/>
-      <x:c r="F53" s="28" t="n">
+      <x:c r="B53" s="29" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C53" s="30" t="s"/>
+      <x:c r="D53" s="30" t="s"/>
+      <x:c r="E53" s="30" t="s"/>
+      <x:c r="F53" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="26" t="s">
+      <x:c r="B54" s="29" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C54" s="30" t="s"/>
+      <x:c r="D54" s="30" t="s"/>
+      <x:c r="E54" s="30" t="s"/>
+      <x:c r="F54" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B55" s="32" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C54" s="27" t="s"/>
-      <x:c r="D54" s="27" t="s"/>
-      <x:c r="E54" s="27" t="s"/>
-      <x:c r="F54" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="29" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C55" s="30" t="s"/>
-      <x:c r="D55" s="30" t="s"/>
-      <x:c r="E55" s="30" t="s"/>
-      <x:c r="F55" s="31" t="n">
+      <x:c r="C55" s="33" t="s"/>
+      <x:c r="D55" s="33" t="s"/>
+      <x:c r="E55" s="33" t="s"/>
+      <x:c r="F55" s="34" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
@@ -4144,1007 +4278,1575 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H8" s="20">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I9" s="20">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="15">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="15">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I12" s="22">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I13" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I14" s="22">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="15">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I19" s="22">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I20" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="15">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I21" s="22">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="15">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I22" s="22">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L22" s="15">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M22" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I23" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="12" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="15">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M23" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H24" s="13">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="15">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M24" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H25" s="13">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J25" s="12" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="15">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M25" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H26" s="13">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I26" s="22">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J26" s="12" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="15">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M26" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H27" s="13">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I27" s="22">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J27" s="12" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L27" s="15">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M27" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H28" s="13">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I28" s="22">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J28" s="12" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L28" s="15">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M28" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H29" s="13">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I29" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K29" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="15">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M29" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H30" s="13">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I30" s="22">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J30" s="12" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="15">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M30" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H31" s="13">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I31" s="13">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J31" s="12" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L31" s="15">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M31" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H32" s="13">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I32" s="13">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J32" s="12" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K32" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L32" s="15">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M32" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H33" s="13">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I33" s="13">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J33" s="12" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K33" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L33" s="15">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M33" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H34" s="13">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I34" s="13">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J34" s="12" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L34" s="15">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M34" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H35" s="13">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I35" s="22">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J35" s="12" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K35" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="15">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M35" s="11" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="E36" s="11" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G36" s="11" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H36" s="13">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I36" s="22">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J36" s="12" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K36" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="15">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M36" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="E37" s="11" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H37" s="13">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I37" s="22">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J37" s="12" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K37" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="L37" s="15">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M37" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C38" s="11" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H38" s="13">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I38" s="22">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J38" s="12" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K38" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="L38" s="15">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M38" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H39" s="13">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I39" s="22">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J39" s="12" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K39" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="L39" s="15">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M39" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G40" s="11" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H40" s="13">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I40" s="22">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J40" s="12" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K40" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="L40" s="15">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M40" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D41" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H41" s="13">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I41" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J41" s="12" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K41" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L41" s="15">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M41" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G42" s="11" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H42" s="13">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I42" s="22">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
+      <x:c r="J42" s="12" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K42" s="14" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
+      <x:c r="L42" s="15">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="20" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C29" s="21" t="s"/>
-      <x:c r="D29" s="21" t="s"/>
-      <x:c r="E29" s="22" t="s"/>
-      <x:c r="F29" s="22" t="s"/>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="23" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C30" s="24" t="s"/>
-      <x:c r="D30" s="24" t="s"/>
-      <x:c r="E30" s="24" t="s"/>
-      <x:c r="F30" s="25" t="s">
-        <x:v>170</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M42" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="23" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C45" s="24" t="s"/>
+      <x:c r="D45" s="24" t="s"/>
+      <x:c r="E45" s="25" t="s"/>
+      <x:c r="F45" s="25" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="26" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="s"/>
+      <x:c r="D46" s="27" t="s"/>
+      <x:c r="E46" s="27" t="s"/>
+      <x:c r="F46" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s"/>
+      <x:c r="D47" s="30" t="s"/>
+      <x:c r="E47" s="30" t="s"/>
+      <x:c r="F47" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s"/>
+      <x:c r="D48" s="30" t="s"/>
+      <x:c r="E48" s="30" t="s"/>
+      <x:c r="F48" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s"/>
+      <x:c r="D49" s="30" t="s"/>
+      <x:c r="E49" s="30" t="s"/>
+      <x:c r="F49" s="31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="29" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="30" t="s"/>
+      <x:c r="F50" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s"/>
+      <x:c r="D51" s="30" t="s"/>
+      <x:c r="E51" s="30" t="s"/>
+      <x:c r="F51" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="29" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s"/>
+      <x:c r="D52" s="30" t="s"/>
+      <x:c r="E52" s="30" t="s"/>
+      <x:c r="F52" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B53" s="32" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C53" s="33" t="s"/>
+      <x:c r="D53" s="33" t="s"/>
+      <x:c r="E53" s="33" t="s"/>
+      <x:c r="F53" s="34" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6089,15 +6791,15 @@
   <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B29:F29"/>
-    <x:mergeCell ref="B30:E30"/>
-    <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
-    <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B45:F45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -1308,7 +1308,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1344,6 +1344,50 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1363,32 +1407,12 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1701,7 +1725,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1762,7 +1786,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -1800,7 +1824,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -1912,1341 +1936,3994 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s"/>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="D10" s="23" t="s"/>
+      <x:c r="E10" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="24">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="23" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+      <x:c r="B11" s="22" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="C11" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s"/>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="D11" s="23" t="s"/>
+      <x:c r="E11" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="F11" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="G11" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="H11" s="24">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I11" s="13">
+      <x:c r="I11" s="24">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="23" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="25" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="26">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
+      <x:c r="M11" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="s">
+      <x:c r="C12" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="s">
+      <x:c r="D12" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="E12" s="22" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="F12" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="G12" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="H12" s="24">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I12" s="13">
+      <x:c r="I12" s="24">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="23" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="26">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
+      <x:c r="M12" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="C13" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
+      <x:c r="D13" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="E13" s="22" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="F13" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="G13" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="H13" s="24">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I13" s="13">
+      <x:c r="I13" s="24">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="23" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="26">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
+      <x:c r="M13" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C14" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="s">
+      <x:c r="D14" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="E14" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="F14" s="22" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="G14" s="22" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="H14" s="24">
         <x:v>46067.1596643518</x:v>
       </x:c>
-      <x:c r="I14" s="22">
+      <x:c r="I14" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="23" t="n">
         <x:v>1505804</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="K14" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="15">
+      <x:c r="L14" s="26">
         <x:v>46079.2772569444</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
+      <x:c r="M14" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
+      <x:c r="C15" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="s">
+      <x:c r="D15" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="E15" s="22" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="F15" s="22" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="G15" s="22" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="H15" s="24">
         <x:v>46067.2222106481</x:v>
       </x:c>
-      <x:c r="I15" s="22">
+      <x:c r="I15" s="27">
         <x:v>46089</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="23" t="n">
         <x:v>1505805</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="K15" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="15">
+      <x:c r="L15" s="26">
         <x:v>46079.2763078704</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
+      <x:c r="M15" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="C16" s="22" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="D16" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="E16" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="F16" s="22" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="G16" s="22" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="H16" s="24">
         <x:v>46072.3605555556</x:v>
       </x:c>
-      <x:c r="I16" s="22">
+      <x:c r="I16" s="27">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="23" t="n">
         <x:v>1507784</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K16" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="15">
+      <x:c r="L16" s="26">
         <x:v>46073.2284953704</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
+      <x:c r="M16" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="s">
+      <x:c r="C17" s="22" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="s">
+      <x:c r="D17" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="E17" s="22" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="F17" s="22" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="G17" s="22" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="H17" s="24">
         <x:v>46072.3529513889</x:v>
       </x:c>
-      <x:c r="I17" s="22">
+      <x:c r="I17" s="27">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="23" t="n">
         <x:v>1507785</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="K17" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="15">
+      <x:c r="L17" s="26">
         <x:v>46073.2314351852</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
+      <x:c r="M17" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="s">
+      <x:c r="C18" s="22" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="s">
+      <x:c r="D18" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="E18" s="22" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="F18" s="22" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="G18" s="22" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="H18" s="24">
         <x:v>46063.1352777778</x:v>
       </x:c>
-      <x:c r="I18" s="22">
+      <x:c r="I18" s="27">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="23" t="n">
         <x:v>1511010</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="K18" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="15">
+      <x:c r="L18" s="26">
         <x:v>46063.2367708333</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
+      <x:c r="M18" s="22" t="s">
         <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="C19" s="22" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s"/>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="22" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
+      <x:c r="F19" s="22" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="s">
+      <x:c r="G19" s="22" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H19" s="13">
+      <x:c r="H19" s="24">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="I19" s="13">
+      <x:c r="I19" s="24">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
+      <x:c r="J19" s="23" t="n">
         <x:v>1507791</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="K19" s="25" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L19" s="15">
+      <x:c r="L19" s="26">
         <x:v>46073.3142476852</x:v>
       </x:c>
-      <x:c r="M19" s="11" t="s">
+      <x:c r="M19" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="C20" s="22" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="s">
+      <x:c r="D20" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="E20" s="22" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="F20" s="22" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="G20" s="22" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H20" s="13">
+      <x:c r="H20" s="24">
         <x:v>46079.3584722222</x:v>
       </x:c>
-      <x:c r="I20" s="13">
+      <x:c r="I20" s="24">
         <x:v>46079.3584953704</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
+      <x:c r="J20" s="23" t="n">
         <x:v>1511622</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="K20" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L20" s="15">
+      <x:c r="L20" s="26">
         <x:v>46080.2311226852</x:v>
       </x:c>
-      <x:c r="M20" s="11" t="s">
+      <x:c r="M20" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="C21" s="22" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="s">
+      <x:c r="D21" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="E21" s="22" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
+      <x:c r="F21" s="22" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="s">
+      <x:c r="G21" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H21" s="13">
+      <x:c r="H21" s="24">
         <x:v>46079.3539699074</x:v>
       </x:c>
-      <x:c r="I21" s="13">
+      <x:c r="I21" s="24">
         <x:v>46079.3539814815</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="n">
+      <x:c r="J21" s="23" t="n">
         <x:v>1511627</x:v>
       </x:c>
-      <x:c r="K21" s="14" t="n">
+      <x:c r="K21" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L21" s="15">
+      <x:c r="L21" s="26">
         <x:v>46080.2440856481</x:v>
       </x:c>
-      <x:c r="M21" s="11" t="s">
+      <x:c r="M21" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="11" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="s">
+      <x:c r="C22" s="22" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="s">
+      <x:c r="D22" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="s">
+      <x:c r="E22" s="22" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="s">
+      <x:c r="F22" s="22" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G22" s="11" t="s">
+      <x:c r="G22" s="22" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H22" s="13">
+      <x:c r="H22" s="24">
         <x:v>46058.1529282407</x:v>
       </x:c>
-      <x:c r="I22" s="13">
+      <x:c r="I22" s="24">
         <x:v>46058.1529398148</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="n">
+      <x:c r="J22" s="23" t="n">
         <x:v>1507657</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="n">
+      <x:c r="K22" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L22" s="15">
+      <x:c r="L22" s="26">
         <x:v>46058.2410648148</x:v>
       </x:c>
-      <x:c r="M22" s="11" t="s">
+      <x:c r="M22" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="11" t="s">
+      <x:c r="B23" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="s">
+      <x:c r="C23" s="22" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="s">
+      <x:c r="D23" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="s">
+      <x:c r="E23" s="22" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="s">
+      <x:c r="F23" s="22" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="s">
+      <x:c r="G23" s="22" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H23" s="13">
+      <x:c r="H23" s="24">
         <x:v>46072.2635300926</x:v>
       </x:c>
-      <x:c r="I23" s="22">
+      <x:c r="I23" s="27">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="n">
+      <x:c r="J23" s="23" t="n">
         <x:v>1507790</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="n">
+      <x:c r="K23" s="25" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L23" s="15">
+      <x:c r="L23" s="26">
         <x:v>46073.3091087963</x:v>
       </x:c>
-      <x:c r="M23" s="11" t="s">
+      <x:c r="M23" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="11" t="s">
+      <x:c r="B24" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C24" s="11" t="s">
+      <x:c r="C24" s="22" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="s">
+      <x:c r="D24" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="s">
+      <x:c r="E24" s="22" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F24" s="11" t="s">
+      <x:c r="F24" s="22" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G24" s="11" t="s">
+      <x:c r="G24" s="22" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H24" s="13">
+      <x:c r="H24" s="24">
         <x:v>46079.3873148148</x:v>
       </x:c>
-      <x:c r="I24" s="22">
+      <x:c r="I24" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="n">
+      <x:c r="J24" s="23" t="n">
         <x:v>1511623</x:v>
       </x:c>
-      <x:c r="K24" s="14" t="n">
+      <x:c r="K24" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="15">
+      <x:c r="L24" s="26">
         <x:v>46080.2360763889</x:v>
       </x:c>
-      <x:c r="M24" s="11" t="s">
+      <x:c r="M24" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="11" t="s">
+      <x:c r="B25" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="s">
+      <x:c r="C25" s="22" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="s">
+      <x:c r="D25" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="s">
+      <x:c r="E25" s="22" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="s">
+      <x:c r="F25" s="22" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="s">
+      <x:c r="G25" s="22" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H25" s="13">
+      <x:c r="H25" s="24">
         <x:v>46079.2523032407</x:v>
       </x:c>
-      <x:c r="I25" s="22">
+      <x:c r="I25" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="n">
+      <x:c r="J25" s="23" t="n">
         <x:v>1511631</x:v>
       </x:c>
-      <x:c r="K25" s="14" t="n">
+      <x:c r="K25" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="15">
+      <x:c r="L25" s="26">
         <x:v>46080.2925810185</x:v>
       </x:c>
-      <x:c r="M25" s="11" t="s">
+      <x:c r="M25" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="11" t="s">
+      <x:c r="B26" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="s">
+      <x:c r="C26" s="22" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D26" s="12" t="s">
+      <x:c r="D26" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="s">
+      <x:c r="E26" s="22" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F26" s="11" t="s">
+      <x:c r="F26" s="22" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="s">
+      <x:c r="G26" s="22" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="H26" s="13">
+      <x:c r="H26" s="24">
         <x:v>46079.2430555556</x:v>
       </x:c>
-      <x:c r="I26" s="22">
+      <x:c r="I26" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="n">
+      <x:c r="J26" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K26" s="14" t="n">
+      <x:c r="K26" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L26" s="15">
+      <x:c r="L26" s="26">
         <x:v>46080.2801273148</x:v>
       </x:c>
-      <x:c r="M26" s="11" t="s">
+      <x:c r="M26" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="11" t="s">
+      <x:c r="B27" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="s">
+      <x:c r="C27" s="22" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D27" s="12" t="s">
+      <x:c r="D27" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="s">
+      <x:c r="E27" s="22" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="s">
+      <x:c r="F27" s="22" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="s">
+      <x:c r="G27" s="22" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H27" s="13">
+      <x:c r="H27" s="24">
         <x:v>46079.3651967593</x:v>
       </x:c>
-      <x:c r="I27" s="22">
+      <x:c r="I27" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J27" s="12" t="n">
+      <x:c r="J27" s="23" t="n">
         <x:v>1511626</x:v>
       </x:c>
-      <x:c r="K27" s="14" t="n">
+      <x:c r="K27" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L27" s="15">
+      <x:c r="L27" s="26">
         <x:v>46080.2425462963</x:v>
       </x:c>
-      <x:c r="M27" s="11" t="s">
+      <x:c r="M27" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="11" t="s">
+      <x:c r="B28" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="s">
+      <x:c r="C28" s="22" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D28" s="12" t="s">
+      <x:c r="D28" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="s">
+      <x:c r="E28" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F28" s="11" t="s">
+      <x:c r="F28" s="22" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G28" s="11" t="s">
+      <x:c r="G28" s="22" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H28" s="13">
+      <x:c r="H28" s="24">
         <x:v>46080.2923611111</x:v>
       </x:c>
-      <x:c r="I28" s="22">
+      <x:c r="I28" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J28" s="12" t="n">
+      <x:c r="J28" s="23" t="n">
         <x:v>1511635</x:v>
       </x:c>
-      <x:c r="K28" s="14" t="n">
+      <x:c r="K28" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="15">
+      <x:c r="L28" s="26">
         <x:v>46080.3208564815</x:v>
       </x:c>
-      <x:c r="M28" s="11" t="s">
+      <x:c r="M28" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="11" t="s">
+      <x:c r="B29" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="s">
+      <x:c r="C29" s="22" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D29" s="12" t="s">
+      <x:c r="D29" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="s">
+      <x:c r="E29" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="s">
+      <x:c r="F29" s="22" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G29" s="11" t="s">
+      <x:c r="G29" s="22" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="H29" s="13">
+      <x:c r="H29" s="24">
         <x:v>46079.31625</x:v>
       </x:c>
-      <x:c r="I29" s="22">
+      <x:c r="I29" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J29" s="12" t="n">
+      <x:c r="J29" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="n">
+      <x:c r="K29" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="15">
+      <x:c r="L29" s="26">
         <x:v>46080.2883680556</x:v>
       </x:c>
-      <x:c r="M29" s="11" t="s">
+      <x:c r="M29" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="11" t="s">
+      <x:c r="B30" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="s">
+      <x:c r="C30" s="22" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D30" s="12" t="s">
+      <x:c r="D30" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="s">
+      <x:c r="E30" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="s">
+      <x:c r="F30" s="22" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G30" s="11" t="s">
+      <x:c r="G30" s="22" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="H30" s="13">
+      <x:c r="H30" s="24">
         <x:v>46079.3059375</x:v>
       </x:c>
-      <x:c r="I30" s="22">
+      <x:c r="I30" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J30" s="12" t="n">
+      <x:c r="J30" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K30" s="14" t="n">
+      <x:c r="K30" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L30" s="15">
+      <x:c r="L30" s="26">
         <x:v>46080.2896875</x:v>
       </x:c>
-      <x:c r="M30" s="11" t="s">
+      <x:c r="M30" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="11" t="s">
+      <x:c r="B31" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C31" s="11" t="s">
+      <x:c r="C31" s="22" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D31" s="12" t="s">
+      <x:c r="D31" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E31" s="11" t="s">
+      <x:c r="E31" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F31" s="11" t="s">
+      <x:c r="F31" s="22" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G31" s="11" t="s">
+      <x:c r="G31" s="22" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H31" s="13">
+      <x:c r="H31" s="24">
         <x:v>46079.2943981482</x:v>
       </x:c>
-      <x:c r="I31" s="22">
+      <x:c r="I31" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J31" s="12" t="n">
+      <x:c r="J31" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K31" s="14" t="n">
+      <x:c r="K31" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L31" s="15">
+      <x:c r="L31" s="26">
         <x:v>46080.2916782407</x:v>
       </x:c>
-      <x:c r="M31" s="11" t="s">
+      <x:c r="M31" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="11" t="s">
+      <x:c r="B32" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="s">
+      <x:c r="C32" s="22" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D32" s="12" t="s">
+      <x:c r="D32" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E32" s="11" t="s">
+      <x:c r="E32" s="22" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F32" s="11" t="s">
+      <x:c r="F32" s="22" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G32" s="11" t="s">
+      <x:c r="G32" s="22" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H32" s="13">
+      <x:c r="H32" s="24">
         <x:v>46079.378900463</x:v>
       </x:c>
-      <x:c r="I32" s="22">
+      <x:c r="I32" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J32" s="12" t="n">
+      <x:c r="J32" s="23" t="n">
         <x:v>1511624</x:v>
       </x:c>
-      <x:c r="K32" s="14" t="n">
+      <x:c r="K32" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L32" s="15">
+      <x:c r="L32" s="26">
         <x:v>46080.2376041667</x:v>
       </x:c>
-      <x:c r="M32" s="11" t="s">
+      <x:c r="M32" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="11" t="s">
+      <x:c r="B33" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C33" s="11" t="s">
+      <x:c r="C33" s="22" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D33" s="12" t="s">
+      <x:c r="D33" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E33" s="11" t="s">
+      <x:c r="E33" s="22" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F33" s="11" t="s">
+      <x:c r="F33" s="22" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G33" s="11" t="s">
+      <x:c r="G33" s="22" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H33" s="13">
+      <x:c r="H33" s="24">
         <x:v>46079.3728240741</x:v>
       </x:c>
-      <x:c r="I33" s="22">
+      <x:c r="I33" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J33" s="12" t="n">
+      <x:c r="J33" s="23" t="n">
         <x:v>1511625</x:v>
       </x:c>
-      <x:c r="K33" s="14" t="n">
+      <x:c r="K33" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L33" s="15">
+      <x:c r="L33" s="26">
         <x:v>46080.2394328704</x:v>
       </x:c>
-      <x:c r="M33" s="11" t="s">
+      <x:c r="M33" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="11" t="s">
+      <x:c r="B34" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C34" s="11" t="s">
+      <x:c r="C34" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D34" s="12" t="s">
+      <x:c r="D34" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E34" s="11" t="s">
+      <x:c r="E34" s="22" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F34" s="11" t="s">
+      <x:c r="F34" s="22" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G34" s="11" t="s">
+      <x:c r="G34" s="22" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H34" s="13">
+      <x:c r="H34" s="24">
         <x:v>46077.0697337963</x:v>
       </x:c>
-      <x:c r="I34" s="22">
+      <x:c r="I34" s="27">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J34" s="12" t="n">
+      <x:c r="J34" s="23" t="n">
         <x:v>1511576</x:v>
       </x:c>
-      <x:c r="K34" s="14" t="n">
+      <x:c r="K34" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L34" s="15">
+      <x:c r="L34" s="26">
         <x:v>46077.1078819444</x:v>
       </x:c>
-      <x:c r="M34" s="11" t="s">
+      <x:c r="M34" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="11" t="s">
+      <x:c r="B35" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C35" s="11" t="s">
+      <x:c r="C35" s="22" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D35" s="12" t="s">
+      <x:c r="D35" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E35" s="11" t="s">
+      <x:c r="E35" s="22" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F35" s="11" t="s">
+      <x:c r="F35" s="22" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G35" s="11" t="s">
+      <x:c r="G35" s="22" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H35" s="13">
+      <x:c r="H35" s="24">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I35" s="13">
+      <x:c r="I35" s="24">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J35" s="12" t="n">
+      <x:c r="J35" s="23" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K35" s="14" t="n">
+      <x:c r="K35" s="25" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L35" s="15">
+      <x:c r="L35" s="26">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M35" s="11" t="s">
+      <x:c r="M35" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="11" t="s">
+      <x:c r="B36" s="22" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C36" s="11" t="s">
+      <x:c r="C36" s="22" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D36" s="12" t="s">
+      <x:c r="D36" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E36" s="11" t="s">
+      <x:c r="E36" s="22" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="s">
+      <x:c r="F36" s="22" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G36" s="11" t="s">
+      <x:c r="G36" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H36" s="13">
+      <x:c r="H36" s="24">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I36" s="22">
+      <x:c r="I36" s="27">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J36" s="12" t="n">
+      <x:c r="J36" s="23" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K36" s="14" t="n">
+      <x:c r="K36" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L36" s="15">
+      <x:c r="L36" s="26">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M36" s="11" t="s">
+      <x:c r="M36" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="11" t="s">
+      <x:c r="B37" s="22" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C37" s="11" t="s">
+      <x:c r="C37" s="22" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D37" s="12" t="s">
+      <x:c r="D37" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="s">
+      <x:c r="E37" s="22" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F37" s="11" t="s">
+      <x:c r="F37" s="22" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G37" s="11" t="s">
+      <x:c r="G37" s="22" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="H37" s="13">
+      <x:c r="H37" s="24">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I37" s="22">
+      <x:c r="I37" s="27">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J37" s="12" t="n">
+      <x:c r="J37" s="23" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K37" s="14" t="n">
+      <x:c r="K37" s="25" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L37" s="15">
+      <x:c r="L37" s="26">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M37" s="11" t="s">
+      <x:c r="M37" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="11" t="s">
+      <x:c r="B38" s="22" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C38" s="11" t="s">
+      <x:c r="C38" s="22" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D38" s="12" t="s">
+      <x:c r="D38" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="s">
+      <x:c r="E38" s="22" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="F38" s="11" t="s">
+      <x:c r="F38" s="22" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G38" s="11" t="s">
+      <x:c r="G38" s="22" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="H38" s="13">
+      <x:c r="H38" s="24">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I38" s="22">
+      <x:c r="I38" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J38" s="12" t="n">
+      <x:c r="J38" s="23" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K38" s="14" t="n">
+      <x:c r="K38" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="15">
+      <x:c r="L38" s="26">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M38" s="11" t="s">
+      <x:c r="M38" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="11" t="s">
+      <x:c r="B39" s="22" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C39" s="11" t="s">
+      <x:c r="C39" s="22" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D39" s="12" t="s">
+      <x:c r="D39" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E39" s="11" t="s">
+      <x:c r="E39" s="22" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="s">
+      <x:c r="F39" s="22" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G39" s="11" t="s">
+      <x:c r="G39" s="22" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H39" s="13">
+      <x:c r="H39" s="24">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I39" s="22">
+      <x:c r="I39" s="27">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J39" s="12" t="n">
+      <x:c r="J39" s="23" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K39" s="14" t="n">
+      <x:c r="K39" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L39" s="15">
+      <x:c r="L39" s="26">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M39" s="11" t="s">
+      <x:c r="M39" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="11" t="s">
+      <x:c r="B40" s="22" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="C40" s="11" t="s">
+      <x:c r="C40" s="22" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="D40" s="12" t="s"/>
-      <x:c r="E40" s="11" t="s">
+      <x:c r="D40" s="23" t="s"/>
+      <x:c r="E40" s="22" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="F40" s="11" t="s">
+      <x:c r="F40" s="22" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="G40" s="11" t="s">
+      <x:c r="G40" s="22" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="H40" s="13">
+      <x:c r="H40" s="24">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I40" s="13">
+      <x:c r="I40" s="24">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J40" s="12" t="n">
+      <x:c r="J40" s="23" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K40" s="14" t="n">
+      <x:c r="K40" s="25" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L40" s="15">
+      <x:c r="L40" s="26">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M40" s="11" t="s">
+      <x:c r="M40" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="11" t="s">
+      <x:c r="B41" s="22" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="C41" s="11" t="s">
+      <x:c r="C41" s="22" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D41" s="12" t="s"/>
-      <x:c r="E41" s="11" t="s">
+      <x:c r="D41" s="23" t="s"/>
+      <x:c r="E41" s="22" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="F41" s="11" t="s">
+      <x:c r="F41" s="22" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G41" s="11" t="s">
+      <x:c r="G41" s="22" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H41" s="13">
+      <x:c r="H41" s="24">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I41" s="13">
+      <x:c r="I41" s="24">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J41" s="12" t="n">
+      <x:c r="J41" s="23" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K41" s="14" t="n">
+      <x:c r="K41" s="25" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L41" s="15">
+      <x:c r="L41" s="26">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M41" s="11" t="s">
+      <x:c r="M41" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="23" t="s">
+    <x:row r="42" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B42" s="28" t="s"/>
+      <x:c r="C42" s="28" t="s"/>
+      <x:c r="D42" s="28" t="s"/>
+      <x:c r="E42" s="28" t="s"/>
+      <x:c r="F42" s="28" t="s"/>
+      <x:c r="G42" s="28" t="s"/>
+      <x:c r="H42" s="28" t="s"/>
+      <x:c r="I42" s="28" t="s"/>
+      <x:c r="J42" s="28" t="s"/>
+      <x:c r="K42" s="28" t="s"/>
+      <x:c r="L42" s="28" t="s"/>
+      <x:c r="M42" s="28" t="s"/>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B43" s="28" t="s"/>
+      <x:c r="C43" s="28" t="s"/>
+      <x:c r="D43" s="28" t="s"/>
+      <x:c r="E43" s="28" t="s"/>
+      <x:c r="F43" s="28" t="s"/>
+      <x:c r="G43" s="28" t="s"/>
+      <x:c r="H43" s="28" t="s"/>
+      <x:c r="I43" s="28" t="s"/>
+      <x:c r="J43" s="28" t="s"/>
+      <x:c r="K43" s="28" t="s"/>
+      <x:c r="L43" s="28" t="s"/>
+      <x:c r="M43" s="28" t="s"/>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="29" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="C44" s="24" t="s"/>
-      <x:c r="D44" s="24" t="s"/>
-      <x:c r="E44" s="25" t="s"/>
-      <x:c r="F44" s="25" t="s"/>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B45" s="26" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C45" s="27" t="s"/>
-      <x:c r="D45" s="27" t="s"/>
-      <x:c r="E45" s="27" t="s"/>
-      <x:c r="F45" s="28" t="s">
-        <x:v>158</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="29" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C46" s="30" t="s"/>
       <x:c r="D46" s="30" t="s"/>
-      <x:c r="E46" s="30" t="s"/>
-      <x:c r="F46" s="31" t="n">
+      <x:c r="E46" s="31" t="s"/>
+      <x:c r="F46" s="31" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B47" s="32" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C47" s="33" t="s"/>
+      <x:c r="D47" s="33" t="s"/>
+      <x:c r="E47" s="33" t="s"/>
+      <x:c r="F47" s="34" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="35" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C48" s="36" t="s"/>
+      <x:c r="D48" s="36" t="s"/>
+      <x:c r="E48" s="36" t="s"/>
+      <x:c r="F48" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="35" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C49" s="36" t="s"/>
+      <x:c r="D49" s="36" t="s"/>
+      <x:c r="E49" s="36" t="s"/>
+      <x:c r="F49" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="35" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C50" s="36" t="s"/>
+      <x:c r="D50" s="36" t="s"/>
+      <x:c r="E50" s="36" t="s"/>
+      <x:c r="F50" s="37" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="35" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C51" s="36" t="s"/>
+      <x:c r="D51" s="36" t="s"/>
+      <x:c r="E51" s="36" t="s"/>
+      <x:c r="F51" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="35" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C52" s="36" t="s"/>
+      <x:c r="D52" s="36" t="s"/>
+      <x:c r="E52" s="36" t="s"/>
+      <x:c r="F52" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="35" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C53" s="36" t="s"/>
+      <x:c r="D53" s="36" t="s"/>
+      <x:c r="E53" s="36" t="s"/>
+      <x:c r="F53" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="35" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C54" s="36" t="s"/>
+      <x:c r="D54" s="36" t="s"/>
+      <x:c r="E54" s="36" t="s"/>
+      <x:c r="F54" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="35" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C55" s="36" t="s"/>
+      <x:c r="D55" s="36" t="s"/>
+      <x:c r="E55" s="36" t="s"/>
+      <x:c r="F55" s="37" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="35" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C56" s="36" t="s"/>
+      <x:c r="D56" s="36" t="s"/>
+      <x:c r="E56" s="36" t="s"/>
+      <x:c r="F56" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B57" s="38" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C57" s="39" t="s"/>
+      <x:c r="D57" s="39" t="s"/>
+      <x:c r="E57" s="39" t="s"/>
+      <x:c r="F57" s="40" t="n">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="15">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B46:F46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H8" s="20">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I9" s="20">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="22" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D10" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G10" s="22" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H10" s="24">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I10" s="24">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J10" s="23" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K10" s="25" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="26">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M10" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D11" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F11" s="22" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G11" s="22" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H11" s="24">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I11" s="27">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J11" s="23" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K11" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="26">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M11" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H12" s="24">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I12" s="27">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J12" s="23" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K12" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="26">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M12" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F13" s="22" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G13" s="22" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H13" s="24">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I13" s="27">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J13" s="23" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K13" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="26">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M13" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F14" s="22" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G14" s="22" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H14" s="24">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I14" s="27">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J14" s="23" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K14" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="26">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M14" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F15" s="22" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G15" s="22" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H15" s="24">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I15" s="27">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J15" s="23" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K15" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="26">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M15" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F16" s="22" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G16" s="22" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H16" s="24">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I16" s="27">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J16" s="23" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K16" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="26">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M16" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F17" s="22" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G17" s="22" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H17" s="24">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I17" s="27">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J17" s="23" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K17" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="26">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M17" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F18" s="22" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G18" s="22" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H18" s="24">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I18" s="27">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J18" s="23" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K18" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="26">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M18" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F19" s="22" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G19" s="22" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H19" s="24">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I19" s="27">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J19" s="23" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K19" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="26">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M19" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F20" s="22" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G20" s="22" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H20" s="24">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I20" s="27">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J20" s="23" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K20" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="26">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M20" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F21" s="22" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G21" s="22" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H21" s="24">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I21" s="27">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J21" s="23" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K21" s="25" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="26">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M21" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F22" s="22" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G22" s="22" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H22" s="24">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I22" s="27">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J22" s="23" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K22" s="25" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L22" s="26">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M22" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E23" s="22" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F23" s="22" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G23" s="22" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H23" s="24">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I23" s="27">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="23" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K23" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="26">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M23" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E24" s="22" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F24" s="22" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G24" s="22" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H24" s="24">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I24" s="27">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J24" s="23" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K24" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="26">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M24" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D25" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E25" s="22" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F25" s="22" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G25" s="22" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H25" s="24">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I25" s="27">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J25" s="23" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K25" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="26">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M25" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C26" s="22" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D26" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E26" s="22" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F26" s="22" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G26" s="22" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H26" s="24">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I26" s="27">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J26" s="23" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K26" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="26">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M26" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E27" s="22" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F27" s="22" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G27" s="22" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H27" s="24">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I27" s="27">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J27" s="23" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K27" s="25" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L27" s="26">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M27" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C28" s="22" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D28" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E28" s="22" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F28" s="22" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G28" s="22" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H28" s="24">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I28" s="27">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J28" s="23" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K28" s="25" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L28" s="26">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M28" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C29" s="22" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D29" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E29" s="22" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F29" s="22" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G29" s="22" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H29" s="24">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I29" s="27">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J29" s="23" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K29" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="26">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M29" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C30" s="22" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D30" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E30" s="22" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F30" s="22" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G30" s="22" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H30" s="24">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I30" s="27">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J30" s="23" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K30" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="26">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M30" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="22" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C31" s="22" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E31" s="22" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F31" s="22" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G31" s="22" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H31" s="24">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I31" s="24">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J31" s="23" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K31" s="25" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L31" s="26">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M31" s="22" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="22" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C32" s="22" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D32" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E32" s="22" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F32" s="22" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G32" s="22" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H32" s="24">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I32" s="24">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J32" s="23" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K32" s="25" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L32" s="26">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M32" s="22" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="22" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C33" s="22" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D33" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E33" s="22" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F33" s="22" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G33" s="22" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H33" s="24">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I33" s="24">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J33" s="23" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K33" s="25" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L33" s="26">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M33" s="22" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="22" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C34" s="22" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D34" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E34" s="22" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F34" s="22" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G34" s="22" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H34" s="24">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I34" s="24">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J34" s="23" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K34" s="25" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L34" s="26">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M34" s="22" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C35" s="22" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D35" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E35" s="22" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F35" s="22" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G35" s="22" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H35" s="24">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I35" s="27">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J35" s="23" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K35" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="26">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M35" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C36" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D36" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E36" s="22" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F36" s="22" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G36" s="22" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H36" s="24">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I36" s="27">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J36" s="23" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K36" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="26">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M36" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C37" s="22" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D37" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E37" s="22" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F37" s="22" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G37" s="22" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H37" s="24">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I37" s="27">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J37" s="23" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K37" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="26">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M37" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C38" s="22" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D38" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E38" s="22" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="F38" s="22" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G38" s="22" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H38" s="24">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I38" s="27">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J38" s="23" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K38" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="26">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M38" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C39" s="22" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D39" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E39" s="22" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F39" s="22" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G39" s="22" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H39" s="24">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I39" s="27">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J39" s="23" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K39" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L39" s="26">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M39" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C40" s="22" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D40" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E40" s="22" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F40" s="22" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G40" s="22" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H40" s="24">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I40" s="27">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J40" s="23" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K40" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L40" s="26">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M40" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="22" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C41" s="22" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D41" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E41" s="22" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F41" s="22" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G41" s="22" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H41" s="24">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I41" s="27">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J41" s="23" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K41" s="25" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L41" s="26">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M41" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="22" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C42" s="22" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D42" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E42" s="22" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F42" s="22" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G42" s="22" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H42" s="24">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I42" s="27">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J42" s="23" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K42" s="25" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L42" s="26">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M42" s="22" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B43" s="28" t="s"/>
+      <x:c r="C43" s="28" t="s"/>
+      <x:c r="D43" s="28" t="s"/>
+      <x:c r="E43" s="28" t="s"/>
+      <x:c r="F43" s="28" t="s"/>
+      <x:c r="G43" s="28" t="s"/>
+      <x:c r="H43" s="28" t="s"/>
+      <x:c r="I43" s="28" t="s"/>
+      <x:c r="J43" s="28" t="s"/>
+      <x:c r="K43" s="28" t="s"/>
+      <x:c r="L43" s="28" t="s"/>
+      <x:c r="M43" s="28" t="s"/>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B44" s="28" t="s"/>
+      <x:c r="C44" s="28" t="s"/>
+      <x:c r="D44" s="28" t="s"/>
+      <x:c r="E44" s="28" t="s"/>
+      <x:c r="F44" s="28" t="s"/>
+      <x:c r="G44" s="28" t="s"/>
+      <x:c r="H44" s="28" t="s"/>
+      <x:c r="I44" s="28" t="s"/>
+      <x:c r="J44" s="28" t="s"/>
+      <x:c r="K44" s="28" t="s"/>
+      <x:c r="L44" s="28" t="s"/>
+      <x:c r="M44" s="28" t="s"/>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
       <x:c r="B47" s="29" t="s">
-        <x:v>28</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C47" s="30" t="s"/>
       <x:c r="D47" s="30" t="s"/>
-      <x:c r="E47" s="30" t="s"/>
-      <x:c r="F47" s="31" t="n">
+      <x:c r="E47" s="31" t="s"/>
+      <x:c r="F47" s="31" t="s"/>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B48" s="32" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C48" s="33" t="s"/>
+      <x:c r="D48" s="33" t="s"/>
+      <x:c r="E48" s="33" t="s"/>
+      <x:c r="F48" s="34" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="35" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C49" s="36" t="s"/>
+      <x:c r="D49" s="36" t="s"/>
+      <x:c r="E49" s="36" t="s"/>
+      <x:c r="F49" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="29" t="s">
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="35" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C50" s="36" t="s"/>
+      <x:c r="D50" s="36" t="s"/>
+      <x:c r="E50" s="36" t="s"/>
+      <x:c r="F50" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="35" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C48" s="30" t="s"/>
-      <x:c r="D48" s="30" t="s"/>
-      <x:c r="E48" s="30" t="s"/>
-      <x:c r="F48" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="29" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C49" s="30" t="s"/>
-      <x:c r="D49" s="30" t="s"/>
-      <x:c r="E49" s="30" t="s"/>
-      <x:c r="F49" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="29" t="s">
+      <x:c r="C51" s="36" t="s"/>
+      <x:c r="D51" s="36" t="s"/>
+      <x:c r="E51" s="36" t="s"/>
+      <x:c r="F51" s="37" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="35" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C50" s="30" t="s"/>
-      <x:c r="D50" s="30" t="s"/>
-      <x:c r="E50" s="30" t="s"/>
-      <x:c r="F50" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="29" t="s">
+      <x:c r="C52" s="36" t="s"/>
+      <x:c r="D52" s="36" t="s"/>
+      <x:c r="E52" s="36" t="s"/>
+      <x:c r="F52" s="37" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="35" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C51" s="30" t="s"/>
-      <x:c r="D51" s="30" t="s"/>
-      <x:c r="E51" s="30" t="s"/>
-      <x:c r="F51" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="29" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C52" s="30" t="s"/>
-      <x:c r="D52" s="30" t="s"/>
-      <x:c r="E52" s="30" t="s"/>
-      <x:c r="F52" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="29" t="s">
+      <x:c r="C53" s="36" t="s"/>
+      <x:c r="D53" s="36" t="s"/>
+      <x:c r="E53" s="36" t="s"/>
+      <x:c r="F53" s="37" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="35" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C53" s="30" t="s"/>
-      <x:c r="D53" s="30" t="s"/>
-      <x:c r="E53" s="30" t="s"/>
-      <x:c r="F53" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="29" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C54" s="30" t="s"/>
-      <x:c r="D54" s="30" t="s"/>
-      <x:c r="E54" s="30" t="s"/>
-      <x:c r="F54" s="31" t="n">
+      <x:c r="C54" s="36" t="s"/>
+      <x:c r="D54" s="36" t="s"/>
+      <x:c r="E54" s="36" t="s"/>
+      <x:c r="F54" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="32" t="s">
+      <x:c r="B55" s="38" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C55" s="33" t="s"/>
-      <x:c r="D55" s="33" t="s"/>
-      <x:c r="E55" s="33" t="s"/>
-      <x:c r="F55" s="34" t="n">
-        <x:v>36</x:v>
+      <x:c r="C55" s="39" t="s"/>
+      <x:c r="D55" s="39" t="s"/>
+      <x:c r="E55" s="39" t="s"/>
+      <x:c r="F55" s="40" t="n">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4188,13 +6865,11 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="14">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B44:F44"/>
-    <x:mergeCell ref="B45:E45"/>
-    <x:mergeCell ref="B46:E46"/>
-    <x:mergeCell ref="B47:E47"/>
+  <x:mergeCells count="12">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B47:F47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
@@ -4217,2601 +6892,4 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="0" summaryRight="0"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:AB993"/>
-  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
-  <x:cols>
-    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
-    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
-    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
-      <x:c r="N5" s="4" t="s"/>
-      <x:c r="O5" s="5" t="s"/>
-      <x:c r="P5" s="5" t="s"/>
-      <x:c r="Q5" s="5" t="s"/>
-      <x:c r="R5" s="5" t="s"/>
-      <x:c r="S5" s="5" t="s"/>
-      <x:c r="T5" s="5" t="s"/>
-      <x:c r="U5" s="5" t="s"/>
-      <x:c r="V5" s="5" t="s"/>
-      <x:c r="W5" s="5" t="s"/>
-      <x:c r="X5" s="5" t="s"/>
-      <x:c r="Y5" s="5" t="s"/>
-      <x:c r="Z5" s="5" t="s"/>
-      <x:c r="AA5" s="5" t="s"/>
-      <x:c r="AB5" s="5" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="N6" s="6" t="s"/>
-      <x:c r="O6" s="7" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I8" s="20">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J8" s="19" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K8" s="21" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I9" s="20">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J9" s="19" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K9" s="21" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H10" s="13">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I10" s="13">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K10" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="15">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H11" s="13">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I11" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K11" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="15">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H12" s="13">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I12" s="22">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K12" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="15">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H13" s="13">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I13" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J13" s="12" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K13" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="15">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M13" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H14" s="13">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I14" s="22">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J14" s="12" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K14" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="15">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M14" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H15" s="13">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I15" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K15" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="15">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M15" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H16" s="13">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I16" s="22">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J16" s="12" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K16" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="15">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M16" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H17" s="13">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I17" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J17" s="12" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K17" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="15">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M17" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F18" s="11" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G18" s="11" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H18" s="13">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I18" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J18" s="12" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K18" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="15">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M18" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H19" s="13">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I19" s="22">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J19" s="12" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K19" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="15">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M19" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H20" s="13">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I20" s="22">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J20" s="12" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K20" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="15">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M20" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H21" s="13">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I21" s="22">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J21" s="12" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K21" s="14" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L21" s="15">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M21" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C22" s="11" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H22" s="13">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I22" s="22">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J22" s="12" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K22" s="14" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L22" s="15">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M22" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C23" s="11" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H23" s="13">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I23" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J23" s="12" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K23" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="15">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M23" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C24" s="11" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="D24" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G24" s="11" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H24" s="13">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I24" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J24" s="12" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K24" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="15">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M24" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C25" s="11" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D25" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H25" s="13">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I25" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J25" s="12" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K25" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="15">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M25" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D26" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H26" s="13">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I26" s="22">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J26" s="12" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K26" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="15">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M26" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D27" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="G27" s="11" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="H27" s="13">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I27" s="22">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J27" s="12" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K27" s="14" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L27" s="15">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M27" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D28" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H28" s="13">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I28" s="22">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J28" s="12" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K28" s="14" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L28" s="15">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M28" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C29" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G29" s="11" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H29" s="13">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I29" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J29" s="12" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K29" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="15">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M29" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D30" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H30" s="13">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I30" s="22">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J30" s="12" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K30" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="15">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M30" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C31" s="11" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D31" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G31" s="11" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="H31" s="13">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I31" s="13">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J31" s="12" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K31" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L31" s="15">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M31" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C32" s="11" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D32" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="G32" s="11" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="H32" s="13">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I32" s="13">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J32" s="12" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K32" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L32" s="15">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M32" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C33" s="11" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D33" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G33" s="11" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H33" s="13">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I33" s="13">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J33" s="12" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K33" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L33" s="15">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M33" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C34" s="11" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D34" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G34" s="11" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H34" s="13">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I34" s="13">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J34" s="12" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K34" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L34" s="15">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M34" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C35" s="11" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D35" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G35" s="11" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H35" s="13">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I35" s="22">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J35" s="12" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K35" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="15">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M35" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C36" s="11" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D36" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E36" s="11" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F36" s="11" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G36" s="11" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H36" s="13">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I36" s="22">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J36" s="12" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K36" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="15">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M36" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C37" s="11" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="D37" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E37" s="11" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="F37" s="11" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="G37" s="11" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H37" s="13">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I37" s="22">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J37" s="12" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K37" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="15">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M37" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C38" s="11" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D38" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E38" s="11" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F38" s="11" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G38" s="11" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="H38" s="13">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I38" s="22">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J38" s="12" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K38" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="15">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M38" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C39" s="11" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D39" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E39" s="11" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="F39" s="11" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="G39" s="11" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="H39" s="13">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I39" s="22">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J39" s="12" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K39" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L39" s="15">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M39" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C40" s="11" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D40" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E40" s="11" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="F40" s="11" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="G40" s="11" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="H40" s="13">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I40" s="22">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J40" s="12" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K40" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L40" s="15">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M40" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="11" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C41" s="11" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="D41" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E41" s="11" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F41" s="11" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G41" s="11" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H41" s="13">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I41" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J41" s="12" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K41" s="14" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L41" s="15">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M41" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="11" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C42" s="11" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D42" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="F42" s="11" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G42" s="11" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="H42" s="13">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I42" s="22">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J42" s="12" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K42" s="14" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L42" s="15">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M42" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="23" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C45" s="24" t="s"/>
-      <x:c r="D45" s="24" t="s"/>
-      <x:c r="E45" s="25" t="s"/>
-      <x:c r="F45" s="25" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="26" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C46" s="27" t="s"/>
-      <x:c r="D46" s="27" t="s"/>
-      <x:c r="E46" s="27" t="s"/>
-      <x:c r="F46" s="28" t="s">
-        <x:v>158</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="29" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C47" s="30" t="s"/>
-      <x:c r="D47" s="30" t="s"/>
-      <x:c r="E47" s="30" t="s"/>
-      <x:c r="F47" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C48" s="30" t="s"/>
-      <x:c r="D48" s="30" t="s"/>
-      <x:c r="E48" s="30" t="s"/>
-      <x:c r="F48" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C49" s="30" t="s"/>
-      <x:c r="D49" s="30" t="s"/>
-      <x:c r="E49" s="30" t="s"/>
-      <x:c r="F49" s="31" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="29" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C50" s="30" t="s"/>
-      <x:c r="D50" s="30" t="s"/>
-      <x:c r="E50" s="30" t="s"/>
-      <x:c r="F50" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="29" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C51" s="30" t="s"/>
-      <x:c r="D51" s="30" t="s"/>
-      <x:c r="E51" s="30" t="s"/>
-      <x:c r="F51" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="29" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C52" s="30" t="s"/>
-      <x:c r="D52" s="30" t="s"/>
-      <x:c r="E52" s="30" t="s"/>
-      <x:c r="F52" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B53" s="32" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C53" s="33" t="s"/>
-      <x:c r="D53" s="33" t="s"/>
-      <x:c r="E53" s="33" t="s"/>
-      <x:c r="F53" s="34" t="n">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
-  </x:sheetData>
-  <x:mergeCells count="11">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
-    <x:mergeCell ref="B47:E47"/>
-    <x:mergeCell ref="B48:E48"/>
-    <x:mergeCell ref="B49:E49"/>
-    <x:mergeCell ref="B50:E50"/>
-    <x:mergeCell ref="B51:E51"/>
-    <x:mergeCell ref="B52:E52"/>
-    <x:mergeCell ref="B53:E53"/>
-  </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
-</x:worksheet>
 </file>
--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="303">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -568,6 +568,24 @@
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
     <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
   </x:si>
   <x:si>
@@ -577,24 +595,6 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
-    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1150-325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0780 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1151-716</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -622,6 +622,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -631,15 +640,6 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-020R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1156-896</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -652,6 +652,24 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -661,24 +679,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -703,6 +703,18 @@
     <x:t>43A-3-2026-1152-831</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBILECRAZE TELECOM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-06-0809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1159-651</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -730,9 +742,6 @@
     <x:t>SYNCNETIC INC</x:t>
   </x:si>
   <x:si>
-    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-MP-24-468R</x:t>
   </x:si>
   <x:si>
@@ -742,6 +751,24 @@
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-18-05-0718</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1083-282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
     <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -751,15 +778,6 @@
     <x:t>43A-2-2026-1108-762</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-02-25-0452R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1168-173</x:t>
-  </x:si>
-  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -769,6 +787,18 @@
     <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
+    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3, 306A, BRGY. TEJERO, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-05-0452-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1084-395</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -784,6 +814,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
   </x:si>
   <x:si>
@@ -793,24 +841,6 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -853,6 +883,15 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -869,15 +908,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -1756,7 +1786,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1824,7 +1854,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -4362,7 +4392,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -4430,7 +4460,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -4603,19 +4633,19 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H11" s="24">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I11" s="27">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J11" s="23" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K11" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="26">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M11" s="22" t="s">
         <x:v>172</x:v>
@@ -4679,19 +4709,19 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="H13" s="24">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I13" s="27">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J13" s="23" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K13" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="26">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M13" s="22" t="s">
         <x:v>172</x:v>
@@ -4793,19 +4823,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H16" s="24">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I16" s="27">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J16" s="23" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K16" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="26">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M16" s="22" t="s">
         <x:v>172</x:v>
@@ -4831,19 +4861,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H17" s="24">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I17" s="27">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J17" s="23" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K17" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="26">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M17" s="22" t="s">
         <x:v>172</x:v>
@@ -4907,19 +4937,19 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="H19" s="24">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I19" s="27">
-        <x:v>46133</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J19" s="23" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K19" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="26">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M19" s="22" t="s">
         <x:v>172</x:v>
@@ -4983,19 +5013,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="H21" s="24">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I21" s="27">
-        <x:v>46035</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J21" s="23" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K21" s="25" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="26">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M21" s="22" t="s">
         <x:v>172</x:v>
@@ -5097,19 +5127,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="H24" s="24">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I24" s="27">
-        <x:v>46100</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J24" s="23" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K24" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="26">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M24" s="22" t="s">
         <x:v>172</x:v>
@@ -5135,19 +5165,19 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H25" s="24">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I25" s="27">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J25" s="23" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K25" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="26">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M25" s="22" t="s">
         <x:v>172</x:v>
@@ -5173,19 +5203,19 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H26" s="24">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I26" s="27">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J26" s="23" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K26" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="26">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M26" s="22" t="s">
         <x:v>172</x:v>
@@ -5202,28 +5232,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="22" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F27" s="22" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="F27" s="22" t="s">
+      <x:c r="G27" s="22" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G27" s="22" t="s">
-        <x:v>241</x:v>
-      </x:c>
       <x:c r="H27" s="24">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I27" s="27">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J27" s="23" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K27" s="25" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="26">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M27" s="22" t="s">
         <x:v>172</x:v>
@@ -5234,7 +5264,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="22" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D28" s="23" t="s">
         <x:v>40</x:v>
@@ -5249,19 +5279,19 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H28" s="24">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I28" s="27">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J28" s="23" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K28" s="25" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="26">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M28" s="22" t="s">
         <x:v>172</x:v>
@@ -5272,7 +5302,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="22" t="s">
-        <x:v>56</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D29" s="23" t="s">
         <x:v>40</x:v>
@@ -5287,19 +5317,19 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H29" s="24">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I29" s="27">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J29" s="23" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K29" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L29" s="26">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M29" s="22" t="s">
         <x:v>172</x:v>
@@ -5310,124 +5340,124 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="22" t="s">
-        <x:v>248</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D30" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E30" s="22" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F30" s="22" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="F30" s="22" t="s">
+      <x:c r="G30" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="G30" s="22" t="s">
-        <x:v>251</x:v>
-      </x:c>
       <x:c r="H30" s="24">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I30" s="27">
-        <x:v>46095</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J30" s="23" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K30" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L30" s="26">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M30" s="22" t="s">
-        <x:v>71</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B31" s="22" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="22" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E31" s="22" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F31" s="22" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="D31" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E31" s="22" t="s">
+      <x:c r="G31" s="22" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="F31" s="22" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G31" s="22" t="s">
-        <x:v>255</x:v>
-      </x:c>
       <x:c r="H31" s="24">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I31" s="24">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I31" s="27">
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J31" s="23" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K31" s="25" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="26">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M31" s="22" t="s">
-        <x:v>11</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B32" s="22" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C32" s="22" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D32" s="23" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E32" s="22" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F32" s="22" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="F32" s="22" t="s">
+      <x:c r="G32" s="22" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="G32" s="22" t="s">
-        <x:v>258</x:v>
-      </x:c>
       <x:c r="H32" s="24">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I32" s="24">
-        <x:v>46085.1709375</x:v>
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I32" s="27">
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J32" s="23" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K32" s="25" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="26">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M32" s="22" t="s">
-        <x:v>11</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B33" s="22" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C33" s="22" t="s">
-        <x:v>252</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D33" s="23" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E33" s="22" t="s">
         <x:v>259</x:v>
@@ -5439,22 +5469,22 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="H33" s="24">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I33" s="24">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I33" s="27">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J33" s="23" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K33" s="25" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="26">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M33" s="22" t="s">
-        <x:v>11</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5462,25 +5492,25 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C34" s="22" t="s">
-        <x:v>252</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D34" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E34" s="22" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="F34" s="22" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="G34" s="22" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="H34" s="24">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I34" s="24">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J34" s="23" t="n">
         <x:v>1507966</x:v>
@@ -5489,7 +5519,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L34" s="26">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M34" s="22" t="s">
         <x:v>11</x:v>
@@ -5497,13 +5527,13 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B35" s="22" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C35" s="22" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D35" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E35" s="22" t="s">
         <x:v>266</x:v>
@@ -5515,33 +5545,33 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="H35" s="24">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I35" s="27">
-        <x:v>46145</x:v>
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I35" s="24">
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J35" s="23" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K35" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L35" s="26">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M35" s="22" t="s">
-        <x:v>172</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B36" s="22" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C36" s="22" t="s">
-        <x:v>198</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D36" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E36" s="22" t="s">
         <x:v>269</x:v>
@@ -5553,60 +5583,60 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="H36" s="24">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I36" s="27">
-        <x:v>46103</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I36" s="24">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J36" s="23" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K36" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="26">
-        <x:v>46097.2478125</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M36" s="22" t="s">
-        <x:v>172</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B37" s="22" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C37" s="22" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D37" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E37" s="22" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D37" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E37" s="22" t="s">
+      <x:c r="F37" s="22" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="F37" s="22" t="s">
+      <x:c r="G37" s="22" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="G37" s="22" t="s">
-        <x:v>275</x:v>
-      </x:c>
       <x:c r="H37" s="24">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I37" s="27">
-        <x:v>46084</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I37" s="24">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J37" s="23" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K37" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="26">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M37" s="22" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5614,7 +5644,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C38" s="22" t="s">
-        <x:v>248</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D38" s="23" t="s">
         <x:v>40</x:v>
@@ -5629,22 +5659,22 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="H38" s="24">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I38" s="27">
-        <x:v>46097</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J38" s="23" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K38" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="26">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M38" s="22" t="s">
-        <x:v>71</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -5652,7 +5682,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C39" s="22" t="s">
-        <x:v>248</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D39" s="23" t="s">
         <x:v>40</x:v>
@@ -5667,22 +5697,22 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="H39" s="24">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I39" s="27">
-        <x:v>46104</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J39" s="23" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K39" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="26">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M39" s="22" t="s">
-        <x:v>71</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
@@ -5690,34 +5720,34 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C40" s="22" t="s">
-        <x:v>248</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D40" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E40" s="22" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="F40" s="22" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G40" s="22" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H40" s="24">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I40" s="27">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J40" s="23" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K40" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="26">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M40" s="22" t="s">
         <x:v>71</x:v>
@@ -5725,10 +5755,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="22" t="s">
-        <x:v>130</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C41" s="22" t="s">
-        <x:v>285</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D41" s="23" t="s">
         <x:v>40</x:v>
@@ -5743,192 +5773,303 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="H41" s="24">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I41" s="27">
-        <x:v>46094</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J41" s="23" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K41" s="25" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L41" s="26">
-        <x:v>46093.3109375</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M41" s="22" t="s">
-        <x:v>172</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="22" t="s">
-        <x:v>130</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C42" s="22" t="s">
-        <x:v>289</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D42" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E42" s="22" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="F42" s="22" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="F42" s="22" t="s">
+      <x:c r="G42" s="22" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="G42" s="22" t="s">
+      <x:c r="H42" s="24">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I42" s="27">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J42" s="23" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K42" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="26">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M42" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C43" s="22" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D43" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E43" s="22" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="H42" s="24">
+      <x:c r="F43" s="22" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G43" s="22" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H43" s="24">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I43" s="27">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J43" s="23" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K43" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="26">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M43" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="22" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C44" s="22" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D44" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E44" s="22" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F44" s="22" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G44" s="22" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H44" s="24">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I44" s="27">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J44" s="23" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K44" s="25" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L44" s="26">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M44" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="22" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C45" s="22" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="D45" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E45" s="22" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F45" s="22" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G45" s="22" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H45" s="24">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I42" s="27">
+      <x:c r="I45" s="27">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J42" s="23" t="n">
+      <x:c r="J45" s="23" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K42" s="25" t="n">
+      <x:c r="K45" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L42" s="26">
+      <x:c r="L45" s="26">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M42" s="22" t="s">
+      <x:c r="M45" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B43" s="28" t="s"/>
-      <x:c r="C43" s="28" t="s"/>
-      <x:c r="D43" s="28" t="s"/>
-      <x:c r="E43" s="28" t="s"/>
-      <x:c r="F43" s="28" t="s"/>
-      <x:c r="G43" s="28" t="s"/>
-      <x:c r="H43" s="28" t="s"/>
-      <x:c r="I43" s="28" t="s"/>
-      <x:c r="J43" s="28" t="s"/>
-      <x:c r="K43" s="28" t="s"/>
-      <x:c r="L43" s="28" t="s"/>
-      <x:c r="M43" s="28" t="s"/>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B44" s="28" t="s"/>
-      <x:c r="C44" s="28" t="s"/>
-      <x:c r="D44" s="28" t="s"/>
-      <x:c r="E44" s="28" t="s"/>
-      <x:c r="F44" s="28" t="s"/>
-      <x:c r="G44" s="28" t="s"/>
-      <x:c r="H44" s="28" t="s"/>
-      <x:c r="I44" s="28" t="s"/>
-      <x:c r="J44" s="28" t="s"/>
-      <x:c r="K44" s="28" t="s"/>
-      <x:c r="L44" s="28" t="s"/>
-      <x:c r="M44" s="28" t="s"/>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="29" t="s">
+    <x:row r="46" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B46" s="28" t="s"/>
+      <x:c r="C46" s="28" t="s"/>
+      <x:c r="D46" s="28" t="s"/>
+      <x:c r="E46" s="28" t="s"/>
+      <x:c r="F46" s="28" t="s"/>
+      <x:c r="G46" s="28" t="s"/>
+      <x:c r="H46" s="28" t="s"/>
+      <x:c r="I46" s="28" t="s"/>
+      <x:c r="J46" s="28" t="s"/>
+      <x:c r="K46" s="28" t="s"/>
+      <x:c r="L46" s="28" t="s"/>
+      <x:c r="M46" s="28" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B47" s="28" t="s"/>
+      <x:c r="C47" s="28" t="s"/>
+      <x:c r="D47" s="28" t="s"/>
+      <x:c r="E47" s="28" t="s"/>
+      <x:c r="F47" s="28" t="s"/>
+      <x:c r="G47" s="28" t="s"/>
+      <x:c r="H47" s="28" t="s"/>
+      <x:c r="I47" s="28" t="s"/>
+      <x:c r="J47" s="28" t="s"/>
+      <x:c r="K47" s="28" t="s"/>
+      <x:c r="L47" s="28" t="s"/>
+      <x:c r="M47" s="28" t="s"/>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="C47" s="30" t="s"/>
-      <x:c r="D47" s="30" t="s"/>
-      <x:c r="E47" s="31" t="s"/>
-      <x:c r="F47" s="31" t="s"/>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B48" s="32" t="s">
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="31" t="s"/>
+      <x:c r="F50" s="31" t="s"/>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B51" s="32" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="C48" s="33" t="s"/>
-      <x:c r="D48" s="33" t="s"/>
-      <x:c r="E48" s="33" t="s"/>
-      <x:c r="F48" s="34" t="s">
+      <x:c r="C51" s="33" t="s"/>
+      <x:c r="D51" s="33" t="s"/>
+      <x:c r="E51" s="33" t="s"/>
+      <x:c r="F51" s="34" t="s">
         <x:v>158</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="35" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C49" s="36" t="s"/>
-      <x:c r="D49" s="36" t="s"/>
-      <x:c r="E49" s="36" t="s"/>
-      <x:c r="F49" s="37" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C50" s="36" t="s"/>
-      <x:c r="D50" s="36" t="s"/>
-      <x:c r="E50" s="36" t="s"/>
-      <x:c r="F50" s="37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="35" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C51" s="36" t="s"/>
-      <x:c r="D51" s="36" t="s"/>
-      <x:c r="E51" s="36" t="s"/>
-      <x:c r="F51" s="37" t="n">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
       <x:c r="B52" s="35" t="s">
-        <x:v>66</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C52" s="36" t="s"/>
       <x:c r="D52" s="36" t="s"/>
       <x:c r="E52" s="36" t="s"/>
       <x:c r="F52" s="37" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
       <x:c r="B53" s="35" t="s">
-        <x:v>80</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C53" s="36" t="s"/>
       <x:c r="D53" s="36" t="s"/>
       <x:c r="E53" s="36" t="s"/>
       <x:c r="F53" s="37" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
       <x:c r="B54" s="35" t="s">
-        <x:v>130</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C54" s="36" t="s"/>
       <x:c r="D54" s="36" t="s"/>
       <x:c r="E54" s="36" t="s"/>
       <x:c r="F54" s="37" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="35" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C55" s="36" t="s"/>
+      <x:c r="D55" s="36" t="s"/>
+      <x:c r="E55" s="36" t="s"/>
+      <x:c r="F55" s="37" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="35" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C56" s="36" t="s"/>
+      <x:c r="D56" s="36" t="s"/>
+      <x:c r="E56" s="36" t="s"/>
+      <x:c r="F56" s="37" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="35" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C57" s="36" t="s"/>
+      <x:c r="D57" s="36" t="s"/>
+      <x:c r="E57" s="36" t="s"/>
+      <x:c r="F57" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="38" t="s">
+    <x:row r="58" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B58" s="38" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C55" s="39" t="s"/>
-      <x:c r="D55" s="39" t="s"/>
-      <x:c r="E55" s="39" t="s"/>
-      <x:c r="F55" s="40" t="n">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C58" s="39" t="s"/>
+      <x:c r="D58" s="39" t="s"/>
+      <x:c r="E58" s="39" t="s"/>
+      <x:c r="F58" s="40" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6869,15 +7010,15 @@
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
     <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B47:F47"/>
-    <x:mergeCell ref="B48:E48"/>
-    <x:mergeCell ref="B49:E49"/>
-    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B50:F50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
+    <x:mergeCell ref="B58:E58"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,9 +23,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="303">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -941,7 +977,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -986,21 +1022,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -1010,6 +1031,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1260,7 +1288,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1271,10 +1299,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1283,62 +1317,50 @@
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1369,56 +1391,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1433,63 +1407,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1788,18 +1774,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1817,1517 +1791,1529 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s"/>
-      <x:c r="E8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="F8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46069.0835648148</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>46069.1000231481</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1506159</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46069.1128587963</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46072.1720833333</x:v>
       </x:c>
-      <x:c r="I9" s="20">
+      <x:c r="I11" s="16">
         <x:v>46072.235162037</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1507783</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>46073.1890277778</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s"/>
-      <x:c r="E10" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H10" s="24">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I10" s="24">
+      <x:c r="I12" s="16">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J10" s="23" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K10" s="25" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="26">
+      <x:c r="L12" s="18">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="22" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H11" s="24">
+      <x:c r="M12" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I11" s="24">
+      <x:c r="I13" s="16">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J11" s="23" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K11" s="25" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="26">
+      <x:c r="L13" s="18">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D12" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E12" s="22" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F12" s="22" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H12" s="24">
+      <x:c r="M13" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I12" s="24">
+      <x:c r="I14" s="16">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J12" s="23" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K12" s="25" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="26">
+      <x:c r="L14" s="18">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M12" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D13" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E13" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G13" s="22" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H13" s="24">
+      <x:c r="M14" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I13" s="24">
+      <x:c r="I15" s="16">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J13" s="23" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K13" s="25" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="26">
+      <x:c r="L15" s="18">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M13" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D14" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E14" s="22" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="M15" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s"/>
+      <x:c r="E21" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G14" s="22" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H14" s="24">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I14" s="27">
+      <x:c r="E22" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J14" s="23" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K14" s="25" t="n">
+      <x:c r="J26" s="15" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="26">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M14" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E15" s="22" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F15" s="22" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G15" s="22" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H15" s="24">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I15" s="27">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J15" s="23" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K15" s="25" t="n">
+      <x:c r="L26" s="18">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="26">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M15" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D16" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F16" s="22" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G16" s="22" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H16" s="24">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I16" s="27">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J16" s="23" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K16" s="25" t="n">
+      <x:c r="L27" s="18">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="26">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M16" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s">
+      <x:c r="L28" s="18">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D17" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="22" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F17" s="22" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G17" s="22" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H17" s="24">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I17" s="27">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J17" s="23" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K17" s="25" t="n">
+      <x:c r="E29" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="26">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M17" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D18" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="22" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F18" s="22" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G18" s="22" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H18" s="24">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I18" s="27">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J18" s="23" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K18" s="25" t="n">
+      <x:c r="L29" s="18">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I30" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="26">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M18" s="22" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="22" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F19" s="22" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G19" s="22" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H19" s="24">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I19" s="24">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J19" s="23" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K19" s="25" t="n">
+      <x:c r="L30" s="18">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I31" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I32" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I33" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I34" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I35" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I36" s="19">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I38" s="19">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L19" s="26">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M19" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D20" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E20" s="22" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H20" s="24">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I20" s="24">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J20" s="23" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K20" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L20" s="26">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M20" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D21" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E21" s="22" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F21" s="22" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G21" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H21" s="24">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I21" s="24">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J21" s="23" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K21" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="26">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M21" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D22" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E22" s="22" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F22" s="22" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G22" s="22" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H22" s="24">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I22" s="24">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J22" s="23" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K22" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="26">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M22" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D23" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E23" s="22" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F23" s="22" t="s">
+      <x:c r="H39" s="16">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I39" s="19">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G23" s="22" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H23" s="24">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I23" s="27">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J23" s="23" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K23" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L23" s="26">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M23" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D24" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E24" s="22" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F24" s="22" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G24" s="22" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H24" s="24">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I24" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J24" s="23" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K24" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="26">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M24" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D25" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E25" s="22" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F25" s="22" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G25" s="22" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H25" s="24">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I25" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="23" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K25" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="26">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M25" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D26" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E26" s="22" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F26" s="22" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G26" s="22" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H26" s="24">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I26" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="23" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K26" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="26">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M26" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C27" s="22" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D27" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E27" s="22" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F27" s="22" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G27" s="22" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H27" s="24">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I27" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="23" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K27" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="26">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M27" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C28" s="22" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D28" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E28" s="22" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F28" s="22" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G28" s="22" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H28" s="24">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I28" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="23" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K28" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="26">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M28" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C29" s="22" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D29" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E29" s="22" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F29" s="22" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G29" s="22" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H29" s="24">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I29" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="23" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K29" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="26">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M29" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C30" s="22" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D30" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E30" s="22" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F30" s="22" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G30" s="22" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H30" s="24">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I30" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="23" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K30" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="26">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M30" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C31" s="22" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D31" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E31" s="22" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F31" s="22" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G31" s="22" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H31" s="24">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I31" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="23" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="26">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M31" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C32" s="22" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D32" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E32" s="22" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F32" s="22" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G32" s="22" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H32" s="24">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I32" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="23" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K32" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="26">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M32" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C33" s="22" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D33" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E33" s="22" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F33" s="22" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G33" s="22" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H33" s="24">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I33" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="23" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K33" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="26">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M33" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C34" s="22" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D34" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E34" s="22" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F34" s="22" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G34" s="22" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H34" s="24">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I34" s="27">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J34" s="23" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K34" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="26">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M34" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C35" s="22" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D35" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E35" s="22" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F35" s="22" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G35" s="22" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H35" s="24">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I35" s="24">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J35" s="23" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K35" s="25" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L35" s="26">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M35" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="22" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C36" s="22" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D36" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E36" s="22" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F36" s="22" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G36" s="22" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H36" s="24">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I36" s="27">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J36" s="23" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K36" s="25" t="n">
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I40" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L36" s="26">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M36" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="22" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C37" s="22" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D37" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E37" s="22" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F37" s="22" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G37" s="22" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H37" s="24">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I37" s="27">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J37" s="23" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K37" s="25" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L37" s="26">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M37" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="22" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C38" s="22" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D38" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E38" s="22" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F38" s="22" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G38" s="22" t="s">
+      <x:c r="L40" s="18">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="H38" s="24">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I38" s="27">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J38" s="23" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K38" s="25" t="n">
+      <x:c r="C41" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I41" s="19">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="26">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M38" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="22" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C39" s="22" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D39" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E39" s="22" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F39" s="22" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G39" s="22" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H39" s="24">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I39" s="27">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J39" s="23" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K39" s="25" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L39" s="26">
+      <x:c r="L41" s="18">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M39" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="22" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C40" s="22" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D40" s="23" t="s"/>
-      <x:c r="E40" s="22" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F40" s="22" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G40" s="22" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H40" s="24">
+      <x:c r="M41" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s"/>
+      <x:c r="E42" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I40" s="24">
+      <x:c r="I42" s="16">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J40" s="23" t="n">
+      <x:c r="J42" s="15" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K40" s="25" t="n">
+      <x:c r="K42" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L40" s="26">
+      <x:c r="L42" s="18">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M40" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="22" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C41" s="22" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D41" s="23" t="s"/>
-      <x:c r="E41" s="22" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F41" s="22" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G41" s="22" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H41" s="24">
+      <x:c r="M42" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s"/>
+      <x:c r="E43" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I41" s="24">
+      <x:c r="I43" s="16">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J41" s="23" t="n">
+      <x:c r="J43" s="15" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K41" s="25" t="n">
+      <x:c r="K43" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L41" s="26">
+      <x:c r="L43" s="18">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M41" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B42" s="28" t="s"/>
-      <x:c r="C42" s="28" t="s"/>
-      <x:c r="D42" s="28" t="s"/>
-      <x:c r="E42" s="28" t="s"/>
-      <x:c r="F42" s="28" t="s"/>
-      <x:c r="G42" s="28" t="s"/>
-      <x:c r="H42" s="28" t="s"/>
-      <x:c r="I42" s="28" t="s"/>
-      <x:c r="J42" s="28" t="s"/>
-      <x:c r="K42" s="28" t="s"/>
-      <x:c r="L42" s="28" t="s"/>
-      <x:c r="M42" s="28" t="s"/>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B43" s="28" t="s"/>
-      <x:c r="C43" s="28" t="s"/>
-      <x:c r="D43" s="28" t="s"/>
-      <x:c r="E43" s="28" t="s"/>
-      <x:c r="F43" s="28" t="s"/>
-      <x:c r="G43" s="28" t="s"/>
-      <x:c r="H43" s="28" t="s"/>
-      <x:c r="I43" s="28" t="s"/>
-      <x:c r="J43" s="28" t="s"/>
-      <x:c r="K43" s="28" t="s"/>
-      <x:c r="L43" s="28" t="s"/>
-      <x:c r="M43" s="28" t="s"/>
+      <x:c r="M43" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="29" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C46" s="30" t="s"/>
-      <x:c r="D46" s="30" t="s"/>
-      <x:c r="E46" s="31" t="s"/>
-      <x:c r="F46" s="31" t="s"/>
+      <x:c r="B46" s="20" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C46" s="21" t="s"/>
+      <x:c r="D46" s="21" t="s"/>
+      <x:c r="E46" s="22" t="s"/>
+      <x:c r="F46" s="22" t="s"/>
     </x:row>
     <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="32" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C47" s="33" t="s"/>
-      <x:c r="D47" s="33" t="s"/>
-      <x:c r="E47" s="33" t="s"/>
-      <x:c r="F47" s="34" t="s">
-        <x:v>158</x:v>
+      <x:c r="B47" s="23" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C47" s="24" t="s"/>
+      <x:c r="D47" s="24" t="s"/>
+      <x:c r="E47" s="24" t="s"/>
+      <x:c r="F47" s="25" t="s">
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="35" t="s">
+      <x:c r="B48" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C48" s="27" t="s"/>
+      <x:c r="D48" s="27" t="s"/>
+      <x:c r="E48" s="27" t="s"/>
+      <x:c r="F48" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C49" s="27" t="s"/>
+      <x:c r="D49" s="27" t="s"/>
+      <x:c r="E49" s="27" t="s"/>
+      <x:c r="F49" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C50" s="27" t="s"/>
+      <x:c r="D50" s="27" t="s"/>
+      <x:c r="E50" s="27" t="s"/>
+      <x:c r="F50" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="26" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C51" s="27" t="s"/>
+      <x:c r="D51" s="27" t="s"/>
+      <x:c r="E51" s="27" t="s"/>
+      <x:c r="F51" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C48" s="36" t="s"/>
-      <x:c r="D48" s="36" t="s"/>
-      <x:c r="E48" s="36" t="s"/>
-      <x:c r="F48" s="37" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C49" s="36" t="s"/>
-      <x:c r="D49" s="36" t="s"/>
-      <x:c r="E49" s="36" t="s"/>
-      <x:c r="F49" s="37" t="n">
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="26" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="s"/>
+      <x:c r="D52" s="27" t="s"/>
+      <x:c r="E52" s="27" t="s"/>
+      <x:c r="F52" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="26" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C53" s="27" t="s"/>
+      <x:c r="D53" s="27" t="s"/>
+      <x:c r="E53" s="27" t="s"/>
+      <x:c r="F53" s="28" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="26" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="s"/>
+      <x:c r="D54" s="27" t="s"/>
+      <x:c r="E54" s="27" t="s"/>
+      <x:c r="F54" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="26" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C55" s="27" t="s"/>
+      <x:c r="D55" s="27" t="s"/>
+      <x:c r="E55" s="27" t="s"/>
+      <x:c r="F55" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="26" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C56" s="27" t="s"/>
+      <x:c r="D56" s="27" t="s"/>
+      <x:c r="E56" s="27" t="s"/>
+      <x:c r="F56" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="35" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C50" s="36" t="s"/>
-      <x:c r="D50" s="36" t="s"/>
-      <x:c r="E50" s="36" t="s"/>
-      <x:c r="F50" s="37" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="35" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C51" s="36" t="s"/>
-      <x:c r="D51" s="36" t="s"/>
-      <x:c r="E51" s="36" t="s"/>
-      <x:c r="F51" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="35" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C52" s="36" t="s"/>
-      <x:c r="D52" s="36" t="s"/>
-      <x:c r="E52" s="36" t="s"/>
-      <x:c r="F52" s="37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="35" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C53" s="36" t="s"/>
-      <x:c r="D53" s="36" t="s"/>
-      <x:c r="E53" s="36" t="s"/>
-      <x:c r="F53" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="35" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C54" s="36" t="s"/>
-      <x:c r="D54" s="36" t="s"/>
-      <x:c r="E54" s="36" t="s"/>
-      <x:c r="F54" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="35" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C55" s="36" t="s"/>
-      <x:c r="D55" s="36" t="s"/>
-      <x:c r="E55" s="36" t="s"/>
-      <x:c r="F55" s="37" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="35" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C56" s="36" t="s"/>
-      <x:c r="D56" s="36" t="s"/>
-      <x:c r="E56" s="36" t="s"/>
-      <x:c r="F56" s="37" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="38" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C57" s="39" t="s"/>
-      <x:c r="D57" s="39" t="s"/>
-      <x:c r="E57" s="39" t="s"/>
-      <x:c r="F57" s="40" t="n">
+      <x:c r="B57" s="29" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C57" s="30" t="s"/>
+      <x:c r="D57" s="30" t="s"/>
+      <x:c r="E57" s="30" t="s"/>
+      <x:c r="F57" s="31" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
@@ -4394,18 +4380,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4423,1650 +4397,1662 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>71</x:v>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46090.2418287037</x:v>
       </x:c>
-      <x:c r="I9" s="20">
+      <x:c r="I11" s="16">
         <x:v>46090.2418518519</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>46093.3049884259</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E10" s="22" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H10" s="24">
+      <x:c r="M11" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46090.2109953704</x:v>
       </x:c>
-      <x:c r="I10" s="24">
+      <x:c r="I12" s="16">
         <x:v>46090.2110069444</x:v>
       </x:c>
-      <x:c r="J10" s="23" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1511204</x:v>
       </x:c>
-      <x:c r="K10" s="25" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="26">
+      <x:c r="L12" s="18">
         <x:v>46093.3080092593</x:v>
       </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H11" s="24">
+      <x:c r="M12" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46083.2380439815</x:v>
       </x:c>
-      <x:c r="I11" s="27">
+      <x:c r="I13" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J11" s="23" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1511234</x:v>
       </x:c>
-      <x:c r="K11" s="25" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="26">
+      <x:c r="L13" s="18">
         <x:v>46097.1564351852</x:v>
       </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D12" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E12" s="22" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="F12" s="22" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H12" s="24">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46083.2322337963</x:v>
       </x:c>
-      <x:c r="I12" s="27">
+      <x:c r="I14" s="19">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J12" s="23" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1511233</x:v>
       </x:c>
-      <x:c r="K12" s="25" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="26">
+      <x:c r="L14" s="18">
         <x:v>46097.149525463</x:v>
       </x:c>
-      <x:c r="M12" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D13" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E13" s="22" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G13" s="22" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H13" s="24">
+      <x:c r="M14" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46080.4532523148</x:v>
       </x:c>
-      <x:c r="I13" s="27">
+      <x:c r="I15" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J13" s="23" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1511232</x:v>
       </x:c>
-      <x:c r="K13" s="25" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="26">
+      <x:c r="L15" s="18">
         <x:v>46097.1461689815</x:v>
       </x:c>
-      <x:c r="M13" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D14" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E14" s="22" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F14" s="22" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G14" s="22" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H14" s="24">
+      <x:c r="M15" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>46083.2599189815</x:v>
       </x:c>
-      <x:c r="I14" s="27">
+      <x:c r="I16" s="19">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J14" s="23" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1511237</x:v>
       </x:c>
-      <x:c r="K14" s="25" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="26">
+      <x:c r="L16" s="18">
         <x:v>46097.1652314815</x:v>
       </x:c>
-      <x:c r="M14" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E15" s="22" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F15" s="22" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G15" s="22" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H15" s="24">
+      <x:c r="M16" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46069.3514814815</x:v>
       </x:c>
-      <x:c r="I15" s="27">
+      <x:c r="I17" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J15" s="23" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1511194</x:v>
       </x:c>
-      <x:c r="K15" s="25" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="26">
+      <x:c r="L17" s="18">
         <x:v>46097.2437384259</x:v>
       </x:c>
-      <x:c r="M15" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D16" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="22" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F16" s="22" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G16" s="22" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H16" s="24">
+      <x:c r="M17" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
         <x:v>46084.0996759259</x:v>
       </x:c>
-      <x:c r="I16" s="27">
+      <x:c r="I18" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J16" s="23" t="n">
+      <x:c r="J18" s="15" t="n">
         <x:v>1511192</x:v>
       </x:c>
-      <x:c r="K16" s="25" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="26">
+      <x:c r="L18" s="18">
         <x:v>46097.2414583333</x:v>
       </x:c>
-      <x:c r="M16" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D17" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="22" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F17" s="22" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G17" s="22" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H17" s="24">
+      <x:c r="M18" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
         <x:v>46084.0854513889</x:v>
       </x:c>
-      <x:c r="I17" s="27">
+      <x:c r="I19" s="19">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J17" s="23" t="n">
+      <x:c r="J19" s="15" t="n">
         <x:v>1511225</x:v>
       </x:c>
-      <x:c r="K17" s="25" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="26">
+      <x:c r="L19" s="18">
         <x:v>46093.3956365741</x:v>
       </x:c>
-      <x:c r="M17" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D18" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="22" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F18" s="22" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G18" s="22" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H18" s="24">
+      <x:c r="M19" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
         <x:v>46069.3573032407</x:v>
       </x:c>
-      <x:c r="I18" s="27">
+      <x:c r="I20" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J18" s="23" t="n">
+      <x:c r="J20" s="15" t="n">
         <x:v>1511193</x:v>
       </x:c>
-      <x:c r="K18" s="25" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="26">
+      <x:c r="L20" s="18">
         <x:v>46097.2426388889</x:v>
       </x:c>
-      <x:c r="M18" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D19" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E19" s="22" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F19" s="22" t="s">
+      <x:c r="M20" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I30" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I31" s="19">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I32" s="19">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I33" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I34" s="19">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I35" s="19">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I40" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L40" s="18">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="G19" s="22" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H19" s="24">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I19" s="27">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J19" s="23" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K19" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="26">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M19" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D20" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E20" s="22" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H20" s="24">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I20" s="27">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J20" s="23" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K20" s="25" t="n">
+      <x:c r="D41" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I41" s="19">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="26">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M20" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D21" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E21" s="22" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F21" s="22" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G21" s="22" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H21" s="24">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I21" s="27">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J21" s="23" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K21" s="25" t="n">
+      <x:c r="L41" s="18">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I42" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="26">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M21" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="D22" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E22" s="22" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F22" s="22" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G22" s="22" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H22" s="24">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I22" s="27">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J22" s="23" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K22" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L22" s="26">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M22" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D23" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E23" s="22" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="F23" s="22" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G23" s="22" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H23" s="24">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I23" s="27">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J23" s="23" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K23" s="25" t="n">
+      <x:c r="L42" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I43" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J43" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="26">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M23" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="D24" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E24" s="22" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F24" s="22" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G24" s="22" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H24" s="24">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I24" s="27">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J24" s="23" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K24" s="25" t="n">
+      <x:c r="L43" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D44" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H44" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I44" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J44" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K44" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="26">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M24" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D25" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E25" s="22" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F25" s="22" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G25" s="22" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H25" s="24">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I25" s="27">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="23" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K25" s="25" t="n">
+      <x:c r="L44" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D45" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="H45" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I45" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J45" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K45" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="26">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M25" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D26" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E26" s="22" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F26" s="22" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G26" s="22" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H26" s="24">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I26" s="27">
+      <x:c r="L45" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D46" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="H46" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I46" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J26" s="23" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K26" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="26">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M26" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C27" s="22" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D27" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E27" s="22" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F27" s="22" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="G27" s="22" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H27" s="24">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I27" s="27">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J27" s="23" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K27" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="26">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M27" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C28" s="22" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D28" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E28" s="22" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F28" s="22" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G28" s="22" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H28" s="24">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I28" s="27">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J28" s="23" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K28" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="26">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M28" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C29" s="22" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D29" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E29" s="22" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F29" s="22" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G29" s="22" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H29" s="24">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I29" s="27">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J29" s="23" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K29" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L29" s="26">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M29" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C30" s="22" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D30" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E30" s="22" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F30" s="22" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G30" s="22" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H30" s="24">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I30" s="27">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J30" s="23" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K30" s="25" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L30" s="26">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M30" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C31" s="22" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D31" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E31" s="22" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="F31" s="22" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="G31" s="22" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="H31" s="24">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I31" s="27">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J31" s="23" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K31" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="26">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M31" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C32" s="22" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="D32" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E32" s="22" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F32" s="22" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G32" s="22" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H32" s="24">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I32" s="27">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J32" s="23" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K32" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="26">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M32" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C33" s="22" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D33" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E33" s="22" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F33" s="22" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G33" s="22" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H33" s="24">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I33" s="27">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J33" s="23" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K33" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="26">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M33" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C34" s="22" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="D34" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E34" s="22" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="F34" s="22" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="G34" s="22" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="H34" s="24">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I34" s="24">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J34" s="23" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K34" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L34" s="26">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M34" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C35" s="22" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="D35" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E35" s="22" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F35" s="22" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G35" s="22" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H35" s="24">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I35" s="24">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J35" s="23" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K35" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L35" s="26">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M35" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C36" s="22" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="D36" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E36" s="22" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F36" s="22" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G36" s="22" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H36" s="24">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I36" s="24">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J36" s="23" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K36" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L36" s="26">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M36" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C37" s="22" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="D37" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E37" s="22" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="F37" s="22" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="G37" s="22" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H37" s="24">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I37" s="24">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J37" s="23" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K37" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="26">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M37" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C38" s="22" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="D38" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E38" s="22" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F38" s="22" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G38" s="22" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="H38" s="24">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I38" s="27">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J38" s="23" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K38" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="26">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M38" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C39" s="22" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D39" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E39" s="22" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="F39" s="22" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="G39" s="22" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="H39" s="24">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I39" s="27">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J39" s="23" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K39" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L39" s="26">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M39" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C40" s="22" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="D40" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E40" s="22" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="F40" s="22" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="G40" s="22" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="H40" s="24">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I40" s="27">
+      <x:c r="J46" s="15" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K46" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L46" s="18">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M46" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="D47" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="H47" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I47" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J40" s="23" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K40" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L40" s="26">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M40" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C41" s="22" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D41" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E41" s="22" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F41" s="22" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G41" s="22" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H41" s="24">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I41" s="27">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J41" s="23" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K41" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="26">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M41" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C42" s="22" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D42" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E42" s="22" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="F42" s="22" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="G42" s="22" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="H42" s="24">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I42" s="27">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J42" s="23" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K42" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="26">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M42" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C43" s="22" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D43" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E43" s="22" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="F43" s="22" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="G43" s="22" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="H43" s="24">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I43" s="27">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J43" s="23" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K43" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="26">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M43" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="22" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C44" s="22" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="D44" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E44" s="22" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="F44" s="22" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="G44" s="22" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H44" s="24">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I44" s="27">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J44" s="23" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K44" s="25" t="n">
+      <x:c r="J47" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K47" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L44" s="26">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M44" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="22" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C45" s="22" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="D45" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E45" s="22" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="F45" s="22" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="G45" s="22" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="H45" s="24">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I45" s="27">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J45" s="23" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K45" s="25" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L45" s="26">
+      <x:c r="L47" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M45" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B46" s="28" t="s"/>
-      <x:c r="C46" s="28" t="s"/>
-      <x:c r="D46" s="28" t="s"/>
-      <x:c r="E46" s="28" t="s"/>
-      <x:c r="F46" s="28" t="s"/>
-      <x:c r="G46" s="28" t="s"/>
-      <x:c r="H46" s="28" t="s"/>
-      <x:c r="I46" s="28" t="s"/>
-      <x:c r="J46" s="28" t="s"/>
-      <x:c r="K46" s="28" t="s"/>
-      <x:c r="L46" s="28" t="s"/>
-      <x:c r="M46" s="28" t="s"/>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B47" s="28" t="s"/>
-      <x:c r="C47" s="28" t="s"/>
-      <x:c r="D47" s="28" t="s"/>
-      <x:c r="E47" s="28" t="s"/>
-      <x:c r="F47" s="28" t="s"/>
-      <x:c r="G47" s="28" t="s"/>
-      <x:c r="H47" s="28" t="s"/>
-      <x:c r="I47" s="28" t="s"/>
-      <x:c r="J47" s="28" t="s"/>
-      <x:c r="K47" s="28" t="s"/>
-      <x:c r="L47" s="28" t="s"/>
-      <x:c r="M47" s="28" t="s"/>
+      <x:c r="M47" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="29" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C50" s="30" t="s"/>
-      <x:c r="D50" s="30" t="s"/>
-      <x:c r="E50" s="31" t="s"/>
-      <x:c r="F50" s="31" t="s"/>
+      <x:c r="B50" s="20" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C50" s="21" t="s"/>
+      <x:c r="D50" s="21" t="s"/>
+      <x:c r="E50" s="22" t="s"/>
+      <x:c r="F50" s="22" t="s"/>
     </x:row>
     <x:row r="51" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B51" s="32" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C51" s="33" t="s"/>
-      <x:c r="D51" s="33" t="s"/>
-      <x:c r="E51" s="33" t="s"/>
-      <x:c r="F51" s="34" t="s">
-        <x:v>158</x:v>
+      <x:c r="B51" s="23" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C51" s="24" t="s"/>
+      <x:c r="D51" s="24" t="s"/>
+      <x:c r="E51" s="24" t="s"/>
+      <x:c r="F51" s="25" t="s">
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="35" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C52" s="36" t="s"/>
-      <x:c r="D52" s="36" t="s"/>
-      <x:c r="E52" s="36" t="s"/>
-      <x:c r="F52" s="37" t="n">
+      <x:c r="B52" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="s"/>
+      <x:c r="D52" s="27" t="s"/>
+      <x:c r="E52" s="27" t="s"/>
+      <x:c r="F52" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C53" s="36" t="s"/>
-      <x:c r="D53" s="36" t="s"/>
-      <x:c r="E53" s="36" t="s"/>
-      <x:c r="F53" s="37" t="n">
+      <x:c r="B53" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C53" s="27" t="s"/>
+      <x:c r="D53" s="27" t="s"/>
+      <x:c r="E53" s="27" t="s"/>
+      <x:c r="F53" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="35" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C54" s="36" t="s"/>
-      <x:c r="D54" s="36" t="s"/>
-      <x:c r="E54" s="36" t="s"/>
-      <x:c r="F54" s="37" t="n">
+      <x:c r="B54" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="s"/>
+      <x:c r="D54" s="27" t="s"/>
+      <x:c r="E54" s="27" t="s"/>
+      <x:c r="F54" s="28" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="35" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C55" s="36" t="s"/>
-      <x:c r="D55" s="36" t="s"/>
-      <x:c r="E55" s="36" t="s"/>
-      <x:c r="F55" s="37" t="n">
+      <x:c r="B55" s="26" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C55" s="27" t="s"/>
+      <x:c r="D55" s="27" t="s"/>
+      <x:c r="E55" s="27" t="s"/>
+      <x:c r="F55" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="35" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C56" s="36" t="s"/>
-      <x:c r="D56" s="36" t="s"/>
-      <x:c r="E56" s="36" t="s"/>
-      <x:c r="F56" s="37" t="n">
+      <x:c r="B56" s="26" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C56" s="27" t="s"/>
+      <x:c r="D56" s="27" t="s"/>
+      <x:c r="E56" s="27" t="s"/>
+      <x:c r="F56" s="28" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="35" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C57" s="36" t="s"/>
-      <x:c r="D57" s="36" t="s"/>
-      <x:c r="E57" s="36" t="s"/>
-      <x:c r="F57" s="37" t="n">
+      <x:c r="B57" s="26" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C57" s="27" t="s"/>
+      <x:c r="D57" s="27" t="s"/>
+      <x:c r="E57" s="27" t="s"/>
+      <x:c r="F57" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B58" s="38" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C58" s="39" t="s"/>
-      <x:c r="D58" s="39" t="s"/>
-      <x:c r="E58" s="39" t="s"/>
-      <x:c r="F58" s="40" t="n">
+      <x:c r="B58" s="29" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C58" s="30" t="s"/>
+      <x:c r="D58" s="30" t="s"/>
+      <x:c r="E58" s="30" t="s"/>
+      <x:c r="F58" s="31" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="319">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -565,6 +565,18 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>RUBEN C. SESCON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blk. 17, Lot 14, Phase 2 Aquino Street, Citihomes, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIV-A-07321-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1203-366</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
@@ -604,6 +616,24 @@
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0781 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1144-933</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -613,24 +643,6 @@
     <x:t>43A-3-2026-1151-716</x:t>
   </x:si>
   <x:si>
-    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1150-325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0781 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1144-933</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -658,6 +670,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -667,18 +688,27 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0762</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1155-834</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -695,24 +725,6 @@
   </x:si>
   <x:si>
     <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
     <x:t>CLIXTEC INC.</x:t>
@@ -1288,9 +1300,12 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1360,7 +1375,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1390,6 +1405,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1724,7 +1743,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46054</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1796,1524 +1817,1524 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46069.0835185185</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46069.1006712963</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1506161</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46069.1133333333</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>46066.3145023148</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1507747</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46066.3194212963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="H10" s="17">
         <x:v>46069.0835648148</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="17">
         <x:v>46069.1000231481</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1506159</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>46069.1128587963</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="C11" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="H11" s="17">
         <x:v>46072.1720833333</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="17">
         <x:v>46072.235162037</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1507783</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>46073.1890277778</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="M11" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="C12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="H12" s="17">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I12" s="16">
+      <x:c r="I12" s="17">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
+      <x:c r="M12" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="B13" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="C13" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="H13" s="17">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I13" s="16">
+      <x:c r="I13" s="17">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
+      <x:c r="M13" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
+      <x:c r="B14" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="C14" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
+      <x:c r="D14" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="E14" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="F14" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="H14" s="17">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I14" s="16">
+      <x:c r="I14" s="17">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="19">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
+      <x:c r="M14" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
+      <x:c r="B15" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="C15" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
+      <x:c r="D15" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="E15" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="F15" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="G15" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="H15" s="17">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I15" s="16">
+      <x:c r="I15" s="17">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L15" s="19">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
+      <x:c r="M15" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
+      <x:c r="B16" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="C16" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
+      <x:c r="D16" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="E16" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="F16" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="G16" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="H16" s="17">
         <x:v>46067.1596643518</x:v>
       </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="I16" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="16" t="n">
         <x:v>1505804</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
+      <x:c r="L16" s="19">
         <x:v>46079.2772569444</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
+      <x:c r="M16" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
+      <x:c r="B17" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="C17" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
+      <x:c r="D17" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="E17" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="F17" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="G17" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H17" s="16">
+      <x:c r="H17" s="17">
         <x:v>46067.2222106481</x:v>
       </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="I17" s="20">
         <x:v>46089</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
+      <x:c r="J17" s="16" t="n">
         <x:v>1505805</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="K17" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
+      <x:c r="L17" s="19">
         <x:v>46079.2763078704</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
+      <x:c r="M17" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
+      <x:c r="B18" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="C18" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
+      <x:c r="D18" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="E18" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="F18" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="G18" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H18" s="16">
+      <x:c r="H18" s="17">
         <x:v>46072.3605555556</x:v>
       </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="I18" s="20">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
+      <x:c r="J18" s="16" t="n">
         <x:v>1507784</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K18" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L18" s="19">
         <x:v>46073.2284953704</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
+      <x:c r="M18" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
+      <x:c r="B19" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C19" s="14" t="s">
+      <x:c r="C19" s="15" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
+      <x:c r="D19" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="E19" s="15" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="F19" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="G19" s="15" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H19" s="16">
+      <x:c r="H19" s="17">
         <x:v>46072.3529513889</x:v>
       </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="I19" s="20">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
+      <x:c r="J19" s="16" t="n">
         <x:v>1507785</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="K19" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="18">
+      <x:c r="L19" s="19">
         <x:v>46073.2314351852</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="s">
+      <x:c r="M19" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
+      <x:c r="B20" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C20" s="14" t="s">
+      <x:c r="C20" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="s">
+      <x:c r="D20" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E20" s="14" t="s">
+      <x:c r="E20" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="F20" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="G20" s="15" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="H20" s="16">
+      <x:c r="H20" s="17">
         <x:v>46063.1352777778</x:v>
       </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="I20" s="20">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="n">
+      <x:c r="J20" s="16" t="n">
         <x:v>1511010</x:v>
       </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="K20" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="18">
+      <x:c r="L20" s="19">
         <x:v>46063.2367708333</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="s">
+      <x:c r="M20" s="15" t="s">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
+      <x:c r="B21" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C21" s="14" t="s">
+      <x:c r="C21" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s"/>
-      <x:c r="E21" s="14" t="s">
+      <x:c r="D21" s="16" t="s"/>
+      <x:c r="E21" s="15" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="F21" s="15" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="G21" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H21" s="16">
+      <x:c r="H21" s="17">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="I21" s="16">
+      <x:c r="I21" s="17">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
+      <x:c r="J21" s="16" t="n">
         <x:v>1507791</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="K21" s="18" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L21" s="18">
+      <x:c r="L21" s="19">
         <x:v>46073.3142476852</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="s">
+      <x:c r="M21" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
+      <x:c r="B22" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="s">
+      <x:c r="C22" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="s">
+      <x:c r="D22" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="s">
+      <x:c r="E22" s="15" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="F22" s="15" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="G22" s="15" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H22" s="16">
+      <x:c r="H22" s="17">
         <x:v>46079.3584722222</x:v>
       </x:c>
-      <x:c r="I22" s="16">
+      <x:c r="I22" s="17">
         <x:v>46079.3584953704</x:v>
       </x:c>
-      <x:c r="J22" s="15" t="n">
+      <x:c r="J22" s="16" t="n">
         <x:v>1511622</x:v>
       </x:c>
-      <x:c r="K22" s="17" t="n">
+      <x:c r="K22" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L22" s="18">
+      <x:c r="L22" s="19">
         <x:v>46080.2311226852</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="s">
+      <x:c r="M22" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
+      <x:c r="B23" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C23" s="14" t="s">
+      <x:c r="C23" s="15" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="s">
+      <x:c r="D23" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E23" s="14" t="s">
+      <x:c r="E23" s="15" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="s">
+      <x:c r="F23" s="15" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="s">
+      <x:c r="G23" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="H23" s="16">
+      <x:c r="H23" s="17">
         <x:v>46079.3539699074</x:v>
       </x:c>
-      <x:c r="I23" s="16">
+      <x:c r="I23" s="17">
         <x:v>46079.3539814815</x:v>
       </x:c>
-      <x:c r="J23" s="15" t="n">
+      <x:c r="J23" s="16" t="n">
         <x:v>1511627</x:v>
       </x:c>
-      <x:c r="K23" s="17" t="n">
+      <x:c r="K23" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L23" s="18">
+      <x:c r="L23" s="19">
         <x:v>46080.2440856481</x:v>
       </x:c>
-      <x:c r="M23" s="14" t="s">
+      <x:c r="M23" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
+      <x:c r="B24" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C24" s="14" t="s">
+      <x:c r="C24" s="15" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="s">
+      <x:c r="D24" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E24" s="14" t="s">
+      <x:c r="E24" s="15" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="s">
+      <x:c r="F24" s="15" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="s">
+      <x:c r="G24" s="15" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H24" s="16">
+      <x:c r="H24" s="17">
         <x:v>46058.1529282407</x:v>
       </x:c>
-      <x:c r="I24" s="16">
+      <x:c r="I24" s="17">
         <x:v>46058.1529398148</x:v>
       </x:c>
-      <x:c r="J24" s="15" t="n">
+      <x:c r="J24" s="16" t="n">
         <x:v>1507657</x:v>
       </x:c>
-      <x:c r="K24" s="17" t="n">
+      <x:c r="K24" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L24" s="18">
+      <x:c r="L24" s="19">
         <x:v>46058.2410648148</x:v>
       </x:c>
-      <x:c r="M24" s="14" t="s">
+      <x:c r="M24" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
+      <x:c r="B25" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C25" s="14" t="s">
+      <x:c r="C25" s="15" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="s">
+      <x:c r="D25" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E25" s="14" t="s">
+      <x:c r="E25" s="15" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="s">
+      <x:c r="F25" s="15" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G25" s="14" t="s">
+      <x:c r="G25" s="15" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="H25" s="16">
+      <x:c r="H25" s="17">
         <x:v>46072.2635300926</x:v>
       </x:c>
-      <x:c r="I25" s="19">
+      <x:c r="I25" s="20">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J25" s="15" t="n">
+      <x:c r="J25" s="16" t="n">
         <x:v>1507790</x:v>
       </x:c>
-      <x:c r="K25" s="17" t="n">
+      <x:c r="K25" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L25" s="18">
+      <x:c r="L25" s="19">
         <x:v>46073.3091087963</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
+      <x:c r="M25" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
+      <x:c r="B26" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C26" s="14" t="s">
+      <x:c r="C26" s="15" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="s">
+      <x:c r="D26" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E26" s="14" t="s">
+      <x:c r="E26" s="15" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="F26" s="15" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="G26" s="15" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H26" s="16">
+      <x:c r="H26" s="17">
         <x:v>46079.3873148148</x:v>
       </x:c>
-      <x:c r="I26" s="19">
+      <x:c r="I26" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J26" s="15" t="n">
+      <x:c r="J26" s="16" t="n">
         <x:v>1511623</x:v>
       </x:c>
-      <x:c r="K26" s="17" t="n">
+      <x:c r="K26" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L26" s="18">
+      <x:c r="L26" s="19">
         <x:v>46080.2360763889</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="s">
+      <x:c r="M26" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
+      <x:c r="B27" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C27" s="14" t="s">
+      <x:c r="C27" s="15" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="s">
+      <x:c r="D27" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E27" s="14" t="s">
+      <x:c r="E27" s="15" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="s">
+      <x:c r="F27" s="15" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="s">
+      <x:c r="G27" s="15" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H27" s="16">
+      <x:c r="H27" s="17">
         <x:v>46079.2523032407</x:v>
       </x:c>
-      <x:c r="I27" s="19">
+      <x:c r="I27" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J27" s="15" t="n">
+      <x:c r="J27" s="16" t="n">
         <x:v>1511631</x:v>
       </x:c>
-      <x:c r="K27" s="17" t="n">
+      <x:c r="K27" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L27" s="18">
+      <x:c r="L27" s="19">
         <x:v>46080.2925810185</x:v>
       </x:c>
-      <x:c r="M27" s="14" t="s">
+      <x:c r="M27" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
+      <x:c r="B28" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C28" s="14" t="s">
+      <x:c r="C28" s="15" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D28" s="15" t="s">
+      <x:c r="D28" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E28" s="14" t="s">
+      <x:c r="E28" s="15" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F28" s="14" t="s">
+      <x:c r="F28" s="15" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G28" s="14" t="s">
+      <x:c r="G28" s="15" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H28" s="16">
+      <x:c r="H28" s="17">
         <x:v>46079.2430555556</x:v>
       </x:c>
-      <x:c r="I28" s="19">
+      <x:c r="I28" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J28" s="15" t="n">
+      <x:c r="J28" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K28" s="17" t="n">
+      <x:c r="K28" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="18">
+      <x:c r="L28" s="19">
         <x:v>46080.2801273148</x:v>
       </x:c>
-      <x:c r="M28" s="14" t="s">
+      <x:c r="M28" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
+      <x:c r="B29" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C29" s="14" t="s">
+      <x:c r="C29" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="D29" s="15" t="s">
+      <x:c r="D29" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E29" s="14" t="s">
+      <x:c r="E29" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="s">
+      <x:c r="F29" s="15" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G29" s="14" t="s">
+      <x:c r="G29" s="15" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H29" s="16">
+      <x:c r="H29" s="17">
         <x:v>46079.3651967593</x:v>
       </x:c>
-      <x:c r="I29" s="19">
+      <x:c r="I29" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J29" s="15" t="n">
+      <x:c r="J29" s="16" t="n">
         <x:v>1511626</x:v>
       </x:c>
-      <x:c r="K29" s="17" t="n">
+      <x:c r="K29" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="18">
+      <x:c r="L29" s="19">
         <x:v>46080.2425462963</x:v>
       </x:c>
-      <x:c r="M29" s="14" t="s">
+      <x:c r="M29" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
+      <x:c r="B30" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C30" s="14" t="s">
+      <x:c r="C30" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="s">
+      <x:c r="D30" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E30" s="14" t="s">
+      <x:c r="E30" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="F30" s="14" t="s">
+      <x:c r="F30" s="15" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="G30" s="14" t="s">
+      <x:c r="G30" s="15" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="H30" s="16">
+      <x:c r="H30" s="17">
         <x:v>46080.2923611111</x:v>
       </x:c>
-      <x:c r="I30" s="19">
+      <x:c r="I30" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J30" s="15" t="n">
+      <x:c r="J30" s="16" t="n">
         <x:v>1511635</x:v>
       </x:c>
-      <x:c r="K30" s="17" t="n">
+      <x:c r="K30" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L30" s="18">
+      <x:c r="L30" s="19">
         <x:v>46080.3208564815</x:v>
       </x:c>
-      <x:c r="M30" s="14" t="s">
+      <x:c r="M30" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
+      <x:c r="B31" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C31" s="14" t="s">
+      <x:c r="C31" s="15" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="s">
+      <x:c r="D31" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E31" s="14" t="s">
+      <x:c r="E31" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="s">
+      <x:c r="F31" s="15" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G31" s="14" t="s">
+      <x:c r="G31" s="15" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="H31" s="16">
+      <x:c r="H31" s="17">
         <x:v>46079.31625</x:v>
       </x:c>
-      <x:c r="I31" s="19">
+      <x:c r="I31" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J31" s="15" t="n">
+      <x:c r="J31" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K31" s="17" t="n">
+      <x:c r="K31" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L31" s="18">
+      <x:c r="L31" s="19">
         <x:v>46080.2883680556</x:v>
       </x:c>
-      <x:c r="M31" s="14" t="s">
+      <x:c r="M31" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
+      <x:c r="B32" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C32" s="14" t="s">
+      <x:c r="C32" s="15" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="s">
+      <x:c r="D32" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E32" s="14" t="s">
+      <x:c r="E32" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="F32" s="14" t="s">
+      <x:c r="F32" s="15" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G32" s="14" t="s">
+      <x:c r="G32" s="15" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H32" s="16">
+      <x:c r="H32" s="17">
         <x:v>46079.3059375</x:v>
       </x:c>
-      <x:c r="I32" s="19">
+      <x:c r="I32" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J32" s="15" t="n">
+      <x:c r="J32" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K32" s="17" t="n">
+      <x:c r="K32" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L32" s="18">
+      <x:c r="L32" s="19">
         <x:v>46080.2896875</x:v>
       </x:c>
-      <x:c r="M32" s="14" t="s">
+      <x:c r="M32" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
+      <x:c r="B33" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C33" s="14" t="s">
+      <x:c r="C33" s="15" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D33" s="15" t="s">
+      <x:c r="D33" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E33" s="14" t="s">
+      <x:c r="E33" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="F33" s="14" t="s">
+      <x:c r="F33" s="15" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G33" s="14" t="s">
+      <x:c r="G33" s="15" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H33" s="16">
+      <x:c r="H33" s="17">
         <x:v>46079.2943981482</x:v>
       </x:c>
-      <x:c r="I33" s="19">
+      <x:c r="I33" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J33" s="15" t="n">
+      <x:c r="J33" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K33" s="17" t="n">
+      <x:c r="K33" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L33" s="18">
+      <x:c r="L33" s="19">
         <x:v>46080.2916782407</x:v>
       </x:c>
-      <x:c r="M33" s="14" t="s">
+      <x:c r="M33" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
+      <x:c r="B34" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C34" s="14" t="s">
+      <x:c r="C34" s="15" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D34" s="15" t="s">
+      <x:c r="D34" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E34" s="14" t="s">
+      <x:c r="E34" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F34" s="14" t="s">
+      <x:c r="F34" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G34" s="14" t="s">
+      <x:c r="G34" s="15" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H34" s="16">
+      <x:c r="H34" s="17">
         <x:v>46079.378900463</x:v>
       </x:c>
-      <x:c r="I34" s="19">
+      <x:c r="I34" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J34" s="15" t="n">
+      <x:c r="J34" s="16" t="n">
         <x:v>1511624</x:v>
       </x:c>
-      <x:c r="K34" s="17" t="n">
+      <x:c r="K34" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L34" s="18">
+      <x:c r="L34" s="19">
         <x:v>46080.2376041667</x:v>
       </x:c>
-      <x:c r="M34" s="14" t="s">
+      <x:c r="M34" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
+      <x:c r="B35" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C35" s="14" t="s">
+      <x:c r="C35" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="s">
+      <x:c r="D35" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E35" s="14" t="s">
+      <x:c r="E35" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F35" s="14" t="s">
+      <x:c r="F35" s="15" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G35" s="14" t="s">
+      <x:c r="G35" s="15" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H35" s="16">
+      <x:c r="H35" s="17">
         <x:v>46079.3728240741</x:v>
       </x:c>
-      <x:c r="I35" s="19">
+      <x:c r="I35" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J35" s="15" t="n">
+      <x:c r="J35" s="16" t="n">
         <x:v>1511625</x:v>
       </x:c>
-      <x:c r="K35" s="17" t="n">
+      <x:c r="K35" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L35" s="18">
+      <x:c r="L35" s="19">
         <x:v>46080.2394328704</x:v>
       </x:c>
-      <x:c r="M35" s="14" t="s">
+      <x:c r="M35" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
+      <x:c r="B36" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C36" s="14" t="s">
+      <x:c r="C36" s="15" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="s">
+      <x:c r="D36" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E36" s="14" t="s">
+      <x:c r="E36" s="15" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F36" s="14" t="s">
+      <x:c r="F36" s="15" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G36" s="14" t="s">
+      <x:c r="G36" s="15" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H36" s="16">
+      <x:c r="H36" s="17">
         <x:v>46077.0697337963</x:v>
       </x:c>
-      <x:c r="I36" s="19">
+      <x:c r="I36" s="20">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J36" s="15" t="n">
+      <x:c r="J36" s="16" t="n">
         <x:v>1511576</x:v>
       </x:c>
-      <x:c r="K36" s="17" t="n">
+      <x:c r="K36" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L36" s="18">
+      <x:c r="L36" s="19">
         <x:v>46077.1078819444</x:v>
       </x:c>
-      <x:c r="M36" s="14" t="s">
+      <x:c r="M36" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
+      <x:c r="B37" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C37" s="14" t="s">
+      <x:c r="C37" s="15" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="s">
+      <x:c r="D37" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E37" s="14" t="s">
+      <x:c r="E37" s="15" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F37" s="14" t="s">
+      <x:c r="F37" s="15" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G37" s="14" t="s">
+      <x:c r="G37" s="15" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H37" s="16">
+      <x:c r="H37" s="17">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I37" s="16">
+      <x:c r="I37" s="17">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J37" s="15" t="n">
+      <x:c r="J37" s="16" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K37" s="17" t="n">
+      <x:c r="K37" s="18" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L37" s="18">
+      <x:c r="L37" s="19">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M37" s="14" t="s">
+      <x:c r="M37" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
+      <x:c r="B38" s="15" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C38" s="14" t="s">
+      <x:c r="C38" s="15" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="s">
+      <x:c r="D38" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E38" s="14" t="s">
+      <x:c r="E38" s="15" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="F38" s="14" t="s">
+      <x:c r="F38" s="15" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G38" s="14" t="s">
+      <x:c r="G38" s="15" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H38" s="16">
+      <x:c r="H38" s="17">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I38" s="19">
+      <x:c r="I38" s="20">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J38" s="15" t="n">
+      <x:c r="J38" s="16" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K38" s="17" t="n">
+      <x:c r="K38" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="18">
+      <x:c r="L38" s="19">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M38" s="14" t="s">
+      <x:c r="M38" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
+      <x:c r="B39" s="15" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C39" s="14" t="s">
+      <x:c r="C39" s="15" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="s">
+      <x:c r="D39" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E39" s="14" t="s">
+      <x:c r="E39" s="15" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F39" s="14" t="s">
+      <x:c r="F39" s="15" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G39" s="14" t="s">
+      <x:c r="G39" s="15" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H39" s="16">
+      <x:c r="H39" s="17">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I39" s="19">
+      <x:c r="I39" s="20">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J39" s="15" t="n">
+      <x:c r="J39" s="16" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K39" s="17" t="n">
+      <x:c r="K39" s="18" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L39" s="18">
+      <x:c r="L39" s="19">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M39" s="14" t="s">
+      <x:c r="M39" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
+      <x:c r="B40" s="15" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C40" s="14" t="s">
+      <x:c r="C40" s="15" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D40" s="15" t="s">
+      <x:c r="D40" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E40" s="14" t="s">
+      <x:c r="E40" s="15" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F40" s="14" t="s">
+      <x:c r="F40" s="15" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G40" s="14" t="s">
+      <x:c r="G40" s="15" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H40" s="16">
+      <x:c r="H40" s="17">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I40" s="19">
+      <x:c r="I40" s="20">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J40" s="15" t="n">
+      <x:c r="J40" s="16" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K40" s="17" t="n">
+      <x:c r="K40" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L40" s="18">
+      <x:c r="L40" s="19">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M40" s="14" t="s">
+      <x:c r="M40" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="14" t="s">
+      <x:c r="B41" s="15" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C41" s="14" t="s">
+      <x:c r="C41" s="15" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D41" s="15" t="s">
+      <x:c r="D41" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E41" s="14" t="s">
+      <x:c r="E41" s="15" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F41" s="14" t="s">
+      <x:c r="F41" s="15" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G41" s="14" t="s">
+      <x:c r="G41" s="15" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H41" s="16">
+      <x:c r="H41" s="17">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I41" s="19">
+      <x:c r="I41" s="20">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J41" s="15" t="n">
+      <x:c r="J41" s="16" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K41" s="17" t="n">
+      <x:c r="K41" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L41" s="18">
+      <x:c r="L41" s="19">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M41" s="14" t="s">
+      <x:c r="M41" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="14" t="s">
+      <x:c r="B42" s="15" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C42" s="14" t="s">
+      <x:c r="C42" s="15" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D42" s="15" t="s"/>
-      <x:c r="E42" s="14" t="s">
+      <x:c r="D42" s="16" t="s"/>
+      <x:c r="E42" s="15" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F42" s="14" t="s">
+      <x:c r="F42" s="15" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G42" s="14" t="s">
+      <x:c r="G42" s="15" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H42" s="16">
+      <x:c r="H42" s="17">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I42" s="16">
+      <x:c r="I42" s="17">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J42" s="15" t="n">
+      <x:c r="J42" s="16" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K42" s="17" t="n">
+      <x:c r="K42" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L42" s="18">
+      <x:c r="L42" s="19">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M42" s="14" t="s">
+      <x:c r="M42" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="14" t="s">
+      <x:c r="B43" s="15" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C43" s="14" t="s">
+      <x:c r="C43" s="15" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D43" s="15" t="s"/>
-      <x:c r="E43" s="14" t="s">
+      <x:c r="D43" s="16" t="s"/>
+      <x:c r="E43" s="15" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F43" s="14" t="s">
+      <x:c r="F43" s="15" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G43" s="14" t="s">
+      <x:c r="G43" s="15" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="H43" s="16">
+      <x:c r="H43" s="17">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I43" s="16">
+      <x:c r="I43" s="17">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J43" s="15" t="n">
+      <x:c r="J43" s="16" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K43" s="17" t="n">
+      <x:c r="K43" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L43" s="18">
+      <x:c r="L43" s="19">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M43" s="14" t="s">
+      <x:c r="M43" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="20" t="s">
+      <x:c r="B46" s="21" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C46" s="21" t="s"/>
-      <x:c r="D46" s="21" t="s"/>
-      <x:c r="E46" s="22" t="s"/>
-      <x:c r="F46" s="22" t="s"/>
+      <x:c r="C46" s="22" t="s"/>
+      <x:c r="D46" s="22" t="s"/>
+      <x:c r="E46" s="23" t="s"/>
+      <x:c r="F46" s="23" t="s"/>
     </x:row>
     <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="23" t="s">
+      <x:c r="B47" s="24" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C47" s="24" t="s"/>
-      <x:c r="D47" s="24" t="s"/>
-      <x:c r="E47" s="24" t="s"/>
-      <x:c r="F47" s="25" t="s">
+      <x:c r="C47" s="25" t="s"/>
+      <x:c r="D47" s="25" t="s"/>
+      <x:c r="E47" s="25" t="s"/>
+      <x:c r="F47" s="26" t="s">
         <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="26" t="s">
+      <x:c r="B48" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C48" s="27" t="s"/>
-      <x:c r="D48" s="27" t="s"/>
-      <x:c r="E48" s="27" t="s"/>
-      <x:c r="F48" s="28" t="n">
+      <x:c r="C48" s="28" t="s"/>
+      <x:c r="D48" s="28" t="s"/>
+      <x:c r="E48" s="28" t="s"/>
+      <x:c r="F48" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
+      <x:c r="B49" s="27" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
+      <x:c r="C49" s="28" t="s"/>
+      <x:c r="D49" s="28" t="s"/>
+      <x:c r="E49" s="28" t="s"/>
+      <x:c r="F49" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
+      <x:c r="B50" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
+      <x:c r="C50" s="28" t="s"/>
+      <x:c r="D50" s="28" t="s"/>
+      <x:c r="E50" s="28" t="s"/>
+      <x:c r="F50" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="26" t="s">
+      <x:c r="B51" s="27" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C51" s="27" t="s"/>
-      <x:c r="D51" s="27" t="s"/>
-      <x:c r="E51" s="27" t="s"/>
-      <x:c r="F51" s="28" t="n">
+      <x:c r="C51" s="28" t="s"/>
+      <x:c r="D51" s="28" t="s"/>
+      <x:c r="E51" s="28" t="s"/>
+      <x:c r="F51" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
+      <x:c r="B52" s="27" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
+      <x:c r="C52" s="28" t="s"/>
+      <x:c r="D52" s="28" t="s"/>
+      <x:c r="E52" s="28" t="s"/>
+      <x:c r="F52" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="26" t="s">
+      <x:c r="B53" s="27" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C53" s="27" t="s"/>
-      <x:c r="D53" s="27" t="s"/>
-      <x:c r="E53" s="27" t="s"/>
-      <x:c r="F53" s="28" t="n">
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="26" t="s">
+      <x:c r="B54" s="27" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C54" s="27" t="s"/>
-      <x:c r="D54" s="27" t="s"/>
-      <x:c r="E54" s="27" t="s"/>
-      <x:c r="F54" s="28" t="n">
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="26" t="s">
+      <x:c r="B55" s="27" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C55" s="27" t="s"/>
-      <x:c r="D55" s="27" t="s"/>
-      <x:c r="E55" s="27" t="s"/>
-      <x:c r="F55" s="28" t="n">
+      <x:c r="C55" s="28" t="s"/>
+      <x:c r="D55" s="28" t="s"/>
+      <x:c r="E55" s="28" t="s"/>
+      <x:c r="F55" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="26" t="s">
+      <x:c r="B56" s="27" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C56" s="27" t="s"/>
-      <x:c r="D56" s="27" t="s"/>
-      <x:c r="E56" s="27" t="s"/>
-      <x:c r="F56" s="28" t="n">
+      <x:c r="C56" s="28" t="s"/>
+      <x:c r="D56" s="28" t="s"/>
+      <x:c r="E56" s="28" t="s"/>
+      <x:c r="F56" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="29" t="s">
+      <x:c r="B57" s="30" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C57" s="30" t="s"/>
-      <x:c r="D57" s="30" t="s"/>
-      <x:c r="E57" s="30" t="s"/>
-      <x:c r="F57" s="31" t="n">
+      <x:c r="C57" s="31" t="s"/>
+      <x:c r="D57" s="31" t="s"/>
+      <x:c r="E57" s="31" t="s"/>
+      <x:c r="F57" s="32" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
@@ -4330,7 +4351,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -4402,1661 +4425,1696 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46091.306099537</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46091.3107986111</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1511778</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46091.3131828704</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46093.1459375</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>46093.1585185185</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1511815</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46093.159537037</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46098.0792592593</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46098.0878935185</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1529776</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46098.0997569444</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="C11" s="15" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="E11" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I11" s="17">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L11" s="19">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
+      <x:c r="M11" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>184</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="D12" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
+      <x:c r="C13" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="E13" s="15" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="L13" s="19">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I14" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I15" s="20">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I16" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I17" s="20">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I18" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I19" s="20">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I20" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I21" s="20">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="20">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I23" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I24" s="20">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I25" s="20">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I26" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I27" s="20">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I28" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="H29" s="17">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I29" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="19">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H30" s="17">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I30" s="20">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="19">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H31" s="17">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I31" s="20">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="19">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M31" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H32" s="17">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I32" s="20">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K32" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L32" s="19">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H33" s="17">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I33" s="20">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L33" s="19">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H34" s="17">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I34" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K34" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="19">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H35" s="17">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I35" s="20">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K35" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="19">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M35" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="H36" s="17">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I36" s="20">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K36" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="19">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M36" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H37" s="17">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I37" s="17">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K37" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="19">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M37" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H38" s="17">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I38" s="17">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K38" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="19">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M38" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="H39" s="17">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I39" s="17">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K39" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="19">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M39" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H40" s="17">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I40" s="17">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K40" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="19">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M40" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H41" s="17">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I41" s="20">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K41" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="19">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M41" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G42" s="15" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H42" s="17">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I42" s="20">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J42" s="16" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K42" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="19">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M42" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E43" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F43" s="15" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G43" s="15" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="H43" s="17">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I43" s="20">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J43" s="16" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K43" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="19">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M43" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E44" s="15" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F44" s="15" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G44" s="15" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="H44" s="17">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I44" s="20">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K44" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="19">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M44" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C45" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E45" s="15" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="F45" s="15" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G45" s="15" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="H45" s="17">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I45" s="20">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J45" s="16" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K45" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="19">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M45" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C46" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E46" s="15" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F46" s="15" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G46" s="15" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="H46" s="17">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I46" s="20">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J46" s="16" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K46" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="19">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M46" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C47" s="15" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E47" s="15" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F47" s="15" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="G47" s="15" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="H47" s="17">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I47" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J47" s="16" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K47" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L47" s="19">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M47" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C48" s="15" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E48" s="15" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F48" s="15" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="G48" s="15" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="H48" s="17">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I48" s="20">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J48" s="16" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K48" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L48" s="19">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M48" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="21" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C51" s="22" t="s"/>
+      <x:c r="D51" s="22" t="s"/>
+      <x:c r="E51" s="23" t="s"/>
+      <x:c r="F51" s="23" t="s"/>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B52" s="24" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C52" s="25" t="s"/>
+      <x:c r="D52" s="25" t="s"/>
+      <x:c r="E52" s="25" t="s"/>
+      <x:c r="F52" s="26" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="27" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I31" s="19">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I32" s="19">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I33" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I34" s="19">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I35" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
+      <x:c r="C55" s="28" t="s"/>
+      <x:c r="D55" s="28" t="s"/>
+      <x:c r="E55" s="28" t="s"/>
+      <x:c r="F55" s="29" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="27" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I36" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I37" s="16">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I38" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
+      <x:c r="C56" s="28" t="s"/>
+      <x:c r="D56" s="28" t="s"/>
+      <x:c r="E56" s="28" t="s"/>
+      <x:c r="F56" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="27" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E40" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I40" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K40" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L40" s="18">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D41" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E41" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="G41" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I41" s="19">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K41" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="18">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M41" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C42" s="14" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="D42" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E42" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="G42" s="14" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="H42" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I42" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J42" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K42" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M42" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C43" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D43" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E43" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="F43" s="14" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="G43" s="14" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="H43" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I43" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J43" s="15" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K43" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="18">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M43" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C44" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D44" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E44" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="F44" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="G44" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="H44" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I44" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J44" s="15" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K44" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="18">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M44" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C45" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D45" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E45" s="14" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F45" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G45" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="H45" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I45" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J45" s="15" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K45" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="18">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M45" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="14" t="s">
+      <x:c r="C57" s="28" t="s"/>
+      <x:c r="D57" s="28" t="s"/>
+      <x:c r="E57" s="28" t="s"/>
+      <x:c r="F57" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="27" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C46" s="14" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D46" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E46" s="14" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="F46" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="G46" s="14" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="H46" s="16">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I46" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J46" s="15" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K46" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L46" s="18">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M46" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C47" s="14" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="D47" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E47" s="14" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="F47" s="14" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="G47" s="14" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="H47" s="16">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I47" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J47" s="15" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K47" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L47" s="18">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M47" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="20" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C50" s="21" t="s"/>
-      <x:c r="D50" s="21" t="s"/>
-      <x:c r="E50" s="22" t="s"/>
-      <x:c r="F50" s="22" t="s"/>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B51" s="23" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C51" s="24" t="s"/>
-      <x:c r="D51" s="24" t="s"/>
-      <x:c r="E51" s="24" t="s"/>
-      <x:c r="F51" s="25" t="s">
-        <x:v>170</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
+      <x:c r="C58" s="28" t="s"/>
+      <x:c r="D58" s="28" t="s"/>
+      <x:c r="E58" s="28" t="s"/>
+      <x:c r="F58" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C53" s="27" t="s"/>
-      <x:c r="D53" s="27" t="s"/>
-      <x:c r="E53" s="27" t="s"/>
-      <x:c r="F53" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C54" s="27" t="s"/>
-      <x:c r="D54" s="27" t="s"/>
-      <x:c r="E54" s="27" t="s"/>
-      <x:c r="F54" s="28" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="26" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C55" s="27" t="s"/>
-      <x:c r="D55" s="27" t="s"/>
-      <x:c r="E55" s="27" t="s"/>
-      <x:c r="F55" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="26" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C56" s="27" t="s"/>
-      <x:c r="D56" s="27" t="s"/>
-      <x:c r="E56" s="27" t="s"/>
-      <x:c r="F56" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="26" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C57" s="27" t="s"/>
-      <x:c r="D57" s="27" t="s"/>
-      <x:c r="E57" s="27" t="s"/>
-      <x:c r="F57" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B58" s="29" t="s">
+    <x:row r="59" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B59" s="30" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C58" s="30" t="s"/>
-      <x:c r="D58" s="30" t="s"/>
-      <x:c r="E58" s="30" t="s"/>
-      <x:c r="F58" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C59" s="31" t="s"/>
+      <x:c r="D59" s="31" t="s"/>
+      <x:c r="E59" s="31" t="s"/>
+      <x:c r="F59" s="32" t="n">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6996,8 +7054,7 @@
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
     <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B50:F50"/>
-    <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B51:F51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
@@ -7005,6 +7062,7 @@
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
+    <x:mergeCell ref="B59:E59"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,11 +23,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="319">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
+    <x:t>IV-A | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -539,6 +542,9 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>HERALD BEBIS</x:t>
@@ -989,7 +995,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1029,6 +1035,22 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1300,12 +1322,15 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1323,59 +1348,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1406,95 +1431,99 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1723,40 +1752,40 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
@@ -1817,1524 +1846,1524 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="C7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="G8" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
         <x:v>46069.0835185185</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46069.1006712963</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="13" t="n">
         <x:v>1506161</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="14">
         <x:v>46069.1133333333</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="13" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
+      <x:c r="B9" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="14">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="14">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="s"/>
+      <x:c r="E10" s="16" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="18">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I9" s="13">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="n">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="16" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="18">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="L11" s="20">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M11" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H12" s="18">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="L12" s="20">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M12" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="s"/>
+      <x:c r="E13" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H13" s="18">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="L13" s="20">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M13" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H14" s="18">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M14" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H15" s="18">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M15" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H16" s="18">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I16" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M16" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H17" s="18">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I17" s="21">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M17" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H18" s="18">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I18" s="21">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M18" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H19" s="18">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I19" s="21">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M19" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H20" s="18">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I20" s="21">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M20" s="16" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="16" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="s"/>
+      <x:c r="E21" s="16" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H21" s="18">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M21" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H22" s="18">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I22" s="18">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="20">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M22" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H23" s="18">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I23" s="18">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K23" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="20">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M23" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H24" s="18">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I24" s="18">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K24" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="20">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M24" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C25" s="16" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E25" s="16" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F25" s="16" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G25" s="16" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H25" s="18">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I25" s="21">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J25" s="17" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K25" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="20">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M25" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E26" s="16" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F26" s="16" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G26" s="16" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H26" s="18">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I26" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K26" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="20">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M26" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E27" s="16" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G27" s="16" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H27" s="18">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I27" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K27" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="20">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M27" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E28" s="16" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F28" s="16" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H28" s="18">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I28" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K28" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="20">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M28" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C29" s="16" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E29" s="16" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F29" s="16" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H29" s="18">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I29" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="17" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K29" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="20">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M29" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C30" s="16" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E30" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F30" s="16" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G30" s="16" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H30" s="18">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I30" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="17" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K30" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="20">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M30" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C31" s="16" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E31" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F31" s="16" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G31" s="16" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H31" s="18">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I31" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K31" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="20">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M31" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C32" s="16" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E32" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F32" s="16" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H32" s="18">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I32" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K32" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="20">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M32" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C33" s="16" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E33" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F33" s="16" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G33" s="16" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H33" s="18">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I33" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K33" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="20">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M33" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C34" s="16" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E34" s="16" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F34" s="16" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G34" s="16" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="H34" s="18">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I34" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="17" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K34" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="20">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M34" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C35" s="16" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E35" s="16" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F35" s="16" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H35" s="18">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I35" s="21">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J35" s="17" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K35" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="20">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M35" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C36" s="16" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E36" s="16" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F36" s="16" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G36" s="16" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H36" s="18">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I36" s="21">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J36" s="17" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K36" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="20">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M36" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="16" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C37" s="16" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E37" s="16" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F37" s="16" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G37" s="16" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H37" s="18">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I37" s="18">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J37" s="17" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K37" s="19" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L37" s="20">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M37" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C38" s="16" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I16" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I17" s="20">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I18" s="20">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I19" s="20">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I20" s="20">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s"/>
-      <x:c r="E21" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="E38" s="16" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F38" s="16" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G38" s="16" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H38" s="18">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I38" s="21">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J38" s="17" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K38" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L38" s="20">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M38" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C39" s="16" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E39" s="16" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F39" s="16" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="G39" s="16" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H39" s="18">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I39" s="21">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J39" s="17" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K39" s="19" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L39" s="20">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M39" s="16" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I25" s="20">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I26" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I27" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I28" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I29" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D30" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G30" s="15" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H30" s="17">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I30" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="16" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="19">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M30" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C31" s="15" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D31" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F31" s="15" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G31" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H31" s="17">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I31" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="19">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M31" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C32" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D32" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F32" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G32" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H32" s="17">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I32" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K32" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="19">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M32" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C33" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D33" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G33" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H33" s="17">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I33" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K33" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="19">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M33" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C34" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D34" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E34" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G34" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H34" s="17">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I34" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="16" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K34" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="19">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M34" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C35" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D35" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E35" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F35" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G35" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H35" s="17">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I35" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K35" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="19">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M35" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C36" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D36" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E36" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F36" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G36" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H36" s="17">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I36" s="20">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J36" s="16" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K36" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="19">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M36" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C37" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D37" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E37" s="15" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F37" s="15" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H37" s="17">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I37" s="17">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K37" s="18" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L37" s="19">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M37" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C38" s="15" t="s">
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="16" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D38" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E38" s="15" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F38" s="15" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G38" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H38" s="17">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I38" s="20">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J38" s="16" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K38" s="18" t="n">
+      <x:c r="C40" s="16" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E40" s="16" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F40" s="16" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G40" s="16" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H40" s="18">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I40" s="21">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J40" s="17" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K40" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="19">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M38" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C39" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E39" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F39" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G39" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H39" s="17">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I39" s="20">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J39" s="16" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K39" s="18" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L39" s="19">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M39" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C40" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D40" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E40" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F40" s="15" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G40" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H40" s="17">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I40" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J40" s="16" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K40" s="18" t="n">
+      <x:c r="L40" s="20">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M40" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C41" s="16" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E41" s="16" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F41" s="16" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H41" s="18">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I41" s="21">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J41" s="17" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K41" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L40" s="19">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M40" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C41" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D41" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E41" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F41" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G41" s="15" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H41" s="17">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I41" s="20">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J41" s="16" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K41" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L41" s="19">
+      <x:c r="L41" s="20">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M41" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M41" s="16" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C42" s="15" t="s">
+      <x:c r="B42" s="16" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D42" s="16" t="s"/>
-      <x:c r="E42" s="15" t="s">
+      <x:c r="C42" s="16" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="s">
+      <x:c r="D42" s="17" t="s"/>
+      <x:c r="E42" s="16" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G42" s="15" t="s">
+      <x:c r="F42" s="16" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H42" s="17">
+      <x:c r="G42" s="16" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H42" s="18">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I42" s="17">
+      <x:c r="I42" s="18">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J42" s="16" t="n">
+      <x:c r="J42" s="17" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K42" s="18" t="n">
+      <x:c r="K42" s="19" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L42" s="19">
+      <x:c r="L42" s="20">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M42" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M42" s="16" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C43" s="15" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D43" s="16" t="s"/>
-      <x:c r="E43" s="15" t="s">
+      <x:c r="B43" s="16" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C43" s="16" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F43" s="15" t="s">
+      <x:c r="D43" s="17" t="s"/>
+      <x:c r="E43" s="16" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G43" s="15" t="s">
+      <x:c r="F43" s="16" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="H43" s="17">
+      <x:c r="G43" s="16" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H43" s="18">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I43" s="17">
+      <x:c r="I43" s="18">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J43" s="16" t="n">
+      <x:c r="J43" s="17" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K43" s="18" t="n">
+      <x:c r="K43" s="19" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L43" s="19">
+      <x:c r="L43" s="20">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M43" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M43" s="16" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="21" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C46" s="22" t="s"/>
-      <x:c r="D46" s="22" t="s"/>
-      <x:c r="E46" s="23" t="s"/>
-      <x:c r="F46" s="23" t="s"/>
+      <x:c r="B46" s="22" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C46" s="23" t="s"/>
+      <x:c r="D46" s="23" t="s"/>
+      <x:c r="E46" s="24" t="s"/>
+      <x:c r="F46" s="24" t="s"/>
     </x:row>
     <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="24" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C47" s="25" t="s"/>
-      <x:c r="D47" s="25" t="s"/>
-      <x:c r="E47" s="25" t="s"/>
-      <x:c r="F47" s="26" t="s">
+      <x:c r="B47" s="25" t="s">
         <x:v>170</x:v>
       </x:c>
+      <x:c r="C47" s="26" t="s"/>
+      <x:c r="D47" s="26" t="s"/>
+      <x:c r="E47" s="26" t="s"/>
+      <x:c r="F47" s="27" t="s">
+        <x:v>171</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C48" s="28" t="s"/>
-      <x:c r="D48" s="28" t="s"/>
-      <x:c r="E48" s="28" t="s"/>
-      <x:c r="F48" s="29" t="n">
+      <x:c r="B48" s="28" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C48" s="29" t="s"/>
+      <x:c r="D48" s="29" t="s"/>
+      <x:c r="E48" s="29" t="s"/>
+      <x:c r="F48" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C49" s="28" t="s"/>
-      <x:c r="D49" s="28" t="s"/>
-      <x:c r="E49" s="28" t="s"/>
-      <x:c r="F49" s="29" t="n">
+      <x:c r="B49" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C49" s="29" t="s"/>
+      <x:c r="D49" s="29" t="s"/>
+      <x:c r="E49" s="29" t="s"/>
+      <x:c r="F49" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C50" s="28" t="s"/>
-      <x:c r="D50" s="28" t="s"/>
-      <x:c r="E50" s="28" t="s"/>
-      <x:c r="F50" s="29" t="n">
+      <x:c r="B50" s="28" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C50" s="29" t="s"/>
+      <x:c r="D50" s="29" t="s"/>
+      <x:c r="E50" s="29" t="s"/>
+      <x:c r="F50" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="27" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C51" s="28" t="s"/>
-      <x:c r="D51" s="28" t="s"/>
-      <x:c r="E51" s="28" t="s"/>
-      <x:c r="F51" s="29" t="n">
+      <x:c r="B51" s="28" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C51" s="29" t="s"/>
+      <x:c r="D51" s="29" t="s"/>
+      <x:c r="E51" s="29" t="s"/>
+      <x:c r="F51" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="27" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C52" s="28" t="s"/>
-      <x:c r="D52" s="28" t="s"/>
-      <x:c r="E52" s="28" t="s"/>
-      <x:c r="F52" s="29" t="n">
+      <x:c r="B52" s="28" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C52" s="29" t="s"/>
+      <x:c r="D52" s="29" t="s"/>
+      <x:c r="E52" s="29" t="s"/>
+      <x:c r="F52" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="27" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
+      <x:c r="B53" s="28" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C53" s="29" t="s"/>
+      <x:c r="D53" s="29" t="s"/>
+      <x:c r="E53" s="29" t="s"/>
+      <x:c r="F53" s="30" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="27" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
+      <x:c r="B54" s="28" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C54" s="29" t="s"/>
+      <x:c r="D54" s="29" t="s"/>
+      <x:c r="E54" s="29" t="s"/>
+      <x:c r="F54" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="27" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C55" s="28" t="s"/>
-      <x:c r="D55" s="28" t="s"/>
-      <x:c r="E55" s="28" t="s"/>
-      <x:c r="F55" s="29" t="n">
+      <x:c r="B55" s="28" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C55" s="29" t="s"/>
+      <x:c r="D55" s="29" t="s"/>
+      <x:c r="E55" s="29" t="s"/>
+      <x:c r="F55" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="27" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C56" s="28" t="s"/>
-      <x:c r="D56" s="28" t="s"/>
-      <x:c r="E56" s="28" t="s"/>
-      <x:c r="F56" s="29" t="n">
+      <x:c r="B56" s="28" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C56" s="29" t="s"/>
+      <x:c r="D56" s="29" t="s"/>
+      <x:c r="E56" s="29" t="s"/>
+      <x:c r="F56" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="30" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C57" s="31" t="s"/>
-      <x:c r="D57" s="31" t="s"/>
-      <x:c r="E57" s="31" t="s"/>
-      <x:c r="F57" s="32" t="n">
+      <x:c r="B57" s="31" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C57" s="32" t="s"/>
+      <x:c r="D57" s="32" t="s"/>
+      <x:c r="E57" s="32" t="s"/>
+      <x:c r="F57" s="33" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
@@ -4331,40 +4360,40 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
@@ -4425,1693 +4454,1693 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="C7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="B8" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="13" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
         <x:v>46091.306099537</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46091.3107986111</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="13" t="n">
         <x:v>1511778</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="14">
         <x:v>46091.3131828704</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>83</x:v>
+      <x:c r="M8" s="13" t="s">
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
+      <x:c r="B9" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="s">
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="F9" s="13" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H9" s="14">
         <x:v>46093.1459375</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46093.1585185185</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="13" t="n">
         <x:v>1511815</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="14">
         <x:v>46093.159537037</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>83</x:v>
+      <x:c r="M9" s="13" t="s">
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="D10" s="17" t="s"/>
+      <x:c r="E10" s="16" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="F10" s="16" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H10" s="18">
         <x:v>46098.0792592593</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="18">
         <x:v>46098.0878935185</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1529776</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="20">
         <x:v>46098.0997569444</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M10" s="16" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="D11" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="F11" s="16" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H11" s="18">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="18">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="20">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>188</x:v>
+      <x:c r="M11" s="16" t="s">
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H12" s="18">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M12" s="16" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H13" s="18">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="L13" s="20">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M13" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H14" s="18">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I14" s="21">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M14" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H15" s="18">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I15" s="21">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M15" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H16" s="18">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I16" s="21">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M16" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H17" s="18">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I17" s="21">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M17" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H18" s="18">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I18" s="21">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M18" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H19" s="18">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I19" s="21">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M19" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H20" s="18">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I20" s="21">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M20" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H21" s="18">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I21" s="21">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M21" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H22" s="18">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="21">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="20">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H23" s="18">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I23" s="21">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K23" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="20">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M23" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H24" s="18">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I24" s="21">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K24" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="20">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M24" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C25" s="16" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E25" s="16" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F25" s="16" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G25" s="16" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H25" s="18">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I25" s="21">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J25" s="17" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K25" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="20">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M25" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E26" s="16" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F26" s="16" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G26" s="16" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H26" s="18">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I26" s="21">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K26" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="20">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M26" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E27" s="16" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G27" s="16" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H27" s="18">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I27" s="21">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K27" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="20">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M27" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E28" s="16" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F28" s="16" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H28" s="18">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I28" s="21">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="17" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K28" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="20">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M28" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C29" s="16" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E29" s="16" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F29" s="16" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H29" s="18">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I29" s="21">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J29" s="17" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K29" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="20">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M29" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C30" s="16" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E30" s="16" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F30" s="16" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G30" s="16" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H30" s="18">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I30" s="21">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J30" s="17" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K30" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="20">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M30" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C31" s="16" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E31" s="16" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="F31" s="16" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G31" s="16" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H31" s="18">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I31" s="21">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J31" s="17" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K31" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="20">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M31" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C32" s="16" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E32" s="16" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F32" s="16" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H32" s="18">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I32" s="21">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J32" s="17" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K32" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L32" s="20">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M32" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C33" s="16" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E33" s="16" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F33" s="16" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G33" s="16" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H33" s="18">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I33" s="21">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J33" s="17" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K33" s="19" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L33" s="20">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M33" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C34" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E34" s="16" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F34" s="16" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G34" s="16" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H34" s="18">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I34" s="21">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J34" s="17" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K34" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="20">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M34" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C35" s="16" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E35" s="16" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F35" s="16" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H35" s="18">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I35" s="21">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J35" s="17" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K35" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="20">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M35" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C36" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E36" s="16" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F36" s="16" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G36" s="16" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H36" s="18">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I36" s="21">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J36" s="17" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K36" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="20">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M36" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C37" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E37" s="16" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F37" s="16" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G37" s="16" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H37" s="18">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I37" s="18">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J37" s="17" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K37" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I14" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="L37" s="20">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M37" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C38" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E38" s="16" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F38" s="16" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G38" s="16" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="H38" s="18">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I38" s="18">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J38" s="17" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K38" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="20">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M38" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C39" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E39" s="16" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F39" s="16" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G39" s="16" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H39" s="18">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I39" s="18">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J39" s="17" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K39" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="20">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M39" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C40" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E40" s="16" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F40" s="16" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G40" s="16" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H40" s="18">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I40" s="18">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J40" s="17" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K40" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="20">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M40" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C41" s="16" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E41" s="16" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="F41" s="16" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="H41" s="18">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I41" s="21">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J41" s="17" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K41" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I15" s="20">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="L41" s="20">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M41" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C42" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E42" s="16" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F42" s="16" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H42" s="18">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I42" s="21">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J42" s="17" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K42" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I16" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="L42" s="20">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M42" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C43" s="16" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E43" s="16" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F43" s="16" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H43" s="18">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I43" s="21">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J43" s="17" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K43" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I17" s="20">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="L43" s="20">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M43" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C44" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D44" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E44" s="16" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F44" s="16" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="H44" s="18">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I44" s="21">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J44" s="17" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K44" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I18" s="20">
+      <x:c r="L44" s="20">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M44" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C45" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D45" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F45" s="16" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="G45" s="16" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H45" s="18">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I45" s="21">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J45" s="17" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K45" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="20">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M45" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C46" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D46" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E46" s="16" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="F46" s="16" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="H46" s="18">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I46" s="21">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J46" s="17" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K46" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="20">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M46" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C47" s="16" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D47" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E47" s="16" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F47" s="16" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="H47" s="18">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I47" s="21">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I19" s="20">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I20" s="20">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I21" s="20">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I22" s="20">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I23" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I24" s="20">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I25" s="20">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I26" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I27" s="20">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I28" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I29" s="20">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="D30" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="G30" s="15" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="H30" s="17">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I30" s="20">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J30" s="16" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="19">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M30" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C31" s="15" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D31" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="F31" s="15" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="G31" s="15" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="H31" s="17">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I31" s="20">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J31" s="16" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K31" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="19">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M31" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C32" s="15" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D32" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="15" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="F32" s="15" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="G32" s="15" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="H32" s="17">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I32" s="20">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J32" s="16" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K32" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L32" s="19">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M32" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C33" s="15" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D33" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="15" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="G33" s="15" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H33" s="17">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I33" s="20">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J33" s="16" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K33" s="18" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L33" s="19">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M33" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C34" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D34" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E34" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="G34" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="H34" s="17">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I34" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J34" s="16" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K34" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="19">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M34" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C35" s="15" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D35" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E35" s="15" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F35" s="15" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G35" s="15" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H35" s="17">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I35" s="20">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K35" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="19">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M35" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C36" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D36" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E36" s="15" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="F36" s="15" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="G36" s="15" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="H36" s="17">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I36" s="20">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J36" s="16" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K36" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="19">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M36" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C37" s="15" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D37" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E37" s="15" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="F37" s="15" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="H37" s="17">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I37" s="17">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K37" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="19">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M37" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C38" s="15" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D38" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E38" s="15" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="F38" s="15" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="G38" s="15" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="H38" s="17">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I38" s="17">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J38" s="16" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K38" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L38" s="19">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M38" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C39" s="15" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E39" s="15" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F39" s="15" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G39" s="15" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H39" s="17">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I39" s="17">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J39" s="16" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K39" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="19">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M39" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C40" s="15" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D40" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E40" s="15" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="F40" s="15" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G40" s="15" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H40" s="17">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I40" s="17">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J40" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K40" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L40" s="19">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M40" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C41" s="15" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="D41" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E41" s="15" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="F41" s="15" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="G41" s="15" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="H41" s="17">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I41" s="20">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J41" s="16" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K41" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="19">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M41" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C42" s="15" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D42" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E42" s="15" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="F42" s="15" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="G42" s="15" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="H42" s="17">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I42" s="20">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J42" s="16" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K42" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="19">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M42" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C43" s="15" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="D43" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E43" s="15" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="F43" s="15" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="G43" s="15" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="H43" s="17">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I43" s="20">
+      <x:c r="J47" s="17" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K47" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L47" s="20">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M47" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C48" s="16" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="D48" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E48" s="16" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F48" s="16" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="G48" s="16" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H48" s="18">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I48" s="21">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J43" s="16" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K43" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="19">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M43" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C44" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D44" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E44" s="15" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="F44" s="15" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="G44" s="15" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="H44" s="17">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I44" s="20">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J44" s="16" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K44" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="19">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M44" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C45" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D45" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E45" s="15" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="F45" s="15" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="G45" s="15" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="H45" s="17">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I45" s="20">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J45" s="16" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K45" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="19">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M45" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C46" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D46" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E46" s="15" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="F46" s="15" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="G46" s="15" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="H46" s="17">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I46" s="20">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J46" s="16" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K46" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L46" s="19">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M46" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C47" s="15" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="D47" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E47" s="15" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="F47" s="15" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="G47" s="15" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="H47" s="17">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I47" s="20">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J47" s="16" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K47" s="18" t="n">
+      <x:c r="J48" s="17" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K48" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L47" s="19">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M47" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C48" s="15" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="D48" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E48" s="15" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="F48" s="15" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="G48" s="15" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="H48" s="17">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I48" s="20">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J48" s="16" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K48" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L48" s="19">
+      <x:c r="L48" s="20">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M48" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M48" s="16" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="21" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C51" s="22" t="s"/>
-      <x:c r="D51" s="22" t="s"/>
-      <x:c r="E51" s="23" t="s"/>
-      <x:c r="F51" s="23" t="s"/>
+      <x:c r="B51" s="22" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C51" s="23" t="s"/>
+      <x:c r="D51" s="23" t="s"/>
+      <x:c r="E51" s="24" t="s"/>
+      <x:c r="F51" s="24" t="s"/>
     </x:row>
     <x:row r="52" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B52" s="24" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C52" s="25" t="s"/>
-      <x:c r="D52" s="25" t="s"/>
-      <x:c r="E52" s="25" t="s"/>
-      <x:c r="F52" s="26" t="s">
+      <x:c r="B52" s="25" t="s">
         <x:v>170</x:v>
       </x:c>
+      <x:c r="C52" s="26" t="s"/>
+      <x:c r="D52" s="26" t="s"/>
+      <x:c r="E52" s="26" t="s"/>
+      <x:c r="F52" s="27" t="s">
+        <x:v>171</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
+      <x:c r="B53" s="28" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C53" s="29" t="s"/>
+      <x:c r="D53" s="29" t="s"/>
+      <x:c r="E53" s="29" t="s"/>
+      <x:c r="F53" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
+      <x:c r="B54" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C54" s="29" t="s"/>
+      <x:c r="D54" s="29" t="s"/>
+      <x:c r="E54" s="29" t="s"/>
+      <x:c r="F54" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C55" s="28" t="s"/>
-      <x:c r="D55" s="28" t="s"/>
-      <x:c r="E55" s="28" t="s"/>
-      <x:c r="F55" s="29" t="n">
+      <x:c r="B55" s="28" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C55" s="29" t="s"/>
+      <x:c r="D55" s="29" t="s"/>
+      <x:c r="E55" s="29" t="s"/>
+      <x:c r="F55" s="30" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="27" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C56" s="28" t="s"/>
-      <x:c r="D56" s="28" t="s"/>
-      <x:c r="E56" s="28" t="s"/>
-      <x:c r="F56" s="29" t="n">
+      <x:c r="B56" s="28" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C56" s="29" t="s"/>
+      <x:c r="D56" s="29" t="s"/>
+      <x:c r="E56" s="29" t="s"/>
+      <x:c r="F56" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="27" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C57" s="28" t="s"/>
-      <x:c r="D57" s="28" t="s"/>
-      <x:c r="E57" s="28" t="s"/>
-      <x:c r="F57" s="29" t="n">
+      <x:c r="B57" s="28" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C57" s="29" t="s"/>
+      <x:c r="D57" s="29" t="s"/>
+      <x:c r="E57" s="29" t="s"/>
+      <x:c r="F57" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="27" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C58" s="28" t="s"/>
-      <x:c r="D58" s="28" t="s"/>
-      <x:c r="E58" s="28" t="s"/>
-      <x:c r="F58" s="29" t="n">
+      <x:c r="B58" s="28" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C58" s="29" t="s"/>
+      <x:c r="D58" s="29" t="s"/>
+      <x:c r="E58" s="29" t="s"/>
+      <x:c r="F58" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B59" s="30" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C59" s="31" t="s"/>
-      <x:c r="D59" s="31" t="s"/>
-      <x:c r="E59" s="31" t="s"/>
-      <x:c r="F59" s="32" t="n">
+      <x:c r="B59" s="31" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C59" s="32" t="s"/>
+      <x:c r="D59" s="32" t="s"/>
+      <x:c r="E59" s="32" t="s"/>
+      <x:c r="F59" s="33" t="n">
         <x:v>41</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -65,6 +65,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -992,10 +1028,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1040,27 +1078,12 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
@@ -1327,13 +1350,13 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1348,59 +1371,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1431,99 +1454,87 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1752,74 +1763,72 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -1844,7 +1853,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1884,1491 +1893,1541 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s"/>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="G8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="13" t="s"/>
+      <x:c r="C9" s="13" t="s"/>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s"/>
+      <x:c r="F9" s="13" t="s"/>
+      <x:c r="G9" s="13" t="s"/>
+      <x:c r="H9" s="13" t="s"/>
+      <x:c r="I9" s="13" t="s"/>
+      <x:c r="J9" s="13" t="s"/>
+      <x:c r="K9" s="13" t="s"/>
+      <x:c r="L9" s="13" t="s"/>
+      <x:c r="M9" s="13" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46069.0835185185</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I10" s="16">
         <x:v>46069.1006712963</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1506161</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L10" s="18">
         <x:v>46069.1133333333</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="13" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F9" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="14">
+      <x:c r="M10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I11" s="16">
         <x:v>46066.3145023148</x:v>
       </x:c>
-      <x:c r="J9" s="13" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1507747</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="14">
+      <x:c r="L11" s="18">
         <x:v>46066.3194212963</x:v>
       </x:c>
-      <x:c r="M9" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s"/>
-      <x:c r="E10" s="16" t="s">
+      <x:c r="M11" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
+      <x:c r="C12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46069.0835648148</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I12" s="16">
         <x:v>46069.1000231481</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1506159</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L12" s="18">
         <x:v>46069.1128587963</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="16" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46072.1720833333</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I13" s="16">
         <x:v>46072.235162037</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1507783</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L13" s="18">
         <x:v>46073.1890277778</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="16" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H12" s="18">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I14" s="16">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L14" s="18">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
+      <x:c r="M14" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I15" s="16">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J13" s="17" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L15" s="18">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
+      <x:c r="M15" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="I16" s="16">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J14" s="17" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="20">
+      <x:c r="L16" s="18">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
+      <x:c r="M16" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I15" s="18">
+      <x:c r="I17" s="16">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J15" s="17" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="20">
+      <x:c r="L17" s="18">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s">
+      <x:c r="M17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s"/>
+      <x:c r="E23" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I31" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I32" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I34" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I35" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I40" s="16">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L40" s="18">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I41" s="16">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L41" s="18">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I42" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L42" s="18">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I43" s="16">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J43" s="15" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L43" s="18">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D44" s="15" t="s"/>
+      <x:c r="E44" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H44" s="16">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I44" s="16">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J44" s="15" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K44" s="17" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L44" s="18">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D45" s="15" t="s"/>
+      <x:c r="E45" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H45" s="16">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I45" s="16">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J45" s="15" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K45" s="17" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L45" s="18">
+        <x:v>46080.3345717593</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B48" s="19" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C48" s="20" t="s"/>
+      <x:c r="D48" s="20" t="s"/>
+      <x:c r="E48" s="21" t="s"/>
+      <x:c r="F48" s="21" t="s"/>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B49" s="22" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C49" s="23" t="s"/>
+      <x:c r="D49" s="23" t="s"/>
+      <x:c r="E49" s="23" t="s"/>
+      <x:c r="F49" s="24" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C50" s="26" t="s"/>
+      <x:c r="D50" s="26" t="s"/>
+      <x:c r="E50" s="26" t="s"/>
+      <x:c r="F50" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="25" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I16" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E17" s="16" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I17" s="21">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
+      <x:c r="C51" s="26" t="s"/>
+      <x:c r="D51" s="26" t="s"/>
+      <x:c r="E51" s="26" t="s"/>
+      <x:c r="F51" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="25" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I18" s="21">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I19" s="21">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="20">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I20" s="21">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s"/>
-      <x:c r="E21" s="16" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I21" s="18">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
+      <x:c r="C52" s="26" t="s"/>
+      <x:c r="D52" s="26" t="s"/>
+      <x:c r="E52" s="26" t="s"/>
+      <x:c r="F52" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="25" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C53" s="26" t="s"/>
+      <x:c r="D53" s="26" t="s"/>
+      <x:c r="E53" s="26" t="s"/>
+      <x:c r="F53" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="25" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C54" s="26" t="s"/>
+      <x:c r="D54" s="26" t="s"/>
+      <x:c r="E54" s="26" t="s"/>
+      <x:c r="F54" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="25" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C55" s="26" t="s"/>
+      <x:c r="D55" s="26" t="s"/>
+      <x:c r="E55" s="26" t="s"/>
+      <x:c r="F55" s="27" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="25" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L21" s="20">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C22" s="16" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D22" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E22" s="16" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F22" s="16" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H22" s="18">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I22" s="18">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J22" s="17" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K22" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="20">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M22" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C23" s="16" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D23" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E23" s="16" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F23" s="16" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H23" s="18">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I23" s="18">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J23" s="17" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K23" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="20">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M23" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C24" s="16" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D24" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E24" s="16" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F24" s="16" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G24" s="16" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H24" s="18">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I24" s="18">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J24" s="17" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K24" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="20">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M24" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C25" s="16" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D25" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E25" s="16" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F25" s="16" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G25" s="16" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H25" s="18">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I25" s="21">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J25" s="17" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K25" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="20">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M25" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C26" s="16" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D26" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E26" s="16" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F26" s="16" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G26" s="16" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H26" s="18">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I26" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="17" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K26" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="20">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M26" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C27" s="16" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D27" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E27" s="16" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F27" s="16" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G27" s="16" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H27" s="18">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I27" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="17" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K27" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="20">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M27" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C28" s="16" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D28" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E28" s="16" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F28" s="16" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G28" s="16" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H28" s="18">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I28" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K28" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="20">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M28" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C29" s="16" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D29" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E29" s="16" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F29" s="16" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G29" s="16" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H29" s="18">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I29" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="17" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K29" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="20">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M29" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C30" s="16" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D30" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E30" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F30" s="16" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G30" s="16" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H30" s="18">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I30" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="17" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K30" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="20">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M30" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C31" s="16" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D31" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E31" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F31" s="16" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G31" s="16" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H31" s="18">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I31" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="20">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M31" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C32" s="16" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D32" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E32" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F32" s="16" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H32" s="18">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I32" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K32" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="20">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M32" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C33" s="16" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D33" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E33" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F33" s="16" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G33" s="16" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H33" s="18">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I33" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K33" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="20">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M33" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C34" s="16" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D34" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E34" s="16" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F34" s="16" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G34" s="16" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H34" s="18">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I34" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="17" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K34" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="20">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M34" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C35" s="16" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D35" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E35" s="16" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F35" s="16" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G35" s="16" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H35" s="18">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I35" s="21">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J35" s="17" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K35" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="20">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M35" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C36" s="16" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D36" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E36" s="16" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F36" s="16" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G36" s="16" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H36" s="18">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I36" s="21">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J36" s="17" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K36" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="20">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M36" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="16" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C37" s="16" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D37" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E37" s="16" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F37" s="16" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G37" s="16" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H37" s="18">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I37" s="18">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J37" s="17" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K37" s="19" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L37" s="20">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M37" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C38" s="16" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D38" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E38" s="16" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F38" s="16" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G38" s="16" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H38" s="18">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I38" s="21">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J38" s="17" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K38" s="19" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L38" s="20">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M38" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C39" s="16" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D39" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E39" s="16" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F39" s="16" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G39" s="16" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H39" s="18">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I39" s="21">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J39" s="17" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K39" s="19" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L39" s="20">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M39" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C40" s="16" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D40" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E40" s="16" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F40" s="16" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G40" s="16" t="s">
+      <x:c r="C56" s="26" t="s"/>
+      <x:c r="D56" s="26" t="s"/>
+      <x:c r="E56" s="26" t="s"/>
+      <x:c r="F56" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="25" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H40" s="18">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I40" s="21">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J40" s="17" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K40" s="19" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L40" s="20">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M40" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C41" s="16" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D41" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E41" s="16" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F41" s="16" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="G41" s="16" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H41" s="18">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I41" s="21">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J41" s="17" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K41" s="19" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L41" s="20">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M41" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="16" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C42" s="16" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D42" s="17" t="s"/>
-      <x:c r="E42" s="16" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F42" s="16" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G42" s="16" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H42" s="18">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I42" s="18">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J42" s="17" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K42" s="19" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L42" s="20">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M42" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="16" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C43" s="16" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D43" s="17" t="s"/>
-      <x:c r="E43" s="16" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F43" s="16" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="G43" s="16" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H43" s="18">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I43" s="18">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J43" s="17" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K43" s="19" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L43" s="20">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M43" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="22" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C46" s="23" t="s"/>
-      <x:c r="D46" s="23" t="s"/>
-      <x:c r="E46" s="24" t="s"/>
-      <x:c r="F46" s="24" t="s"/>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="25" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C47" s="26" t="s"/>
-      <x:c r="D47" s="26" t="s"/>
-      <x:c r="E47" s="26" t="s"/>
-      <x:c r="F47" s="27" t="s">
-        <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="28" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C48" s="29" t="s"/>
-      <x:c r="D48" s="29" t="s"/>
-      <x:c r="E48" s="29" t="s"/>
-      <x:c r="F48" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C49" s="29" t="s"/>
-      <x:c r="D49" s="29" t="s"/>
-      <x:c r="E49" s="29" t="s"/>
-      <x:c r="F49" s="30" t="n">
+      <x:c r="C57" s="26" t="s"/>
+      <x:c r="D57" s="26" t="s"/>
+      <x:c r="E57" s="26" t="s"/>
+      <x:c r="F57" s="27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="25" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C58" s="26" t="s"/>
+      <x:c r="D58" s="26" t="s"/>
+      <x:c r="E58" s="26" t="s"/>
+      <x:c r="F58" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="28" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C50" s="29" t="s"/>
-      <x:c r="D50" s="29" t="s"/>
-      <x:c r="E50" s="29" t="s"/>
-      <x:c r="F50" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="28" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C51" s="29" t="s"/>
-      <x:c r="D51" s="29" t="s"/>
-      <x:c r="E51" s="29" t="s"/>
-      <x:c r="F51" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="28" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C52" s="29" t="s"/>
-      <x:c r="D52" s="29" t="s"/>
-      <x:c r="E52" s="29" t="s"/>
-      <x:c r="F52" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="28" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C53" s="29" t="s"/>
-      <x:c r="D53" s="29" t="s"/>
-      <x:c r="E53" s="29" t="s"/>
-      <x:c r="F53" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="28" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C54" s="29" t="s"/>
-      <x:c r="D54" s="29" t="s"/>
-      <x:c r="E54" s="29" t="s"/>
-      <x:c r="F54" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="28" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C55" s="29" t="s"/>
-      <x:c r="D55" s="29" t="s"/>
-      <x:c r="E55" s="29" t="s"/>
-      <x:c r="F55" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="28" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C56" s="29" t="s"/>
-      <x:c r="D56" s="29" t="s"/>
-      <x:c r="E56" s="29" t="s"/>
-      <x:c r="F56" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="31" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C57" s="32" t="s"/>
-      <x:c r="D57" s="32" t="s"/>
-      <x:c r="E57" s="32" t="s"/>
-      <x:c r="F57" s="33" t="n">
+    <x:row r="59" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B59" s="28" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C59" s="29" t="s"/>
+      <x:c r="D59" s="29" t="s"/>
+      <x:c r="E59" s="29" t="s"/>
+      <x:c r="F59" s="30" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4305,12 +4364,10 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="15">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B46:F46"/>
-    <x:mergeCell ref="B47:E47"/>
-    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B48:F48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
@@ -4320,6 +4377,8 @@
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
+    <x:mergeCell ref="B58:E58"/>
+    <x:mergeCell ref="B59:E59"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4360,74 +4419,72 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -4452,7 +4509,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -4492,1660 +4549,1710 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D8" s="13" t="s"/>
-      <x:c r="E8" s="13" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="F8" s="13" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="G8" s="13" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="C8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="13" t="s"/>
+      <x:c r="C9" s="13" t="s"/>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s"/>
+      <x:c r="F9" s="13" t="s"/>
+      <x:c r="G9" s="13" t="s"/>
+      <x:c r="H9" s="13" t="s"/>
+      <x:c r="I9" s="13" t="s"/>
+      <x:c r="J9" s="13" t="s"/>
+      <x:c r="K9" s="13" t="s"/>
+      <x:c r="L9" s="13" t="s"/>
+      <x:c r="M9" s="13" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46091.306099537</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I10" s="16">
         <x:v>46091.3107986111</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1511778</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L10" s="18">
         <x:v>46091.3131828704</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="13" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F9" s="13" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
+      <x:c r="M10" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46098.0792592593</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46098.0878935185</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1529776</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46098.0997569444</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I31" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I32" s="16">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I34" s="16">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I35" s="16">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I40" s="16">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="18">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I41" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L41" s="18">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I42" s="16">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L42" s="18">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I43" s="16">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J43" s="15" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="18">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D44" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="H44" s="16">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I44" s="16">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J44" s="15" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K44" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="18">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="D45" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="H45" s="16">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I45" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J45" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K45" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D46" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="H46" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I46" s="16">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J46" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K46" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M46" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D47" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="H47" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I47" s="16">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J47" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K47" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L47" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M47" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D48" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="G48" s="14" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="H48" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I48" s="16">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J48" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K48" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L48" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M48" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B49" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="D49" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="G49" s="14" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="H49" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I49" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J49" s="15" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K49" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L49" s="18">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M49" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B50" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="D50" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="H50" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I50" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J50" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K50" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L50" s="18">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M50" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="19" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="H9" s="14">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J9" s="13" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L9" s="14">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M9" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
+      <x:c r="C53" s="20" t="s"/>
+      <x:c r="D53" s="20" t="s"/>
+      <x:c r="E53" s="21" t="s"/>
+      <x:c r="F53" s="21" t="s"/>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B54" s="22" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D10" s="17" t="s"/>
-      <x:c r="E10" s="16" t="s">
+      <x:c r="C54" s="23" t="s"/>
+      <x:c r="D54" s="23" t="s"/>
+      <x:c r="E54" s="23" t="s"/>
+      <x:c r="F54" s="24" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F10" s="16" t="s">
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C55" s="26" t="s"/>
+      <x:c r="D55" s="26" t="s"/>
+      <x:c r="E55" s="26" t="s"/>
+      <x:c r="F55" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C56" s="26" t="s"/>
+      <x:c r="D56" s="26" t="s"/>
+      <x:c r="E56" s="26" t="s"/>
+      <x:c r="F56" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="25" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C57" s="26" t="s"/>
+      <x:c r="D57" s="26" t="s"/>
+      <x:c r="E57" s="26" t="s"/>
+      <x:c r="F57" s="27" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="25" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C58" s="26" t="s"/>
+      <x:c r="D58" s="26" t="s"/>
+      <x:c r="E58" s="26" t="s"/>
+      <x:c r="F58" s="27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B59" s="25" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C59" s="26" t="s"/>
+      <x:c r="D59" s="26" t="s"/>
+      <x:c r="E59" s="26" t="s"/>
+      <x:c r="F59" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B60" s="25" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C60" s="26" t="s"/>
+      <x:c r="D60" s="26" t="s"/>
+      <x:c r="E60" s="26" t="s"/>
+      <x:c r="F60" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B61" s="28" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
+      <x:c r="C61" s="29" t="s"/>
+      <x:c r="D61" s="29" t="s"/>
+      <x:c r="E61" s="29" t="s"/>
+      <x:c r="F61" s="30" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E12" s="16" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I13" s="18">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="20">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I14" s="21">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="20">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I15" s="21">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="20">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E16" s="16" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I16" s="21">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E17" s="16" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I17" s="21">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I18" s="21">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I19" s="21">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="20">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I20" s="21">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E21" s="16" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I21" s="21">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="20">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C22" s="16" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D22" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E22" s="16" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F22" s="16" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H22" s="18">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I22" s="21">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J22" s="17" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K22" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="20">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M22" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C23" s="16" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D23" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E23" s="16" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F23" s="16" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H23" s="18">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I23" s="21">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J23" s="17" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K23" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="20">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M23" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C24" s="16" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D24" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E24" s="16" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F24" s="16" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G24" s="16" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H24" s="18">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I24" s="21">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J24" s="17" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K24" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="20">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M24" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C25" s="16" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D25" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E25" s="16" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="F25" s="16" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G25" s="16" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="H25" s="18">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I25" s="21">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J25" s="17" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K25" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="20">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M25" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C26" s="16" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="D26" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E26" s="16" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F26" s="16" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G26" s="16" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H26" s="18">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I26" s="21">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J26" s="17" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K26" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="20">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M26" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C27" s="16" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D27" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E27" s="16" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F27" s="16" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G27" s="16" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H27" s="18">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I27" s="21">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J27" s="17" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K27" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="20">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M27" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C28" s="16" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D28" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E28" s="16" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F28" s="16" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G28" s="16" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H28" s="18">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I28" s="21">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J28" s="17" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K28" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="20">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M28" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C29" s="16" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D29" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E29" s="16" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F29" s="16" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G29" s="16" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="H29" s="18">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I29" s="21">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J29" s="17" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K29" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="20">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M29" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C30" s="16" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D30" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E30" s="16" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F30" s="16" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="G30" s="16" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="H30" s="18">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I30" s="21">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J30" s="17" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K30" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="20">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M30" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C31" s="16" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="D31" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E31" s="16" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F31" s="16" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="G31" s="16" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="H31" s="18">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I31" s="21">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J31" s="17" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K31" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="20">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M31" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C32" s="16" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="D32" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E32" s="16" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="F32" s="16" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="H32" s="18">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I32" s="21">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J32" s="17" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K32" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L32" s="20">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M32" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C33" s="16" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="D33" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E33" s="16" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F33" s="16" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G33" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H33" s="18">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I33" s="21">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J33" s="17" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K33" s="19" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L33" s="20">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M33" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C34" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D34" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E34" s="16" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F34" s="16" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G34" s="16" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H34" s="18">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I34" s="21">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J34" s="17" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K34" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="20">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M34" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C35" s="16" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="D35" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E35" s="16" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="F35" s="16" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="G35" s="16" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H35" s="18">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I35" s="21">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J35" s="17" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K35" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="20">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M35" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C36" s="16" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D36" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E36" s="16" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F36" s="16" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G36" s="16" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H36" s="18">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I36" s="21">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J36" s="17" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K36" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="20">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M36" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C37" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D37" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E37" s="16" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F37" s="16" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G37" s="16" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H37" s="18">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I37" s="18">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J37" s="17" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K37" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="20">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M37" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C38" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D38" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E38" s="16" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="F38" s="16" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="G38" s="16" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="H38" s="18">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I38" s="18">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J38" s="17" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K38" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L38" s="20">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M38" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C39" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D39" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E39" s="16" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="F39" s="16" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="G39" s="16" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="H39" s="18">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I39" s="18">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J39" s="17" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K39" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="20">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M39" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C40" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D40" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E40" s="16" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="F40" s="16" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G40" s="16" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="H40" s="18">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I40" s="18">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J40" s="17" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K40" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L40" s="20">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M40" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C41" s="16" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="D41" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E41" s="16" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="F41" s="16" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="G41" s="16" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="H41" s="18">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I41" s="21">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J41" s="17" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K41" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="20">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M41" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C42" s="16" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D42" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E42" s="16" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="F42" s="16" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="G42" s="16" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="H42" s="18">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I42" s="21">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J42" s="17" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K42" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="20">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M42" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C43" s="16" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="D43" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E43" s="16" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="F43" s="16" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="G43" s="16" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="H43" s="18">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I43" s="21">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J43" s="17" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K43" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="20">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M43" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C44" s="16" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D44" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E44" s="16" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F44" s="16" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G44" s="16" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="H44" s="18">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I44" s="21">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J44" s="17" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K44" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="20">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M44" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C45" s="16" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D45" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E45" s="16" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="F45" s="16" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="G45" s="16" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="H45" s="18">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I45" s="21">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J45" s="17" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K45" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="20">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M45" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C46" s="16" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D46" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E46" s="16" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="F46" s="16" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="G46" s="16" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="H46" s="18">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I46" s="21">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J46" s="17" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K46" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L46" s="20">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M46" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C47" s="16" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="D47" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E47" s="16" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="F47" s="16" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="G47" s="16" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="H47" s="18">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I47" s="21">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J47" s="17" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K47" s="19" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L47" s="20">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M47" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C48" s="16" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="D48" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E48" s="16" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="F48" s="16" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="G48" s="16" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="H48" s="18">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I48" s="21">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J48" s="17" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K48" s="19" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L48" s="20">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M48" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="22" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C51" s="23" t="s"/>
-      <x:c r="D51" s="23" t="s"/>
-      <x:c r="E51" s="24" t="s"/>
-      <x:c r="F51" s="24" t="s"/>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B52" s="25" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C52" s="26" t="s"/>
-      <x:c r="D52" s="26" t="s"/>
-      <x:c r="E52" s="26" t="s"/>
-      <x:c r="F52" s="27" t="s">
-        <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="28" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C53" s="29" t="s"/>
-      <x:c r="D53" s="29" t="s"/>
-      <x:c r="E53" s="29" t="s"/>
-      <x:c r="F53" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C54" s="29" t="s"/>
-      <x:c r="D54" s="29" t="s"/>
-      <x:c r="E54" s="29" t="s"/>
-      <x:c r="F54" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="28" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C55" s="29" t="s"/>
-      <x:c r="D55" s="29" t="s"/>
-      <x:c r="E55" s="29" t="s"/>
-      <x:c r="F55" s="30" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="28" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C56" s="29" t="s"/>
-      <x:c r="D56" s="29" t="s"/>
-      <x:c r="E56" s="29" t="s"/>
-      <x:c r="F56" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="28" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C57" s="29" t="s"/>
-      <x:c r="D57" s="29" t="s"/>
-      <x:c r="E57" s="29" t="s"/>
-      <x:c r="F57" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="28" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C58" s="29" t="s"/>
-      <x:c r="D58" s="29" t="s"/>
-      <x:c r="E58" s="29" t="s"/>
-      <x:c r="F58" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B59" s="31" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C59" s="32" t="s"/>
-      <x:c r="D59" s="32" t="s"/>
-      <x:c r="E59" s="32" t="s"/>
-      <x:c r="F59" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7080,18 +7187,18 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="12">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B51:F51"/>
-    <x:mergeCell ref="B52:E52"/>
-    <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B53:F53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
+    <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B61:E61"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -65,42 +65,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -1033,7 +997,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1077,13 +1041,20 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
@@ -1345,7 +1316,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1353,10 +1324,10 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1371,13 +1342,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1389,41 +1354,50 @@
     <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1454,24 +1428,16 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1486,55 +1452,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1853,7 +1835,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1893,1541 +1875,1491 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="14">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="H9" s="14">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="14">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="13" t="s"/>
-      <x:c r="C9" s="13" t="s"/>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s"/>
-      <x:c r="F9" s="13" t="s"/>
-      <x:c r="G9" s="13" t="s"/>
-      <x:c r="H9" s="13" t="s"/>
-      <x:c r="I9" s="13" t="s"/>
-      <x:c r="J9" s="13" t="s"/>
-      <x:c r="K9" s="13" t="s"/>
-      <x:c r="L9" s="13" t="s"/>
-      <x:c r="M9" s="13" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="D10" s="17" t="s"/>
+      <x:c r="E10" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="H10" s="18">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M10" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="16" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="F11" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="18">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="L11" s="20">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M11" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="16" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="F12" s="16" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="G12" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H12" s="18">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="L12" s="20">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M12" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="s"/>
+      <x:c r="E13" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H13" s="18">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M13" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H14" s="18">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M14" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H15" s="18">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M15" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H16" s="18">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M16" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H17" s="18">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M17" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H18" s="18">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M18" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H19" s="18">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M19" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H20" s="18">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M20" s="16" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="16" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="s"/>
+      <x:c r="E21" s="16" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H21" s="18">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M21" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H22" s="18">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I22" s="18">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="20">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M22" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H23" s="18">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I23" s="18">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K23" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="20">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M23" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H24" s="18">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I24" s="18">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K24" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="20">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M24" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C25" s="16" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E25" s="16" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F25" s="16" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G25" s="16" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H25" s="18">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I25" s="18">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J25" s="17" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K25" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="20">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M25" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E26" s="16" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F26" s="16" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G26" s="16" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H26" s="18">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I26" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K26" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="20">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M26" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E27" s="16" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G27" s="16" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H27" s="18">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I27" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K27" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="20">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M27" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E28" s="16" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F28" s="16" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H28" s="18">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I28" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K28" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="20">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M28" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C29" s="16" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E29" s="16" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F29" s="16" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H29" s="18">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I29" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="17" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K29" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="20">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M29" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C30" s="16" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E30" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F30" s="16" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G30" s="16" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H30" s="18">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I30" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="17" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K30" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="20">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M30" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C31" s="16" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E31" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F31" s="16" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G31" s="16" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H31" s="18">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I31" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K31" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="20">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M31" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C32" s="16" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E32" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F32" s="16" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H32" s="18">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I32" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K32" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="20">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M32" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C33" s="16" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E33" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F33" s="16" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G33" s="16" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H33" s="18">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I33" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="17" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K33" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="20">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M33" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C34" s="16" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E34" s="16" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F34" s="16" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G34" s="16" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H34" s="18">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I34" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="17" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K34" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="20">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M34" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C35" s="16" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E35" s="16" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F35" s="16" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H35" s="18">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I35" s="18">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J35" s="17" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K35" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="20">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M35" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C36" s="16" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E36" s="16" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F36" s="16" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G36" s="16" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H36" s="18">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I36" s="18">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J36" s="17" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K36" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="20">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M36" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="16" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C37" s="16" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E37" s="16" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F37" s="16" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G37" s="16" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H37" s="18">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I37" s="18">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J37" s="17" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K37" s="19" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L37" s="20">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M37" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C38" s="16" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E38" s="16" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F38" s="16" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G38" s="16" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H38" s="18">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I38" s="18">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J38" s="17" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K38" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L38" s="20">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M38" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C39" s="16" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E39" s="16" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F39" s="16" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G39" s="16" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H39" s="18">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I39" s="18">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J39" s="17" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K39" s="19" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L39" s="20">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M39" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C40" s="16" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E40" s="16" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F40" s="16" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G40" s="16" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H40" s="18">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I40" s="18">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J40" s="17" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K40" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L40" s="20">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M40" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C41" s="16" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E41" s="16" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F41" s="16" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H41" s="18">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I41" s="18">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J41" s="17" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K41" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L41" s="20">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M41" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="16" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C42" s="16" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="s"/>
+      <x:c r="E42" s="16" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F42" s="16" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H42" s="18">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I42" s="18">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J42" s="17" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K42" s="19" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L42" s="20">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M42" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="16" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C43" s="16" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="s"/>
+      <x:c r="E43" s="16" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F43" s="16" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H43" s="18">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I43" s="18">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J43" s="17" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K43" s="19" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L43" s="20">
+        <x:v>46080.3345717593</x:v>
+      </x:c>
+      <x:c r="M43" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="21" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C46" s="22" t="s"/>
+      <x:c r="D46" s="22" t="s"/>
+      <x:c r="E46" s="23" t="s"/>
+      <x:c r="F46" s="23" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B47" s="24" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C47" s="25" t="s"/>
+      <x:c r="D47" s="25" t="s"/>
+      <x:c r="E47" s="25" t="s"/>
+      <x:c r="F47" s="26" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C48" s="28" t="s"/>
+      <x:c r="D48" s="28" t="s"/>
+      <x:c r="E48" s="28" t="s"/>
+      <x:c r="F48" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="27" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C49" s="28" t="s"/>
+      <x:c r="D49" s="28" t="s"/>
+      <x:c r="E49" s="28" t="s"/>
+      <x:c r="F49" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="27" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C50" s="28" t="s"/>
+      <x:c r="D50" s="28" t="s"/>
+      <x:c r="E50" s="28" t="s"/>
+      <x:c r="F50" s="29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="27" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C51" s="28" t="s"/>
+      <x:c r="D51" s="28" t="s"/>
+      <x:c r="E51" s="28" t="s"/>
+      <x:c r="F51" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="27" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C52" s="28" t="s"/>
+      <x:c r="D52" s="28" t="s"/>
+      <x:c r="E52" s="28" t="s"/>
+      <x:c r="F52" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="27" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="27" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C55" s="28" t="s"/>
+      <x:c r="D55" s="28" t="s"/>
+      <x:c r="E55" s="28" t="s"/>
+      <x:c r="F55" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="27" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C56" s="28" t="s"/>
+      <x:c r="D56" s="28" t="s"/>
+      <x:c r="E56" s="28" t="s"/>
+      <x:c r="F56" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B57" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C57" s="31" t="s"/>
+      <x:c r="D57" s="31" t="s"/>
+      <x:c r="E57" s="31" t="s"/>
+      <x:c r="F57" s="32" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s"/>
-      <x:c r="E23" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I28" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I29" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I30" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I31" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I32" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I33" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I34" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I35" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I36" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I37" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I38" s="16">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E40" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I40" s="16">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K40" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L40" s="18">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D41" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E41" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G41" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I41" s="16">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K41" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L41" s="18">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M41" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C42" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D42" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E42" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G42" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H42" s="16">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I42" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J42" s="15" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K42" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L42" s="18">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M42" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C43" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D43" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E43" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="F43" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G43" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="H43" s="16">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I43" s="16">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J43" s="15" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K43" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L43" s="18">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M43" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C44" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D44" s="15" t="s"/>
-      <x:c r="E44" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="F44" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G44" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H44" s="16">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I44" s="16">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J44" s="15" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K44" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L44" s="18">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M44" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C45" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D45" s="15" t="s"/>
-      <x:c r="E45" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="F45" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="G45" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H45" s="16">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I45" s="16">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J45" s="15" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K45" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L45" s="18">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M45" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="19" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C48" s="20" t="s"/>
-      <x:c r="D48" s="20" t="s"/>
-      <x:c r="E48" s="21" t="s"/>
-      <x:c r="F48" s="21" t="s"/>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B49" s="22" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C49" s="23" t="s"/>
-      <x:c r="D49" s="23" t="s"/>
-      <x:c r="E49" s="23" t="s"/>
-      <x:c r="F49" s="24" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C50" s="26" t="s"/>
-      <x:c r="D50" s="26" t="s"/>
-      <x:c r="E50" s="26" t="s"/>
-      <x:c r="F50" s="27" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C51" s="26" t="s"/>
-      <x:c r="D51" s="26" t="s"/>
-      <x:c r="E51" s="26" t="s"/>
-      <x:c r="F51" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="25" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C52" s="26" t="s"/>
-      <x:c r="D52" s="26" t="s"/>
-      <x:c r="E52" s="26" t="s"/>
-      <x:c r="F52" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="25" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C53" s="26" t="s"/>
-      <x:c r="D53" s="26" t="s"/>
-      <x:c r="E53" s="26" t="s"/>
-      <x:c r="F53" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="25" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C54" s="26" t="s"/>
-      <x:c r="D54" s="26" t="s"/>
-      <x:c r="E54" s="26" t="s"/>
-      <x:c r="F54" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="25" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C55" s="26" t="s"/>
-      <x:c r="D55" s="26" t="s"/>
-      <x:c r="E55" s="26" t="s"/>
-      <x:c r="F55" s="27" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="25" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C56" s="26" t="s"/>
-      <x:c r="D56" s="26" t="s"/>
-      <x:c r="E56" s="26" t="s"/>
-      <x:c r="F56" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="25" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C57" s="26" t="s"/>
-      <x:c r="D57" s="26" t="s"/>
-      <x:c r="E57" s="26" t="s"/>
-      <x:c r="F57" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="25" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C58" s="26" t="s"/>
-      <x:c r="D58" s="26" t="s"/>
-      <x:c r="E58" s="26" t="s"/>
-      <x:c r="F58" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B59" s="28" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="C59" s="29" t="s"/>
-      <x:c r="D59" s="29" t="s"/>
-      <x:c r="E59" s="29" t="s"/>
-      <x:c r="F59" s="30" t="n">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4367,7 +4299,9 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B48:F48"/>
+    <x:mergeCell ref="B46:F46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
@@ -4377,8 +4311,6 @@
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
-    <x:mergeCell ref="B58:E58"/>
-    <x:mergeCell ref="B59:E59"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4472,7 +4404,7 @@
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
       <x:c r="B4" s="11" t="s">
-        <x:v>185</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -4509,7 +4441,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -4549,1710 +4481,1660 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C8" s="13" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H9" s="14">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L9" s="14">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="s"/>
+      <x:c r="E10" s="16" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H10" s="18">
+        <x:v>46098.0792592593</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>46098.0878935185</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="n">
+        <x:v>1529776</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>46098.0997569444</x:v>
+      </x:c>
+      <x:c r="M10" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H11" s="18">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M11" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H12" s="18">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M12" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H13" s="18">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M13" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H14" s="18">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M14" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H15" s="18">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M15" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H16" s="18">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M16" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H17" s="18">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M17" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H18" s="18">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M18" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H19" s="18">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M19" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H20" s="18">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M20" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H21" s="18">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M21" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H22" s="18">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="18">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="20">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H23" s="18">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I23" s="18">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K23" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="20">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M23" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H24" s="18">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I24" s="18">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K24" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="20">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M24" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C25" s="16" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E25" s="16" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F25" s="16" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G25" s="16" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H25" s="18">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I25" s="18">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J25" s="17" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K25" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="20">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M25" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E26" s="16" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F26" s="16" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G26" s="16" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H26" s="18">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I26" s="18">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K26" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="20">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M26" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E27" s="16" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G27" s="16" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H27" s="18">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I27" s="18">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K27" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="20">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M27" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E28" s="16" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F28" s="16" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H28" s="18">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I28" s="18">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="17" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K28" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="20">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M28" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C29" s="16" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E29" s="16" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F29" s="16" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H29" s="18">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I29" s="18">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J29" s="17" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K29" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="20">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M29" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C30" s="16" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E30" s="16" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F30" s="16" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G30" s="16" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H30" s="18">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I30" s="18">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J30" s="17" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K30" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="20">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M30" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C31" s="16" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E31" s="16" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="F31" s="16" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G31" s="16" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H31" s="18">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I31" s="18">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J31" s="17" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K31" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="20">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M31" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C32" s="16" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E32" s="16" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F32" s="16" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H32" s="18">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I32" s="18">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J32" s="17" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K32" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L32" s="20">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M32" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C33" s="16" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E33" s="16" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F33" s="16" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G33" s="16" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H33" s="18">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I33" s="18">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J33" s="17" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K33" s="19" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L33" s="20">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M33" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C34" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E34" s="16" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F34" s="16" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G34" s="16" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H34" s="18">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I34" s="18">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J34" s="17" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K34" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="20">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M34" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C35" s="16" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E35" s="16" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F35" s="16" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H35" s="18">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I35" s="18">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J35" s="17" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K35" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="20">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M35" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C36" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E36" s="16" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F36" s="16" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G36" s="16" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H36" s="18">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I36" s="18">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J36" s="17" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K36" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="20">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M36" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C37" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E37" s="16" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F37" s="16" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G37" s="16" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H37" s="18">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I37" s="18">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J37" s="17" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K37" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="20">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M37" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C38" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E38" s="16" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F38" s="16" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G38" s="16" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="H38" s="18">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I38" s="18">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J38" s="17" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K38" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="20">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M38" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C39" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E39" s="16" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F39" s="16" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G39" s="16" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H39" s="18">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I39" s="18">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J39" s="17" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K39" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="20">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M39" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C40" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E40" s="16" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F40" s="16" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G40" s="16" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H40" s="18">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I40" s="18">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J40" s="17" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K40" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="20">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M40" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C41" s="16" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E41" s="16" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="F41" s="16" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="H41" s="18">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I41" s="18">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J41" s="17" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K41" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="20">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M41" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C42" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E42" s="16" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F42" s="16" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H42" s="18">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I42" s="18">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J42" s="17" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K42" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="20">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M42" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C43" s="16" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E43" s="16" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F43" s="16" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H43" s="18">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I43" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J43" s="17" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K43" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="20">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M43" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C44" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D44" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E44" s="16" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F44" s="16" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="H44" s="18">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I44" s="18">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J44" s="17" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K44" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="20">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M44" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C45" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D45" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F45" s="16" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="G45" s="16" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H45" s="18">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I45" s="18">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J45" s="17" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K45" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="20">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M45" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C46" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D46" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E46" s="16" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="F46" s="16" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="H46" s="18">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I46" s="18">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J46" s="17" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K46" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="20">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M46" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C47" s="16" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D47" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E47" s="16" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F47" s="16" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="H47" s="18">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I47" s="18">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J47" s="17" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K47" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L47" s="20">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M47" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C48" s="16" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="D48" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E48" s="16" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F48" s="16" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="G48" s="16" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H48" s="18">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I48" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J48" s="17" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K48" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L48" s="20">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M48" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="21" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C51" s="22" t="s"/>
+      <x:c r="D51" s="22" t="s"/>
+      <x:c r="E51" s="23" t="s"/>
+      <x:c r="F51" s="23" t="s"/>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B52" s="24" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C52" s="25" t="s"/>
+      <x:c r="D52" s="25" t="s"/>
+      <x:c r="E52" s="25" t="s"/>
+      <x:c r="F52" s="26" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="27" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="27" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C55" s="28" t="s"/>
+      <x:c r="D55" s="28" t="s"/>
+      <x:c r="E55" s="28" t="s"/>
+      <x:c r="F55" s="29" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="13" t="s"/>
-      <x:c r="C9" s="13" t="s"/>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s"/>
-      <x:c r="F9" s="13" t="s"/>
-      <x:c r="G9" s="13" t="s"/>
-      <x:c r="H9" s="13" t="s"/>
-      <x:c r="I9" s="13" t="s"/>
-      <x:c r="J9" s="13" t="s"/>
-      <x:c r="K9" s="13" t="s"/>
-      <x:c r="L9" s="13" t="s"/>
-      <x:c r="M9" s="13" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I28" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I29" s="16">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I30" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I31" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I32" s="16">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I33" s="16">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I34" s="16">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I35" s="16">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I36" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I37" s="16">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I38" s="16">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E40" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I40" s="16">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K40" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L40" s="18">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D41" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E41" s="14" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="G41" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I41" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K41" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L41" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M41" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C42" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D42" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E42" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="G42" s="14" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="H42" s="16">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I42" s="16">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J42" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K42" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L42" s="18">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M42" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C43" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="D43" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E43" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="F43" s="14" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="G43" s="14" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="H43" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I43" s="16">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J43" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K43" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="18">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M43" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C44" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D44" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E44" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="F44" s="14" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="G44" s="14" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="H44" s="16">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I44" s="16">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J44" s="15" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K44" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="18">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M44" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C45" s="14" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="D45" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E45" s="14" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="F45" s="14" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="G45" s="14" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="H45" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I45" s="16">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J45" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K45" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M45" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C46" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D46" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E46" s="14" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="F46" s="14" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="G46" s="14" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="H46" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I46" s="16">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J46" s="15" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K46" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L46" s="18">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M46" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C47" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D47" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E47" s="14" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="F47" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="G47" s="14" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="H47" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I47" s="16">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J47" s="15" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K47" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L47" s="18">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M47" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C48" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D48" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E48" s="14" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="F48" s="14" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="G48" s="14" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="H48" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I48" s="16">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J48" s="15" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K48" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L48" s="18">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M48" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B49" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C49" s="14" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="D49" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E49" s="14" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="F49" s="14" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="G49" s="14" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="H49" s="16">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I49" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J49" s="15" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K49" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L49" s="18">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M49" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B50" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C50" s="14" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="D50" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E50" s="14" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="F50" s="14" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="G50" s="14" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="H50" s="16">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I50" s="16">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J50" s="15" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K50" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L50" s="18">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M50" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="19" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C53" s="20" t="s"/>
-      <x:c r="D53" s="20" t="s"/>
-      <x:c r="E53" s="21" t="s"/>
-      <x:c r="F53" s="21" t="s"/>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B54" s="22" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C54" s="23" t="s"/>
-      <x:c r="D54" s="23" t="s"/>
-      <x:c r="E54" s="23" t="s"/>
-      <x:c r="F54" s="24" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C55" s="26" t="s"/>
-      <x:c r="D55" s="26" t="s"/>
-      <x:c r="E55" s="26" t="s"/>
-      <x:c r="F55" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C56" s="26" t="s"/>
-      <x:c r="D56" s="26" t="s"/>
-      <x:c r="E56" s="26" t="s"/>
-      <x:c r="F56" s="27" t="n">
-        <x:v>3</x:v>
+      <x:c r="B56" s="27" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C56" s="28" t="s"/>
+      <x:c r="D56" s="28" t="s"/>
+      <x:c r="E56" s="28" t="s"/>
+      <x:c r="F56" s="29" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="25" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C57" s="26" t="s"/>
-      <x:c r="D57" s="26" t="s"/>
-      <x:c r="E57" s="26" t="s"/>
-      <x:c r="F57" s="27" t="n">
-        <x:v>23</x:v>
+      <x:c r="B57" s="27" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C57" s="28" t="s"/>
+      <x:c r="D57" s="28" t="s"/>
+      <x:c r="E57" s="28" t="s"/>
+      <x:c r="F57" s="29" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="25" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C58" s="26" t="s"/>
-      <x:c r="D58" s="26" t="s"/>
-      <x:c r="E58" s="26" t="s"/>
-      <x:c r="F58" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B59" s="25" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C59" s="26" t="s"/>
-      <x:c r="D59" s="26" t="s"/>
-      <x:c r="E59" s="26" t="s"/>
-      <x:c r="F59" s="27" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B60" s="25" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C60" s="26" t="s"/>
-      <x:c r="D60" s="26" t="s"/>
-      <x:c r="E60" s="26" t="s"/>
-      <x:c r="F60" s="27" t="n">
+      <x:c r="B58" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C58" s="28" t="s"/>
+      <x:c r="D58" s="28" t="s"/>
+      <x:c r="E58" s="28" t="s"/>
+      <x:c r="F58" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B61" s="28" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="C61" s="29" t="s"/>
-      <x:c r="D61" s="29" t="s"/>
-      <x:c r="E61" s="29" t="s"/>
-      <x:c r="F61" s="30" t="n">
+    <x:row r="59" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B59" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C59" s="31" t="s"/>
+      <x:c r="D59" s="31" t="s"/>
+      <x:c r="E59" s="31" t="s"/>
+      <x:c r="F59" s="32" t="n">
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7190,15 +7072,15 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B53:F53"/>
+    <x:mergeCell ref="B51:F51"/>
+    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
-    <x:mergeCell ref="B60:E60"/>
-    <x:mergeCell ref="B61:E61"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -586,6 +586,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -595,18 +607,6 @@
     <x:t>43A-3-2026-1179-857</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06915-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1178-478</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -631,6 +631,15 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -640,15 +649,6 @@
     <x:t>43A-3-2026-1150-325</x:t>
   </x:si>
   <x:si>
-    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0780 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1151-716</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -697,6 +697,24 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -706,15 +724,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -724,15 +733,6 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -868,6 +868,15 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -895,15 +904,6 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -962,6 +962,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBOY INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLOOR CYBERZONE SM CALAMBA NATIONAL HIGHWAY, REAL, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-16-12-0951</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1205-403</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -4610,10 +4622,10 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="H11" s="18">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I11" s="18">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J11" s="17" t="n">
         <x:v>1511203</x:v>
@@ -4622,7 +4634,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M11" s="16" t="s">
         <x:v>190</x:v>
@@ -4648,10 +4660,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H12" s="18">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J12" s="17" t="n">
         <x:v>1511203</x:v>
@@ -4660,7 +4672,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M12" s="16" t="s">
         <x:v>190</x:v>
@@ -4762,19 +4774,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H15" s="18">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J15" s="17" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46097.149525463</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M15" s="16" t="s">
         <x:v>190</x:v>
@@ -4800,19 +4812,19 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H16" s="18">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J16" s="17" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M16" s="16" t="s">
         <x:v>190</x:v>
@@ -4990,19 +5002,19 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H21" s="18">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>46133</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J21" s="17" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M21" s="16" t="s">
         <x:v>190</x:v>
@@ -5066,19 +5078,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H23" s="18">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J23" s="17" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M23" s="16" t="s">
         <x:v>190</x:v>
@@ -5104,19 +5116,19 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="H24" s="18">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46035</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J24" s="17" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M24" s="16" t="s">
         <x:v>190</x:v>
@@ -5598,10 +5610,10 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="H37" s="18">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I37" s="18">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J37" s="17" t="n">
         <x:v>1507966</x:v>
@@ -5610,7 +5622,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M37" s="16" t="s">
         <x:v>24</x:v>
@@ -5636,19 +5648,19 @@
         <x:v>286</x:v>
       </x:c>
       <x:c r="H38" s="18">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I38" s="18">
-        <x:v>46085.1709375</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J38" s="17" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M38" s="16" t="s">
         <x:v>24</x:v>
@@ -5674,19 +5686,19 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="H39" s="18">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I39" s="18">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J39" s="17" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M39" s="16" t="s">
         <x:v>24</x:v>
@@ -5712,19 +5724,19 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="H40" s="18">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I40" s="18">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J40" s="17" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M40" s="16" t="s">
         <x:v>24</x:v>
@@ -5978,22 +5990,22 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="H47" s="18">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46098.2908796296</x:v>
       </x:c>
       <x:c r="I47" s="18">
-        <x:v>46094</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J47" s="17" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511858</x:v>
       </x:c>
       <x:c r="K47" s="19" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L47" s="20">
-        <x:v>46093.3109375</x:v>
+        <x:v>46098.3188657407</x:v>
       </x:c>
       <x:c r="M47" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
@@ -6016,60 +6028,87 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="H48" s="18">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I48" s="18">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J48" s="17" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K48" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L48" s="20">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M48" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B49" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C49" s="16" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D49" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E49" s="16" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F49" s="16" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="G49" s="16" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="H49" s="18">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I49" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J49" s="17" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K49" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L49" s="20">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M48" s="16" t="s">
+      <x:c r="M49" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="21" t="s">
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B52" s="21" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C51" s="22" t="s"/>
-      <x:c r="D51" s="22" t="s"/>
-      <x:c r="E51" s="23" t="s"/>
-      <x:c r="F51" s="23" t="s"/>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B52" s="24" t="s">
+      <x:c r="C52" s="22" t="s"/>
+      <x:c r="D52" s="22" t="s"/>
+      <x:c r="E52" s="23" t="s"/>
+      <x:c r="F52" s="23" t="s"/>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B53" s="24" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C52" s="25" t="s"/>
-      <x:c r="D52" s="25" t="s"/>
-      <x:c r="E52" s="25" t="s"/>
-      <x:c r="F52" s="26" t="s">
+      <x:c r="C53" s="25" t="s"/>
+      <x:c r="D53" s="25" t="s"/>
+      <x:c r="E53" s="25" t="s"/>
+      <x:c r="F53" s="26" t="s">
         <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
       <x:c r="B54" s="27" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C54" s="28" t="s"/>
       <x:c r="D54" s="28" t="s"/>
@@ -6080,60 +6119,70 @@
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
       <x:c r="B55" s="27" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C55" s="28" t="s"/>
       <x:c r="D55" s="28" t="s"/>
       <x:c r="E55" s="28" t="s"/>
       <x:c r="F55" s="29" t="n">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
       <x:c r="B56" s="27" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C56" s="28" t="s"/>
       <x:c r="D56" s="28" t="s"/>
       <x:c r="E56" s="28" t="s"/>
       <x:c r="F56" s="29" t="n">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
       <x:c r="B57" s="27" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C57" s="28" t="s"/>
       <x:c r="D57" s="28" t="s"/>
       <x:c r="E57" s="28" t="s"/>
       <x:c r="F57" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="27" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C58" s="28" t="s"/>
       <x:c r="D58" s="28" t="s"/>
       <x:c r="E58" s="28" t="s"/>
       <x:c r="F58" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B59" s="30" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B59" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C59" s="28" t="s"/>
+      <x:c r="D59" s="28" t="s"/>
+      <x:c r="E59" s="28" t="s"/>
+      <x:c r="F59" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B60" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="C59" s="31" t="s"/>
-      <x:c r="D59" s="31" t="s"/>
-      <x:c r="E59" s="31" t="s"/>
-      <x:c r="F59" s="32" t="n">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C60" s="31" t="s"/>
+      <x:c r="D60" s="31" t="s"/>
+      <x:c r="E60" s="31" t="s"/>
+      <x:c r="F60" s="32" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7072,8 +7121,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B51:F51"/>
-    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B52:F52"/>
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
@@ -7081,6 +7129,7 @@
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
+    <x:mergeCell ref="B60:E60"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -586,6 +586,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06919-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1179-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -595,18 +607,6 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06919-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1179-857</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -622,6 +622,24 @@
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
     <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
   </x:si>
   <x:si>
@@ -631,24 +649,6 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
-    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0780 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1151-716</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1150-325</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -676,6 +676,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -685,18 +694,36 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-020R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1156-896</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
     <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
   </x:si>
   <x:si>
@@ -706,33 +733,6 @@
     <x:t>43A-2-2026-1085-453</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -745,6 +745,18 @@
     <x:t>43A-2-2026-1086-471</x:t>
   </x:si>
   <x:si>
+    <x:t>HLH GENTECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-17-11-0683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1109-317</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
   </x:si>
   <x:si>
@@ -805,6 +817,15 @@
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-471R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1108-762</x:t>
+  </x:si>
+  <x:si>
     <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -823,15 +844,6 @@
     <x:t>43A-3-2026-1168-173</x:t>
   </x:si>
   <x:si>
-    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 24-471R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1108-762</x:t>
-  </x:si>
-  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -868,6 +880,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -875,24 +905,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
@@ -4622,10 +4634,10 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="H11" s="18">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I11" s="18">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J11" s="17" t="n">
         <x:v>1511203</x:v>
@@ -4634,7 +4646,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M11" s="16" t="s">
         <x:v>190</x:v>
@@ -4660,10 +4672,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H12" s="18">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J12" s="17" t="n">
         <x:v>1511203</x:v>
@@ -4672,7 +4684,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M12" s="16" t="s">
         <x:v>190</x:v>
@@ -4736,19 +4748,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H14" s="18">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I14" s="18">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J14" s="17" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M14" s="16" t="s">
         <x:v>190</x:v>
@@ -4774,19 +4786,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H15" s="18">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J15" s="17" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M15" s="16" t="s">
         <x:v>190</x:v>
@@ -4812,19 +4824,19 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H16" s="18">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J16" s="17" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46097.149525463</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M16" s="16" t="s">
         <x:v>190</x:v>
@@ -4926,19 +4938,19 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="H19" s="18">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J19" s="17" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M19" s="16" t="s">
         <x:v>190</x:v>
@@ -4964,19 +4976,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="H20" s="18">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J20" s="17" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M20" s="16" t="s">
         <x:v>190</x:v>
@@ -5002,19 +5014,19 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H21" s="18">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>46035</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J21" s="17" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M21" s="16" t="s">
         <x:v>190</x:v>
@@ -5078,19 +5090,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H23" s="18">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>46133</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J23" s="17" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M23" s="16" t="s">
         <x:v>190</x:v>
@@ -5116,19 +5128,19 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="H24" s="18">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46100</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J24" s="17" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M24" s="16" t="s">
         <x:v>190</x:v>
@@ -5192,19 +5204,19 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="H26" s="18">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>46100</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J26" s="17" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M26" s="16" t="s">
         <x:v>190</x:v>
@@ -5230,19 +5242,19 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H27" s="18">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J27" s="17" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M27" s="16" t="s">
         <x:v>190</x:v>
@@ -5268,19 +5280,19 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="H28" s="18">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>46100</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J28" s="17" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M28" s="16" t="s">
         <x:v>190</x:v>
@@ -5306,19 +5318,19 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="H29" s="18">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J29" s="17" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M29" s="16" t="s">
         <x:v>190</x:v>
@@ -5335,28 +5347,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E30" s="16" t="s">
-        <x:v>245</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F30" s="16" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G30" s="16" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="H30" s="18">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J30" s="17" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M30" s="16" t="s">
         <x:v>190</x:v>
@@ -5367,13 +5379,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C31" s="16" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="D31" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E31" s="16" t="s">
-        <x:v>260</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F31" s="16" t="s">
         <x:v>261</x:v>
@@ -5382,19 +5394,19 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="H31" s="18">
-        <x:v>46069.115150463</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I31" s="18">
-        <x:v>46172</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J31" s="17" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M31" s="16" t="s">
         <x:v>190</x:v>
@@ -5405,34 +5417,34 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C32" s="16" t="s">
-        <x:v>259</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D32" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E32" s="16" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F32" s="16" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G32" s="16" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H32" s="18">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I32" s="18">
-        <x:v>46070</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J32" s="17" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M32" s="16" t="s">
         <x:v>190</x:v>
@@ -5443,34 +5455,34 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="16" t="s">
-        <x:v>259</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D33" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E33" s="16" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F33" s="16" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G33" s="16" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="H33" s="18">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I33" s="18">
-        <x:v>45751</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J33" s="17" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K33" s="19" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="20">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M33" s="16" t="s">
         <x:v>190</x:v>
@@ -5481,34 +5493,34 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C34" s="16" t="s">
-        <x:v>69</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D34" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E34" s="16" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="F34" s="16" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G34" s="16" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="H34" s="18">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J34" s="17" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M34" s="16" t="s">
         <x:v>190</x:v>
@@ -5519,7 +5531,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C35" s="16" t="s">
-        <x:v>272</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D35" s="17" t="s">
         <x:v>53</x:v>
@@ -5534,19 +5546,19 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="H35" s="18">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I35" s="18">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J35" s="17" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M35" s="16" t="s">
         <x:v>190</x:v>
@@ -5572,33 +5584,33 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H36" s="18">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I36" s="18">
-        <x:v>46095</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J36" s="17" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M36" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B37" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C37" s="16" t="s">
         <x:v>280</x:v>
       </x:c>
       <x:c r="D37" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E37" s="16" t="s">
         <x:v>281</x:v>
@@ -5610,22 +5622,22 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="H37" s="18">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I37" s="18">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J37" s="17" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M37" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5633,19 +5645,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C38" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D38" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E38" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F38" s="16" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G38" s="16" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="H38" s="18">
         <x:v>46085.16625</x:v>
@@ -5671,19 +5683,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C39" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D39" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E39" s="16" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F39" s="16" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G39" s="16" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H39" s="18">
         <x:v>46085.1709143519</x:v>
@@ -5709,34 +5721,34 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C40" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D40" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E40" s="16" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="F40" s="16" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="G40" s="16" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="H40" s="18">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I40" s="18">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J40" s="17" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M40" s="16" t="s">
         <x:v>24</x:v>
@@ -5744,13 +5756,13 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C41" s="16" t="s">
-        <x:v>293</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D41" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E41" s="16" t="s">
         <x:v>294</x:v>
@@ -5762,22 +5774,22 @@
         <x:v>296</x:v>
       </x:c>
       <x:c r="H41" s="18">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I41" s="18">
-        <x:v>46145</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J41" s="17" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M41" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
@@ -5785,34 +5797,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C42" s="16" t="s">
-        <x:v>216</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D42" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E42" s="16" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F42" s="16" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="G42" s="16" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H42" s="18">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I42" s="18">
-        <x:v>46103</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J42" s="17" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46097.2478125</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M42" s="16" t="s">
         <x:v>190</x:v>
@@ -5823,7 +5835,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C43" s="16" t="s">
-        <x:v>300</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D43" s="17" t="s">
         <x:v>53</x:v>
@@ -5838,22 +5850,22 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="H43" s="18">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I43" s="18">
-        <x:v>46084</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J43" s="17" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K43" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L43" s="20">
-        <x:v>46083.104224537</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M43" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
@@ -5861,34 +5873,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C44" s="16" t="s">
-        <x:v>276</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="D44" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E44" s="16" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F44" s="16" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="G44" s="16" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="H44" s="18">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I44" s="18">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J44" s="17" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K44" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="20">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M44" s="16" t="s">
         <x:v>84</x:v>
@@ -5899,34 +5911,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C45" s="16" t="s">
-        <x:v>276</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D45" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E45" s="16" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F45" s="16" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="G45" s="16" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="H45" s="18">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I45" s="18">
-        <x:v>46097</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J45" s="17" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K45" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="20">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M45" s="16" t="s">
         <x:v>84</x:v>
@@ -5937,34 +5949,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="16" t="s">
-        <x:v>276</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D46" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="16" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="F46" s="16" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="G46" s="16" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="H46" s="18">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I46" s="18">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J46" s="17" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K46" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="20">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M46" s="16" t="s">
         <x:v>84</x:v>
@@ -5972,10 +5984,10 @@
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B47" s="16" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C47" s="16" t="s">
-        <x:v>313</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D47" s="17" t="s">
         <x:v>53</x:v>
@@ -5990,19 +6002,19 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="H47" s="18">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I47" s="18">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J47" s="17" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K47" s="19" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="20">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M47" s="16" t="s">
         <x:v>84</x:v>
@@ -6028,22 +6040,22 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="H48" s="18">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46098.2908796296</x:v>
       </x:c>
       <x:c r="I48" s="18">
-        <x:v>46094</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J48" s="17" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511858</x:v>
       </x:c>
       <x:c r="K48" s="19" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L48" s="20">
-        <x:v>46093.3109375</x:v>
+        <x:v>46098.3188657407</x:v>
       </x:c>
       <x:c r="M48" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
@@ -6066,60 +6078,87 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="H49" s="18">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I49" s="18">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J49" s="17" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K49" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L49" s="20">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M49" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B50" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C50" s="16" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="D50" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E50" s="16" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F50" s="16" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="G50" s="16" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="H50" s="18">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I50" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J50" s="17" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K50" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L50" s="20">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M49" s="16" t="s">
+      <x:c r="M50" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B52" s="21" t="s">
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="21" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C52" s="22" t="s"/>
-      <x:c r="D52" s="22" t="s"/>
-      <x:c r="E52" s="23" t="s"/>
-      <x:c r="F52" s="23" t="s"/>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B53" s="24" t="s">
+      <x:c r="C53" s="22" t="s"/>
+      <x:c r="D53" s="22" t="s"/>
+      <x:c r="E53" s="23" t="s"/>
+      <x:c r="F53" s="23" t="s"/>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B54" s="24" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C53" s="25" t="s"/>
-      <x:c r="D53" s="25" t="s"/>
-      <x:c r="E53" s="25" t="s"/>
-      <x:c r="F53" s="26" t="s">
+      <x:c r="C54" s="25" t="s"/>
+      <x:c r="D54" s="25" t="s"/>
+      <x:c r="E54" s="25" t="s"/>
+      <x:c r="F54" s="26" t="s">
         <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
       <x:c r="B55" s="27" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="28" t="s"/>
       <x:c r="D55" s="28" t="s"/>
@@ -6130,60 +6169,70 @@
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
       <x:c r="B56" s="27" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C56" s="28" t="s"/>
       <x:c r="D56" s="28" t="s"/>
       <x:c r="E56" s="28" t="s"/>
       <x:c r="F56" s="29" t="n">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
       <x:c r="B57" s="27" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C57" s="28" t="s"/>
       <x:c r="D57" s="28" t="s"/>
       <x:c r="E57" s="28" t="s"/>
       <x:c r="F57" s="29" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="27" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C58" s="28" t="s"/>
       <x:c r="D58" s="28" t="s"/>
       <x:c r="E58" s="28" t="s"/>
       <x:c r="F58" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="18" customHeight="1">
       <x:c r="B59" s="27" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C59" s="28" t="s"/>
       <x:c r="D59" s="28" t="s"/>
       <x:c r="E59" s="28" t="s"/>
       <x:c r="F59" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B60" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C60" s="28" t="s"/>
+      <x:c r="D60" s="28" t="s"/>
+      <x:c r="E60" s="28" t="s"/>
+      <x:c r="F60" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B60" s="30" t="s">
+    <x:row r="61" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B61" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="C60" s="31" t="s"/>
-      <x:c r="D60" s="31" t="s"/>
-      <x:c r="E60" s="31" t="s"/>
-      <x:c r="F60" s="32" t="n">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C61" s="31" t="s"/>
+      <x:c r="D61" s="31" t="s"/>
+      <x:c r="E61" s="31" t="s"/>
+      <x:c r="F61" s="32" t="n">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7121,8 +7170,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B52:F52"/>
-    <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B53:F53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
@@ -7130,6 +7178,7 @@
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
     <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B61:E61"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -697,6 +697,24 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -706,15 +724,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -724,15 +733,6 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -781,6 +781,18 @@
     <x:t>43A-3-2026-1159-651</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBILECRAZE TELECOM INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NO. 6 PUREGOLD BLDG. SAN PABLO COLAGO AVE, SAN ROQUE, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1113-757</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -889,6 +901,15 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -896,15 +917,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
@@ -5014,19 +5026,19 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H21" s="18">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>46133</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J21" s="17" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M21" s="16" t="s">
         <x:v>190</x:v>
@@ -5090,19 +5102,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H23" s="18">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J23" s="17" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M23" s="16" t="s">
         <x:v>190</x:v>
@@ -5128,19 +5140,19 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="H24" s="18">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46035</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J24" s="17" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M24" s="16" t="s">
         <x:v>190</x:v>
@@ -5318,19 +5330,19 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="H29" s="18">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J29" s="17" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M29" s="16" t="s">
         <x:v>190</x:v>
@@ -5356,19 +5368,19 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="H30" s="18">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J30" s="17" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M30" s="16" t="s">
         <x:v>190</x:v>
@@ -5385,28 +5397,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E31" s="16" t="s">
-        <x:v>249</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F31" s="16" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G31" s="16" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H31" s="18">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I31" s="18">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J31" s="17" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M31" s="16" t="s">
         <x:v>190</x:v>
@@ -5417,13 +5429,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C32" s="16" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D32" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E32" s="16" t="s">
-        <x:v>264</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F32" s="16" t="s">
         <x:v>265</x:v>
@@ -5432,19 +5444,19 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="H32" s="18">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I32" s="18">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J32" s="17" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M32" s="16" t="s">
         <x:v>190</x:v>
@@ -5455,34 +5467,34 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="16" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D33" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E33" s="16" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="F33" s="16" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G33" s="16" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H33" s="18">
-        <x:v>46069.115150463</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I33" s="18">
-        <x:v>46172</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J33" s="17" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K33" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L33" s="20">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M33" s="16" t="s">
         <x:v>190</x:v>
@@ -5493,34 +5505,34 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C34" s="16" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D34" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E34" s="16" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F34" s="16" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G34" s="16" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H34" s="18">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J34" s="17" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M34" s="16" t="s">
         <x:v>190</x:v>
@@ -5531,34 +5543,34 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C35" s="16" t="s">
-        <x:v>69</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D35" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E35" s="16" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="F35" s="16" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="G35" s="16" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="H35" s="18">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I35" s="18">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J35" s="17" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M35" s="16" t="s">
         <x:v>190</x:v>
@@ -5569,7 +5581,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C36" s="16" t="s">
-        <x:v>276</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D36" s="17" t="s">
         <x:v>53</x:v>
@@ -5584,19 +5596,19 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H36" s="18">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I36" s="18">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J36" s="17" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M36" s="16" t="s">
         <x:v>190</x:v>
@@ -5622,33 +5634,33 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="H37" s="18">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I37" s="18">
-        <x:v>46095</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J37" s="17" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M37" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B38" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C38" s="16" t="s">
         <x:v>284</x:v>
       </x:c>
       <x:c r="D38" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E38" s="16" t="s">
         <x:v>285</x:v>
@@ -5660,22 +5672,22 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="H38" s="18">
-        <x:v>46085.16625</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I38" s="18">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J38" s="17" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M38" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -5683,34 +5695,34 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C39" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D39" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E39" s="16" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="F39" s="16" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G39" s="16" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H39" s="18">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I39" s="18">
-        <x:v>46085.1709375</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J39" s="17" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M39" s="16" t="s">
         <x:v>24</x:v>
@@ -5721,19 +5733,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C40" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D40" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E40" s="16" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F40" s="16" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G40" s="16" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H40" s="18">
         <x:v>46085.1627430556</x:v>
@@ -5759,34 +5771,34 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C41" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D41" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E41" s="16" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F41" s="16" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="G41" s="16" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="H41" s="18">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I41" s="18">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J41" s="17" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M41" s="16" t="s">
         <x:v>24</x:v>
@@ -5794,13 +5806,13 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C42" s="16" t="s">
-        <x:v>297</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D42" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E42" s="16" t="s">
         <x:v>298</x:v>
@@ -5812,22 +5824,22 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="H42" s="18">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I42" s="18">
-        <x:v>46145</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J42" s="17" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M42" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
@@ -5835,34 +5847,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C43" s="16" t="s">
-        <x:v>216</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="D43" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E43" s="16" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F43" s="16" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="G43" s="16" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H43" s="18">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I43" s="18">
-        <x:v>46103</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J43" s="17" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K43" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L43" s="20">
-        <x:v>46097.2478125</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M43" s="16" t="s">
         <x:v>190</x:v>
@@ -5873,7 +5885,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C44" s="16" t="s">
-        <x:v>304</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D44" s="17" t="s">
         <x:v>53</x:v>
@@ -5888,22 +5900,22 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="H44" s="18">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I44" s="18">
-        <x:v>46084</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J44" s="17" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K44" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="20">
-        <x:v>46083.104224537</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M44" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -5911,34 +5923,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C45" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="D45" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E45" s="16" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F45" s="16" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="G45" s="16" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="H45" s="18">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I45" s="18">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J45" s="17" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K45" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="20">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M45" s="16" t="s">
         <x:v>84</x:v>
@@ -5949,34 +5961,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D46" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="16" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F46" s="16" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="G46" s="16" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="H46" s="18">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I46" s="18">
-        <x:v>46097</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J46" s="17" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K46" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="20">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M46" s="16" t="s">
         <x:v>84</x:v>
@@ -5987,34 +5999,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C47" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D47" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E47" s="16" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F47" s="16" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G47" s="16" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="H47" s="18">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I47" s="18">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J47" s="17" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K47" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="20">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M47" s="16" t="s">
         <x:v>84</x:v>
@@ -6022,10 +6034,10 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="16" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C48" s="16" t="s">
-        <x:v>317</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D48" s="17" t="s">
         <x:v>53</x:v>
@@ -6040,19 +6052,19 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="H48" s="18">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I48" s="18">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J48" s="17" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K48" s="19" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L48" s="20">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M48" s="16" t="s">
         <x:v>84</x:v>
@@ -6078,22 +6090,22 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="H49" s="18">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46098.2908796296</x:v>
       </x:c>
       <x:c r="I49" s="18">
-        <x:v>46094</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J49" s="17" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511858</x:v>
       </x:c>
       <x:c r="K49" s="19" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L49" s="20">
-        <x:v>46093.3109375</x:v>
+        <x:v>46098.3188657407</x:v>
       </x:c>
       <x:c r="M49" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
@@ -6116,60 +6128,87 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="H50" s="18">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I50" s="18">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J50" s="17" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K50" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L50" s="20">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M50" s="16" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B51" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C51" s="16" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="D51" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E51" s="16" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="F51" s="16" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="G51" s="16" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="H51" s="18">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I51" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J51" s="17" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K51" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L51" s="20">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M50" s="16" t="s">
+      <x:c r="M51" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="21" t="s">
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B54" s="21" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C53" s="22" t="s"/>
-      <x:c r="D53" s="22" t="s"/>
-      <x:c r="E53" s="23" t="s"/>
-      <x:c r="F53" s="23" t="s"/>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B54" s="24" t="s">
+      <x:c r="C54" s="22" t="s"/>
+      <x:c r="D54" s="22" t="s"/>
+      <x:c r="E54" s="23" t="s"/>
+      <x:c r="F54" s="23" t="s"/>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B55" s="24" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C54" s="25" t="s"/>
-      <x:c r="D54" s="25" t="s"/>
-      <x:c r="E54" s="25" t="s"/>
-      <x:c r="F54" s="26" t="s">
+      <x:c r="C55" s="25" t="s"/>
+      <x:c r="D55" s="25" t="s"/>
+      <x:c r="E55" s="25" t="s"/>
+      <x:c r="F55" s="26" t="s">
         <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C55" s="28" t="s"/>
-      <x:c r="D55" s="28" t="s"/>
-      <x:c r="E55" s="28" t="s"/>
-      <x:c r="F55" s="29" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
       <x:c r="B56" s="27" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C56" s="28" t="s"/>
       <x:c r="D56" s="28" t="s"/>
@@ -6180,60 +6219,70 @@
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
       <x:c r="B57" s="27" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C57" s="28" t="s"/>
       <x:c r="D57" s="28" t="s"/>
       <x:c r="E57" s="28" t="s"/>
       <x:c r="F57" s="29" t="n">
-        <x:v>24</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="27" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C58" s="28" t="s"/>
       <x:c r="D58" s="28" t="s"/>
       <x:c r="E58" s="28" t="s"/>
       <x:c r="F58" s="29" t="n">
-        <x:v>4</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="18" customHeight="1">
       <x:c r="B59" s="27" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C59" s="28" t="s"/>
       <x:c r="D59" s="28" t="s"/>
       <x:c r="E59" s="28" t="s"/>
       <x:c r="F59" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="18" customHeight="1">
       <x:c r="B60" s="27" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C60" s="28" t="s"/>
       <x:c r="D60" s="28" t="s"/>
       <x:c r="E60" s="28" t="s"/>
       <x:c r="F60" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B61" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C61" s="28" t="s"/>
+      <x:c r="D61" s="28" t="s"/>
+      <x:c r="E61" s="28" t="s"/>
+      <x:c r="F61" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B61" s="30" t="s">
+    <x:row r="62" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B62" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="C61" s="31" t="s"/>
-      <x:c r="D61" s="31" t="s"/>
-      <x:c r="E61" s="31" t="s"/>
-      <x:c r="F61" s="32" t="n">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C62" s="31" t="s"/>
+      <x:c r="D62" s="31" t="s"/>
+      <x:c r="E62" s="31" t="s"/>
+      <x:c r="F62" s="32" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7170,8 +7219,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B53:F53"/>
-    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B54:F54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
@@ -7179,6 +7227,7 @@
     <x:mergeCell ref="B59:E59"/>
     <x:mergeCell ref="B60:E60"/>
     <x:mergeCell ref="B61:E61"/>
+    <x:mergeCell ref="B62:E62"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -547,6 +547,18 @@
     <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
+    <x:t>ALCALA, GLENN GUIBAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Block 2 Lot 9 Sunridge Ville Phase 1 Isarog Street, Barangay Isabang, City Of Tayabas, Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03011-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1207-652</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -676,6 +688,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -685,18 +706,36 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0762</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1155-834</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
   </x:si>
   <x:si>
@@ -706,33 +745,6 @@
     <x:t>43A-2-2026-1085-453</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -856,6 +868,18 @@
     <x:t>43A-3-2026-1168-173</x:t>
   </x:si>
   <x:si>
+    <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1201-204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -892,6 +916,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06698-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1169-102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -901,15 +943,6 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -919,15 +952,6 @@
     <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
-    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-06698-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1169-102</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -961,6 +985,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -968,24 +1010,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1173-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
     <x:t>CELLBOY INC.</x:t>
@@ -4536,19 +4560,19 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H8" s="14">
-        <x:v>46091.306099537</x:v>
+        <x:v>46100.1144675926</x:v>
       </x:c>
       <x:c r="I8" s="14">
-        <x:v>46091.3107986111</x:v>
+        <x:v>46100.1505092593</x:v>
       </x:c>
       <x:c r="J8" s="13" t="n">
-        <x:v>1511778</x:v>
+        <x:v>1511906</x:v>
       </x:c>
       <x:c r="K8" s="15" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L8" s="14">
-        <x:v>46091.3131828704</x:v>
+        <x:v>46100.1652777778</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
         <x:v>84</x:v>
@@ -4572,19 +4596,19 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="H9" s="14">
-        <x:v>46093.1459375</x:v>
+        <x:v>46091.306099537</x:v>
       </x:c>
       <x:c r="I9" s="14">
-        <x:v>46093.1585185185</x:v>
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J9" s="13" t="n">
-        <x:v>1511815</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K9" s="15" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L9" s="14">
-        <x:v>46093.159537037</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
         <x:v>84</x:v>
@@ -4608,34 +4632,32 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H10" s="18">
-        <x:v>46098.0792592593</x:v>
+        <x:v>46093.1459375</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>46098.0878935185</x:v>
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J10" s="17" t="n">
-        <x:v>1529776</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>130</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46098.0997569444</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M10" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="16" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D11" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
+      <x:c r="D11" s="17" t="s"/>
       <x:c r="E11" s="16" t="s">
         <x:v>187</x:v>
       </x:c>
@@ -4646,22 +4668,22 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="H11" s="18">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46098.0792592593</x:v>
       </x:c>
       <x:c r="I11" s="18">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46098.0878935185</x:v>
       </x:c>
       <x:c r="J11" s="17" t="n">
-        <x:v>1511203</x:v>
+        <x:v>1529776</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46098.0997569444</x:v>
       </x:c>
       <x:c r="M11" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -4669,7 +4691,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>186</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D12" s="17" t="s">
         <x:v>43</x:v>
@@ -4684,10 +4706,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H12" s="18">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J12" s="17" t="n">
         <x:v>1511203</x:v>
@@ -4696,10 +4718,10 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M12" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
@@ -4707,7 +4729,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D13" s="17" t="s">
         <x:v>43</x:v>
@@ -4722,33 +4744,33 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="H13" s="18">
-        <x:v>46090.2109953704</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>46090.2110069444</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J13" s="17" t="n">
-        <x:v>1511204</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46093.3080092593</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M13" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="16" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
         <x:v>198</x:v>
       </x:c>
       <x:c r="D14" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E14" s="16" t="s">
         <x:v>199</x:v>
@@ -4760,22 +4782,22 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H14" s="18">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46090.2109953704</x:v>
       </x:c>
       <x:c r="I14" s="18">
-        <x:v>46100</x:v>
+        <x:v>46090.2110069444</x:v>
       </x:c>
       <x:c r="J14" s="17" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511204</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M14" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -4783,37 +4805,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D15" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E15" s="16" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F15" s="16" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G15" s="16" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H15" s="18">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J15" s="17" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46097.149525463</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M15" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -4821,37 +4843,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D16" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E16" s="16" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F16" s="16" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G16" s="16" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H16" s="18">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J16" s="17" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M16" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -4859,7 +4881,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D17" s="17" t="s">
         <x:v>53</x:v>
@@ -4874,22 +4896,22 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="H17" s="18">
-        <x:v>46083.2599189815</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J17" s="17" t="n">
-        <x:v>1511237</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46097.1652314815</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M17" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -4912,22 +4934,22 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="H18" s="18">
-        <x:v>46069.3514814815</x:v>
+        <x:v>46083.2599189815</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46094</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J18" s="17" t="n">
-        <x:v>1511194</x:v>
+        <x:v>1511237</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46097.1652314815</x:v>
       </x:c>
       <x:c r="M18" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -4950,22 +4972,22 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="H19" s="18">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46069.3514814815</x:v>
       </x:c>
       <x:c r="I19" s="18">
         <x:v>46094</x:v>
       </x:c>
       <x:c r="J19" s="17" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511194</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M19" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -4973,19 +4995,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>216</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D20" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="16" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F20" s="16" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G20" s="16" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H20" s="18">
         <x:v>46084.0854513889</x:v>
@@ -5003,7 +5025,7 @@
         <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M20" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -5011,7 +5033,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>223</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D21" s="17" t="s">
         <x:v>53</x:v>
@@ -5026,22 +5048,22 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H21" s="18">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>46035</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J21" s="17" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M21" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5049,37 +5071,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D22" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E22" s="16" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F22" s="16" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G22" s="16" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H22" s="18">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>46144</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J22" s="17" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M22" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5087,37 +5109,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C23" s="16" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D23" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E23" s="16" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F23" s="16" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G23" s="16" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H23" s="18">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J23" s="17" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M23" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5125,37 +5147,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C24" s="16" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D24" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E24" s="16" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F24" s="16" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G24" s="16" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H24" s="18">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J24" s="17" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M24" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5163,7 +5185,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
-        <x:v>236</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D25" s="17" t="s">
         <x:v>53</x:v>
@@ -5178,22 +5200,22 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H25" s="18">
-        <x:v>46069.2178703704</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I25" s="18">
-        <x:v>46051</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J25" s="17" t="n">
-        <x:v>1511196</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46097.2456365741</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M25" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5216,22 +5238,22 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="H26" s="18">
-        <x:v>46073.125162037</x:v>
+        <x:v>46069.2178703704</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>45619</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J26" s="17" t="n">
-        <x:v>1511246</x:v>
+        <x:v>1511196</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
-        <x:v>11280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46099.1200231481</x:v>
+        <x:v>46097.2456365741</x:v>
       </x:c>
       <x:c r="M26" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5254,22 +5276,22 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H27" s="18">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>46100</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J27" s="17" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M27" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5292,22 +5314,22 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="H28" s="18">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J28" s="17" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M28" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5330,22 +5352,22 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="H29" s="18">
-        <x:v>46073.1541087963</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>46030</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J29" s="17" t="n">
-        <x:v>1511248</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46099.1583912037</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M29" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5368,22 +5390,22 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="H30" s="18">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J30" s="17" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M30" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5406,22 +5428,22 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="H31" s="18">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I31" s="18">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J31" s="17" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M31" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5435,31 +5457,31 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E32" s="16" t="s">
-        <x:v>249</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F32" s="16" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G32" s="16" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H32" s="18">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I32" s="18">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J32" s="17" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M32" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5467,13 +5489,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="16" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D33" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E33" s="16" t="s">
-        <x:v>268</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="F33" s="16" t="s">
         <x:v>269</x:v>
@@ -5482,22 +5504,22 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="H33" s="18">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I33" s="18">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J33" s="17" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K33" s="19" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="20">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M33" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5505,37 +5527,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C34" s="16" t="s">
-        <x:v>267</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D34" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E34" s="16" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F34" s="16" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G34" s="16" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="H34" s="18">
-        <x:v>46069.115150463</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>46172</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J34" s="17" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M34" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5543,37 +5565,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C35" s="16" t="s">
-        <x:v>267</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D35" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E35" s="16" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F35" s="16" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G35" s="16" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="H35" s="18">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I35" s="18">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J35" s="17" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M35" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -5581,37 +5603,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C36" s="16" t="s">
-        <x:v>69</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D36" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E36" s="16" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F36" s="16" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G36" s="16" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="H36" s="18">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I36" s="18">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J36" s="17" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M36" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -5619,7 +5641,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C37" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D37" s="17" t="s">
         <x:v>53</x:v>
@@ -5634,22 +5656,22 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="H37" s="18">
-        <x:v>46069.121724537</x:v>
+        <x:v>46097.4214930556</x:v>
       </x:c>
       <x:c r="I37" s="18">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J37" s="17" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511270</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46097.3375</x:v>
+        <x:v>46100.2966666667</x:v>
       </x:c>
       <x:c r="M37" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5657,7 +5679,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C38" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D38" s="17" t="s">
         <x:v>53</x:v>
@@ -5672,33 +5694,33 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="H38" s="18">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I38" s="18">
-        <x:v>46095</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J38" s="17" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M38" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B39" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C39" s="16" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="D39" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E39" s="16" t="s">
         <x:v>289</x:v>
@@ -5710,60 +5732,60 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="H39" s="18">
-        <x:v>46085.16625</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I39" s="18">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J39" s="17" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M39" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B40" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C40" s="16" t="s">
-        <x:v>288</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D40" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E40" s="16" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F40" s="16" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G40" s="16" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H40" s="18">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I40" s="18">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J40" s="17" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M40" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
@@ -5771,34 +5793,34 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C41" s="16" t="s">
-        <x:v>288</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D41" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E41" s="16" t="s">
-        <x:v>295</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="F41" s="16" t="s">
-        <x:v>296</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="G41" s="16" t="s">
-        <x:v>297</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="H41" s="18">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I41" s="18">
-        <x:v>46085.1709375</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J41" s="17" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M41" s="16" t="s">
         <x:v>24</x:v>
@@ -5809,34 +5831,34 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C42" s="16" t="s">
-        <x:v>288</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D42" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E42" s="16" t="s">
-        <x:v>298</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F42" s="16" t="s">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="G42" s="16" t="s">
-        <x:v>300</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="H42" s="18">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I42" s="18">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J42" s="17" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M42" s="16" t="s">
         <x:v>24</x:v>
@@ -5844,78 +5866,78 @@
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B43" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C43" s="16" t="s">
-        <x:v>301</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D43" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E43" s="16" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F43" s="16" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="G43" s="16" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="H43" s="18">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I43" s="18">
-        <x:v>46145</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J43" s="17" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K43" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L43" s="20">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M43" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B44" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C44" s="16" t="s">
-        <x:v>216</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D44" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E44" s="16" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F44" s="16" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="G44" s="16" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="H44" s="18">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I44" s="18">
-        <x:v>46103</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J44" s="17" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K44" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L44" s="20">
-        <x:v>46097.2478125</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M44" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -5923,37 +5945,37 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C45" s="16" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="D45" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E45" s="16" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F45" s="16" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="G45" s="16" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="H45" s="18">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I45" s="18">
-        <x:v>46084</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J45" s="17" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K45" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="20">
-        <x:v>46083.104224537</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M45" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
@@ -5961,37 +5983,37 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D46" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="16" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F46" s="16" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="G46" s="16" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="H46" s="18">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I46" s="18">
-        <x:v>46098</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J46" s="17" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K46" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="20">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M46" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
@@ -5999,34 +6021,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C47" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="D47" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E47" s="16" t="s">
-        <x:v>315</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="F47" s="16" t="s">
-        <x:v>316</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="G47" s="16" t="s">
-        <x:v>317</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="H47" s="18">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I47" s="18">
-        <x:v>46097</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J47" s="17" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K47" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="20">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M47" s="16" t="s">
         <x:v>84</x:v>
@@ -6037,34 +6059,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C48" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D48" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E48" s="16" t="s">
-        <x:v>318</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F48" s="16" t="s">
-        <x:v>319</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="G48" s="16" t="s">
-        <x:v>320</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="H48" s="18">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I48" s="18">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J48" s="17" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K48" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L48" s="20">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M48" s="16" t="s">
         <x:v>84</x:v>
@@ -6072,37 +6094,37 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B49" s="16" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C49" s="16" t="s">
-        <x:v>321</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D49" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E49" s="16" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F49" s="16" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="G49" s="16" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="H49" s="18">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I49" s="18">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J49" s="17" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K49" s="19" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L49" s="20">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M49" s="16" t="s">
         <x:v>84</x:v>
@@ -6110,10 +6132,10 @@
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B50" s="16" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C50" s="16" t="s">
-        <x:v>325</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D50" s="17" t="s">
         <x:v>53</x:v>
@@ -6128,22 +6150,22 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="H50" s="18">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I50" s="18">
-        <x:v>46094</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J50" s="17" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K50" s="19" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L50" s="20">
-        <x:v>46093.3109375</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M50" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
@@ -6166,125 +6188,199 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="H51" s="18">
+        <x:v>46098.2908796296</x:v>
+      </x:c>
+      <x:c r="I51" s="18">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J51" s="17" t="n">
+        <x:v>1511858</x:v>
+      </x:c>
+      <x:c r="K51" s="19" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L51" s="20">
+        <x:v>46098.3188657407</x:v>
+      </x:c>
+      <x:c r="M51" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B52" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C52" s="16" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="D52" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E52" s="16" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="F52" s="16" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="G52" s="16" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="H52" s="18">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I52" s="18">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J52" s="17" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K52" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L52" s="20">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M52" s="16" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B53" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C53" s="16" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="D53" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E53" s="16" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="F53" s="16" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="G53" s="16" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="H53" s="18">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I51" s="18">
+      <x:c r="I53" s="18">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J51" s="17" t="n">
+      <x:c r="J53" s="17" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K51" s="19" t="n">
+      <x:c r="K53" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L51" s="20">
+      <x:c r="L53" s="20">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M51" s="16" t="s">
+      <x:c r="M53" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="21" t="s">
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B56" s="21" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C54" s="22" t="s"/>
-      <x:c r="D54" s="22" t="s"/>
-      <x:c r="E54" s="23" t="s"/>
-      <x:c r="F54" s="23" t="s"/>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B55" s="24" t="s">
+      <x:c r="C56" s="22" t="s"/>
+      <x:c r="D56" s="22" t="s"/>
+      <x:c r="E56" s="23" t="s"/>
+      <x:c r="F56" s="23" t="s"/>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B57" s="24" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C55" s="25" t="s"/>
-      <x:c r="D55" s="25" t="s"/>
-      <x:c r="E55" s="25" t="s"/>
-      <x:c r="F55" s="26" t="s">
+      <x:c r="C57" s="25" t="s"/>
+      <x:c r="D57" s="25" t="s"/>
+      <x:c r="E57" s="25" t="s"/>
+      <x:c r="F57" s="26" t="s">
         <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C56" s="28" t="s"/>
-      <x:c r="D56" s="28" t="s"/>
-      <x:c r="E56" s="28" t="s"/>
-      <x:c r="F56" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C57" s="28" t="s"/>
-      <x:c r="D57" s="28" t="s"/>
-      <x:c r="E57" s="28" t="s"/>
-      <x:c r="F57" s="29" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="27" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C58" s="28" t="s"/>
       <x:c r="D58" s="28" t="s"/>
       <x:c r="E58" s="28" t="s"/>
       <x:c r="F58" s="29" t="n">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="18" customHeight="1">
       <x:c r="B59" s="27" t="s">
-        <x:v>79</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C59" s="28" t="s"/>
       <x:c r="D59" s="28" t="s"/>
       <x:c r="E59" s="28" t="s"/>
       <x:c r="F59" s="29" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="18" customHeight="1">
       <x:c r="B60" s="27" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C60" s="28" t="s"/>
       <x:c r="D60" s="28" t="s"/>
       <x:c r="E60" s="28" t="s"/>
       <x:c r="F60" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:28" ht="18" customHeight="1">
       <x:c r="B61" s="27" t="s">
-        <x:v>143</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C61" s="28" t="s"/>
       <x:c r="D61" s="28" t="s"/>
       <x:c r="E61" s="28" t="s"/>
       <x:c r="F61" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B62" s="27" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C62" s="28" t="s"/>
+      <x:c r="D62" s="28" t="s"/>
+      <x:c r="E62" s="28" t="s"/>
+      <x:c r="F62" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B63" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C63" s="28" t="s"/>
+      <x:c r="D63" s="28" t="s"/>
+      <x:c r="E63" s="28" t="s"/>
+      <x:c r="F63" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B62" s="30" t="s">
+    <x:row r="64" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B64" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="C62" s="31" t="s"/>
-      <x:c r="D62" s="31" t="s"/>
-      <x:c r="E62" s="31" t="s"/>
-      <x:c r="F62" s="32" t="n">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C64" s="31" t="s"/>
+      <x:c r="D64" s="31" t="s"/>
+      <x:c r="E64" s="31" t="s"/>
+      <x:c r="F64" s="32" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
     <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7219,15 +7315,15 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B54:F54"/>
-    <x:mergeCell ref="B55:E55"/>
-    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B56:F56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
     <x:mergeCell ref="B60:E60"/>
     <x:mergeCell ref="B61:E61"/>
     <x:mergeCell ref="B62:E62"/>
+    <x:mergeCell ref="B63:E63"/>
+    <x:mergeCell ref="B64:E64"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="366">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -559,6 +559,24 @@
     <x:t>43A-3-2026-1207-652</x:t>
   </x:si>
   <x:si>
+    <x:t>CHRISTOPHER I. PALLESCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Block 3 Lot 12 Phase 1 Lavanya Subdivision, Bacao 2, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03055C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1210-786</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-02054C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1209-851</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -598,6 +616,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -607,18 +637,6 @@
     <x:t>43A-3-2026-1179-857</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06915-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1178-478</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -676,6 +694,18 @@
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>LG05 SM MARKETMALL, BUROL I, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-010R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1089-192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -718,6 +748,33 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1111-408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -727,24 +784,6 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -760,6 +799,15 @@
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CENTER ILLUSTRE AVE, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1097-702</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -817,6 +865,18 @@
     <x:t>43A-3-2026-1153-796</x:t>
   </x:si>
   <x:si>
+    <x:t>PHONEVILLE MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sm City Taytay Manila East Road Sm City Taytay Manila East Road, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1202-217</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -877,9 +937,6 @@
     <x:t>43A-3-2026-1201-204</x:t>
   </x:si>
   <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -901,6 +958,15 @@
     <x:t>43A-2-2026-1084-395</x:t>
   </x:si>
   <x:si>
+    <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-20-01-0883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1087-228</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -983,6 +1049,15 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1146-031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-02-2011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1163-392</x:t>
   </x:si>
   <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
@@ -4596,22 +4671,22 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="H9" s="14">
-        <x:v>46091.306099537</x:v>
+        <x:v>46100.3734490741</x:v>
       </x:c>
       <x:c r="I9" s="14">
-        <x:v>46091.3107986111</x:v>
+        <x:v>46100.388599537</x:v>
       </x:c>
       <x:c r="J9" s="13" t="n">
-        <x:v>1511778</x:v>
+        <x:v>1529812</x:v>
       </x:c>
       <x:c r="K9" s="15" t="n">
-        <x:v>230</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="14">
-        <x:v>46091.3131828704</x:v>
+        <x:v>46100.3957175926</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
@@ -4619,35 +4694,35 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>182</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D10" s="17" t="s"/>
       <x:c r="E10" s="16" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>185</x:v>
-      </x:c>
       <x:c r="H10" s="18">
-        <x:v>46093.1459375</x:v>
+        <x:v>46100.365787037</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>46093.1585185185</x:v>
+        <x:v>46100.3731712963</x:v>
       </x:c>
       <x:c r="J10" s="17" t="n">
-        <x:v>1511815</x:v>
+        <x:v>1529809</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>230</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46093.159537037</x:v>
+        <x:v>46100.3868981482</x:v>
       </x:c>
       <x:c r="M10" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -4655,111 +4730,107 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>186</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D11" s="17" t="s"/>
       <x:c r="E11" s="16" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>189</x:v>
-      </x:c>
       <x:c r="H11" s="18">
-        <x:v>46098.0792592593</x:v>
+        <x:v>46091.306099537</x:v>
       </x:c>
       <x:c r="I11" s="18">
-        <x:v>46098.0878935185</x:v>
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J11" s="17" t="n">
-        <x:v>1529776</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
-        <x:v>130</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46098.0997569444</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M11" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="16" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="16" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D12" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E12" s="16" t="s">
+      <x:c r="G12" s="16" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>193</x:v>
-      </x:c>
       <x:c r="H12" s="18">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46093.1459375</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J12" s="17" t="n">
-        <x:v>1511203</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M12" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="16" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="s"/>
       <x:c r="E13" s="16" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>197</x:v>
-      </x:c>
       <x:c r="H13" s="18">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46098.0792592593</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46098.0878935185</x:v>
       </x:c>
       <x:c r="J13" s="17" t="n">
-        <x:v>1511203</x:v>
+        <x:v>1529776</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46098.0997569444</x:v>
       </x:c>
       <x:c r="M13" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
@@ -4767,113 +4838,113 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D14" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E14" s="16" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>201</x:v>
-      </x:c>
       <x:c r="H14" s="18">
-        <x:v>46090.2109953704</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I14" s="18">
-        <x:v>46090.2110069444</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J14" s="17" t="n">
-        <x:v>1511204</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46093.3080092593</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M14" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="16" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D15" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="s">
+      <x:c r="G15" s="16" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>205</x:v>
-      </x:c>
       <x:c r="H15" s="18">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46100</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J15" s="17" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M15" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="16" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D16" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E16" s="16" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="F16" s="16" t="s">
+      <x:c r="G16" s="16" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>208</x:v>
-      </x:c>
       <x:c r="H16" s="18">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46090.2109953704</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46112</x:v>
+        <x:v>46090.2110069444</x:v>
       </x:c>
       <x:c r="J16" s="17" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511204</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46097.149525463</x:v>
+        <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M16" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -4881,7 +4952,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>202</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D17" s="17" t="s">
         <x:v>53</x:v>
@@ -4896,22 +4967,22 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="H17" s="18">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I17" s="18">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J17" s="17" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M17" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -4919,37 +4990,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
-        <x:v>212</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D18" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E18" s="16" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="F18" s="16" t="s">
+      <x:c r="G18" s="16" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>215</x:v>
-      </x:c>
       <x:c r="H18" s="18">
-        <x:v>46083.2599189815</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46101</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J18" s="17" t="n">
-        <x:v>1511237</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46097.1652314815</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M18" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -4957,37 +5028,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C19" s="16" t="s">
-        <x:v>216</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D19" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E19" s="16" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>219</x:v>
-      </x:c>
       <x:c r="H19" s="18">
-        <x:v>46069.3514814815</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J19" s="17" t="n">
-        <x:v>1511194</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M19" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -4995,37 +5066,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D20" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="16" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>223</x:v>
-      </x:c>
       <x:c r="H20" s="18">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46083.2599189815</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>46144</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J20" s="17" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511237</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46097.1652314815</x:v>
       </x:c>
       <x:c r="M20" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -5033,37 +5104,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D21" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E21" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="F21" s="16" t="s">
+      <x:c r="G21" s="16" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="G21" s="16" t="s">
+      <x:c r="H21" s="18">
+        <x:v>46069.2785648148</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:v>1511276</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46100.3884027778</x:v>
+      </x:c>
+      <x:c r="M21" s="16" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I21" s="18">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="20">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5071,37 +5142,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>227</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D22" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E22" s="16" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="F22" s="16" t="s">
+      <x:c r="G22" s="16" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G22" s="16" t="s">
-        <x:v>230</x:v>
-      </x:c>
       <x:c r="H22" s="18">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46069.3514814815</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J22" s="17" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511194</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M22" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5109,7 +5180,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C23" s="16" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D23" s="17" t="s">
         <x:v>53</x:v>
@@ -5124,22 +5195,22 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H23" s="18">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I23" s="18">
         <x:v>46144</x:v>
       </x:c>
       <x:c r="J23" s="17" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M23" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5147,7 +5218,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C24" s="16" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D24" s="17" t="s">
         <x:v>53</x:v>
@@ -5162,22 +5233,22 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="H24" s="18">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46133</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J24" s="17" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M24" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5185,37 +5256,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
-        <x:v>227</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D25" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E25" s="16" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F25" s="16" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G25" s="16" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H25" s="18">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I25" s="18">
-        <x:v>46035</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J25" s="17" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M25" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5223,7 +5294,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="16" t="s">
-        <x:v>240</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D26" s="17" t="s">
         <x:v>53</x:v>
@@ -5238,22 +5309,22 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="H26" s="18">
-        <x:v>46069.2178703704</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>46051</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J26" s="17" t="n">
-        <x:v>1511196</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46097.2456365741</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M26" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5261,37 +5332,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C27" s="16" t="s">
-        <x:v>244</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D27" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E27" s="16" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="F27" s="16" t="s">
+      <x:c r="G27" s="16" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G27" s="16" t="s">
-        <x:v>247</x:v>
-      </x:c>
       <x:c r="H27" s="18">
-        <x:v>46073.125162037</x:v>
+        <x:v>46073.1441087963</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>45619</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J27" s="17" t="n">
-        <x:v>1511246</x:v>
+        <x:v>1511278</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
-        <x:v>11280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46099.1200231481</x:v>
+        <x:v>46100.4005439815</x:v>
       </x:c>
       <x:c r="M27" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5299,37 +5370,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C28" s="16" t="s">
-        <x:v>248</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D28" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E28" s="16" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F28" s="16" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="F28" s="16" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G28" s="16" t="s">
-        <x:v>251</x:v>
-      </x:c>
       <x:c r="H28" s="18">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J28" s="17" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M28" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5337,37 +5408,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C29" s="16" t="s">
-        <x:v>252</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D29" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E29" s="16" t="s">
-        <x:v>253</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F29" s="16" t="s">
-        <x:v>254</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G29" s="16" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H29" s="18">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>46172</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J29" s="17" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M29" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5375,37 +5446,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C30" s="16" t="s">
-        <x:v>256</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D30" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E30" s="16" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F30" s="16" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G30" s="16" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="H30" s="18">
-        <x:v>46073.1541087963</x:v>
+        <x:v>46069.2178703704</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>46030</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J30" s="17" t="n">
-        <x:v>1511248</x:v>
+        <x:v>1511196</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46099.1583912037</x:v>
+        <x:v>46097.2456365741</x:v>
       </x:c>
       <x:c r="M30" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5413,37 +5484,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C31" s="16" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D31" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E31" s="16" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F31" s="16" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G31" s="16" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H31" s="18">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46069.3717592593</x:v>
       </x:c>
       <x:c r="I31" s="18">
-        <x:v>46100</x:v>
+        <x:v>46066</x:v>
       </x:c>
       <x:c r="J31" s="17" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511274</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46100.3754861111</x:v>
       </x:c>
       <x:c r="M31" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5451,37 +5522,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C32" s="16" t="s">
-        <x:v>264</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D32" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E32" s="16" t="s">
-        <x:v>265</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F32" s="16" t="s">
-        <x:v>266</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G32" s="16" t="s">
-        <x:v>267</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H32" s="18">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I32" s="18">
-        <x:v>46094</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J32" s="17" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M32" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5489,37 +5560,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="16" t="s">
-        <x:v>268</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D33" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E33" s="16" t="s">
-        <x:v>253</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F33" s="16" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G33" s="16" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H33" s="18">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I33" s="18">
-        <x:v>46102</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J33" s="17" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K33" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="20">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M33" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5527,37 +5598,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C34" s="16" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D34" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E34" s="16" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F34" s="16" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G34" s="16" t="s">
-        <x:v>274</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="H34" s="18">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>45751</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J34" s="17" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M34" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5565,37 +5636,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C35" s="16" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D35" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E35" s="16" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F35" s="16" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="F35" s="16" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="G35" s="16" t="s">
-        <x:v>277</x:v>
-      </x:c>
       <x:c r="H35" s="18">
-        <x:v>46069.115150463</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I35" s="18">
-        <x:v>46172</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J35" s="17" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M35" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -5603,37 +5674,37 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C36" s="16" t="s">
-        <x:v>271</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D36" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E36" s="16" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F36" s="16" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="F36" s="16" t="s">
+      <x:c r="G36" s="16" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="G36" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
       <x:c r="H36" s="18">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I36" s="18">
-        <x:v>46070</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J36" s="17" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M36" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -5641,7 +5712,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C37" s="16" t="s">
-        <x:v>69</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D37" s="17" t="s">
         <x:v>53</x:v>
@@ -5656,22 +5727,22 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="H37" s="18">
-        <x:v>46097.4214930556</x:v>
+        <x:v>46097.4788425926</x:v>
       </x:c>
       <x:c r="I37" s="18">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J37" s="17" t="n">
-        <x:v>1511270</x:v>
+        <x:v>1511271</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46100.2966666667</x:v>
+        <x:v>46100.29875</x:v>
       </x:c>
       <x:c r="M37" s="16" t="s">
-        <x:v>284</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5679,7 +5750,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C38" s="16" t="s">
-        <x:v>69</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D38" s="17" t="s">
         <x:v>53</x:v>
@@ -5694,22 +5765,22 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="H38" s="18">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I38" s="18">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J38" s="17" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M38" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -5723,31 +5794,31 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E39" s="16" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F39" s="16" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="F39" s="16" t="s">
+      <x:c r="G39" s="16" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="G39" s="16" t="s">
-        <x:v>291</x:v>
-      </x:c>
       <x:c r="H39" s="18">
-        <x:v>46069.121724537</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I39" s="18">
-        <x:v>46157</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J39" s="17" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M39" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
@@ -5755,300 +5826,300 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C40" s="16" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D40" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E40" s="16" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F40" s="16" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="F40" s="16" t="s">
+      <x:c r="G40" s="16" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="G40" s="16" t="s">
-        <x:v>295</x:v>
-      </x:c>
       <x:c r="H40" s="18">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I40" s="18">
-        <x:v>46095</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J40" s="17" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M40" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C41" s="16" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E41" s="16" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F41" s="16" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="D41" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E41" s="16" t="s">
+      <x:c r="G41" s="16" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="F41" s="16" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="G41" s="16" t="s">
-        <x:v>299</x:v>
-      </x:c>
       <x:c r="H41" s="18">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I41" s="18">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J41" s="17" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M41" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C42" s="16" t="s">
-        <x:v>296</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D42" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E42" s="16" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="F42" s="16" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="F42" s="16" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="G42" s="16" t="s">
-        <x:v>302</x:v>
-      </x:c>
       <x:c r="H42" s="18">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I42" s="18">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J42" s="17" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M42" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B43" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C43" s="16" t="s">
-        <x:v>296</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D43" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E43" s="16" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F43" s="16" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="F43" s="16" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="G43" s="16" t="s">
-        <x:v>305</x:v>
-      </x:c>
       <x:c r="H43" s="18">
-        <x:v>46085.16625</x:v>
+        <x:v>46097.4214930556</x:v>
       </x:c>
       <x:c r="I43" s="18">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J43" s="17" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511270</x:v>
       </x:c>
       <x:c r="K43" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L43" s="20">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46100.2966666667</x:v>
       </x:c>
       <x:c r="M43" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B44" s="16" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="16" t="s">
-        <x:v>296</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D44" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E44" s="16" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F44" s="16" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="F44" s="16" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="G44" s="16" t="s">
-        <x:v>308</x:v>
-      </x:c>
       <x:c r="H44" s="18">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I44" s="18">
-        <x:v>46085.1709375</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J44" s="17" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K44" s="19" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="20">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M44" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B45" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C45" s="16" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D45" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E45" s="16" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F45" s="16" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G45" s="16" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="F45" s="16" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="G45" s="16" t="s">
-        <x:v>312</x:v>
-      </x:c>
       <x:c r="H45" s="18">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I45" s="18">
-        <x:v>46145</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J45" s="17" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K45" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="20">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M45" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B46" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C46" s="16" t="s">
-        <x:v>220</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D46" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="16" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="F46" s="16" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="F46" s="16" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="G46" s="16" t="s">
-        <x:v>315</x:v>
-      </x:c>
       <x:c r="H46" s="18">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46069.2327893519</x:v>
       </x:c>
       <x:c r="I46" s="18">
-        <x:v>46103</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J46" s="17" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1511275</x:v>
       </x:c>
       <x:c r="K46" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L46" s="20">
-        <x:v>46097.2478125</x:v>
+        <x:v>46100.3816782407</x:v>
       </x:c>
       <x:c r="M46" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B47" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C47" s="16" t="s">
-        <x:v>316</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="D47" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E47" s="16" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="F47" s="16" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="F47" s="16" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="G47" s="16" t="s">
-        <x:v>319</x:v>
-      </x:c>
       <x:c r="H47" s="18">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I47" s="18">
-        <x:v>46084</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J47" s="17" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K47" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="20">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M47" s="16" t="s">
         <x:v>84</x:v>
@@ -6056,339 +6127,635 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C48" s="16" t="s">
-        <x:v>292</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D48" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E48" s="16" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="F48" s="16" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="F48" s="16" t="s">
+      <x:c r="G48" s="16" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="G48" s="16" t="s">
-        <x:v>322</x:v>
-      </x:c>
       <x:c r="H48" s="18">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I48" s="18">
-        <x:v>46097</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J48" s="17" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K48" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L48" s="20">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M48" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B49" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C49" s="16" t="s">
-        <x:v>292</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D49" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E49" s="16" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F49" s="16" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="F49" s="16" t="s">
+      <x:c r="G49" s="16" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="G49" s="16" t="s">
-        <x:v>325</x:v>
-      </x:c>
       <x:c r="H49" s="18">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I49" s="18">
-        <x:v>46104</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J49" s="17" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K49" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L49" s="20">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M49" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B50" s="16" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C50" s="16" t="s">
-        <x:v>292</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D50" s="17" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E50" s="16" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="F50" s="16" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="F50" s="16" t="s">
+      <x:c r="G50" s="16" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="G50" s="16" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="H50" s="18">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I50" s="18">
-        <x:v>46098</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J50" s="17" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K50" s="19" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L50" s="20">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M50" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B51" s="16" t="s">
-        <x:v>143</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C51" s="16" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="D51" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E51" s="16" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="F51" s="16" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="D51" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E51" s="16" t="s">
+      <x:c r="G51" s="16" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="F51" s="16" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="G51" s="16" t="s">
-        <x:v>332</x:v>
-      </x:c>
       <x:c r="H51" s="18">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I51" s="18">
-        <x:v>45997</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J51" s="17" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K51" s="19" t="n">
-        <x:v>2550</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L51" s="20">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M51" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B52" s="16" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C52" s="16" t="s">
-        <x:v>333</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="D52" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E52" s="16" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="F52" s="16" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="G52" s="16" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="F52" s="16" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="G52" s="16" t="s">
-        <x:v>336</x:v>
-      </x:c>
       <x:c r="H52" s="18">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I52" s="18">
-        <x:v>46094</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J52" s="17" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K52" s="19" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L52" s="20">
-        <x:v>46093.3109375</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M52" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B53" s="16" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C53" s="16" t="s">
-        <x:v>337</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D53" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E53" s="16" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F53" s="16" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="G53" s="16" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="H53" s="18">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I53" s="18">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J53" s="17" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K53" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L53" s="20">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M53" s="16" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B54" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C54" s="16" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="F53" s="16" t="s">
+      <x:c r="D54" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E54" s="16" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="G53" s="16" t="s">
+      <x:c r="F54" s="16" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="H53" s="18">
+      <x:c r="G54" s="16" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="H54" s="18">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I54" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J54" s="17" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K54" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L54" s="20">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M54" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B55" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C55" s="16" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D55" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E55" s="16" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="F55" s="16" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="G55" s="16" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="H55" s="18">
+        <x:v>46084.1627430556</x:v>
+      </x:c>
+      <x:c r="I55" s="18">
+        <x:v>46060</x:v>
+      </x:c>
+      <x:c r="J55" s="17" t="n">
+        <x:v>1511277</x:v>
+      </x:c>
+      <x:c r="K55" s="19" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L55" s="20">
+        <x:v>46100.3929282407</x:v>
+      </x:c>
+      <x:c r="M55" s="16" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B56" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C56" s="16" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D56" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E56" s="16" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="F56" s="16" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="H56" s="18">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I56" s="18">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J56" s="17" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K56" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L56" s="20">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M56" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B57" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C57" s="16" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D57" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E57" s="16" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="F57" s="16" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="G57" s="16" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="H57" s="18">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I57" s="18">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J57" s="17" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K57" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L57" s="20">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M57" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B58" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C58" s="16" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D58" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E58" s="16" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="F58" s="16" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="G58" s="16" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="H58" s="18">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I58" s="18">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J58" s="17" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K58" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L58" s="20">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M58" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B59" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="D59" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E59" s="16" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F59" s="16" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="G59" s="16" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="H59" s="18">
+        <x:v>46098.2908796296</x:v>
+      </x:c>
+      <x:c r="I59" s="18">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J59" s="17" t="n">
+        <x:v>1511858</x:v>
+      </x:c>
+      <x:c r="K59" s="19" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L59" s="20">
+        <x:v>46098.3188657407</x:v>
+      </x:c>
+      <x:c r="M59" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B60" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C60" s="16" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="D60" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E60" s="16" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="F60" s="16" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="G60" s="16" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="H60" s="18">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I60" s="18">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J60" s="17" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K60" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L60" s="20">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M60" s="16" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B61" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C61" s="16" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="D61" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E61" s="16" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="F61" s="16" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="G61" s="16" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="H61" s="18">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I53" s="18">
+      <x:c r="I61" s="18">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J53" s="17" t="n">
+      <x:c r="J61" s="17" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K53" s="19" t="n">
+      <x:c r="K61" s="19" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L53" s="20">
+      <x:c r="L61" s="20">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M53" s="16" t="s">
+      <x:c r="M61" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B56" s="21" t="s">
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B64" s="21" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C56" s="22" t="s"/>
-      <x:c r="D56" s="22" t="s"/>
-      <x:c r="E56" s="23" t="s"/>
-      <x:c r="F56" s="23" t="s"/>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B57" s="24" t="s">
+      <x:c r="C64" s="22" t="s"/>
+      <x:c r="D64" s="22" t="s"/>
+      <x:c r="E64" s="23" t="s"/>
+      <x:c r="F64" s="23" t="s"/>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B65" s="24" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C57" s="25" t="s"/>
-      <x:c r="D57" s="25" t="s"/>
-      <x:c r="E57" s="25" t="s"/>
-      <x:c r="F57" s="26" t="s">
+      <x:c r="C65" s="25" t="s"/>
+      <x:c r="D65" s="25" t="s"/>
+      <x:c r="E65" s="25" t="s"/>
+      <x:c r="F65" s="26" t="s">
         <x:v>171</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="27" t="s">
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="27" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C58" s="28" t="s"/>
-      <x:c r="D58" s="28" t="s"/>
-      <x:c r="E58" s="28" t="s"/>
-      <x:c r="F58" s="29" t="n">
+      <x:c r="C66" s="28" t="s"/>
+      <x:c r="D66" s="28" t="s"/>
+      <x:c r="E66" s="28" t="s"/>
+      <x:c r="F66" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="27" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C67" s="28" t="s"/>
+      <x:c r="D67" s="28" t="s"/>
+      <x:c r="E67" s="28" t="s"/>
+      <x:c r="F67" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B68" s="27" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C68" s="28" t="s"/>
+      <x:c r="D68" s="28" t="s"/>
+      <x:c r="E68" s="28" t="s"/>
+      <x:c r="F68" s="29" t="n">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B69" s="27" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C69" s="28" t="s"/>
+      <x:c r="D69" s="28" t="s"/>
+      <x:c r="E69" s="28" t="s"/>
+      <x:c r="F69" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B59" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C59" s="28" t="s"/>
-      <x:c r="D59" s="28" t="s"/>
-      <x:c r="E59" s="28" t="s"/>
-      <x:c r="F59" s="29" t="n">
+    <x:row r="70" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B70" s="27" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C70" s="28" t="s"/>
+      <x:c r="D70" s="28" t="s"/>
+      <x:c r="E70" s="28" t="s"/>
+      <x:c r="F70" s="29" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B71" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C71" s="28" t="s"/>
+      <x:c r="D71" s="28" t="s"/>
+      <x:c r="E71" s="28" t="s"/>
+      <x:c r="F71" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B60" s="27" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C60" s="28" t="s"/>
-      <x:c r="D60" s="28" t="s"/>
-      <x:c r="E60" s="28" t="s"/>
-      <x:c r="F60" s="29" t="n">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B61" s="27" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C61" s="28" t="s"/>
-      <x:c r="D61" s="28" t="s"/>
-      <x:c r="E61" s="28" t="s"/>
-      <x:c r="F61" s="29" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B62" s="27" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C62" s="28" t="s"/>
-      <x:c r="D62" s="28" t="s"/>
-      <x:c r="E62" s="28" t="s"/>
-      <x:c r="F62" s="29" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B63" s="27" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C63" s="28" t="s"/>
-      <x:c r="D63" s="28" t="s"/>
-      <x:c r="E63" s="28" t="s"/>
-      <x:c r="F63" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B64" s="30" t="s">
+    <x:row r="72" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B72" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="C64" s="31" t="s"/>
-      <x:c r="D64" s="31" t="s"/>
-      <x:c r="E64" s="31" t="s"/>
-      <x:c r="F64" s="32" t="n">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C72" s="31" t="s"/>
+      <x:c r="D72" s="31" t="s"/>
+      <x:c r="E72" s="31" t="s"/>
+      <x:c r="F72" s="32" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
     <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7315,15 +7682,15 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B56:F56"/>
-    <x:mergeCell ref="B57:E57"/>
-    <x:mergeCell ref="B58:E58"/>
-    <x:mergeCell ref="B59:E59"/>
-    <x:mergeCell ref="B60:E60"/>
-    <x:mergeCell ref="B61:E61"/>
-    <x:mergeCell ref="B62:E62"/>
-    <x:mergeCell ref="B63:E63"/>
-    <x:mergeCell ref="B64:E64"/>
+    <x:mergeCell ref="B64:F64"/>
+    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B66:E66"/>
+    <x:mergeCell ref="B67:E67"/>
+    <x:mergeCell ref="B68:E68"/>
+    <x:mergeCell ref="B69:E69"/>
+    <x:mergeCell ref="B70:E70"/>
+    <x:mergeCell ref="B71:E71"/>
+    <x:mergeCell ref="B72:E72"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="366">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="451">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -82,6 +82,9 @@
     <x:t>43A-2-2026-1081-190</x:t>
   </x:si>
   <x:si>
+    <x:t>1506161</x:t>
+  </x:si>
+  <x:si>
     <x:t>Nerrisa Manalo</x:t>
   </x:si>
   <x:si>
@@ -97,6 +100,9 @@
     <x:t>43A-2-2026-1076-698</x:t>
   </x:si>
   <x:si>
+    <x:t>1507747</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ricardo Natividad</x:t>
   </x:si>
   <x:si>
@@ -112,6 +118,9 @@
     <x:t>43A-2-2026-1082-997</x:t>
   </x:si>
   <x:si>
+    <x:t>1506159</x:t>
+  </x:si>
+  <x:si>
     <x:t>JORETO S. GABAT</x:t>
   </x:si>
   <x:si>
@@ -124,6 +133,9 @@
     <x:t>43A-2-2026-1103-424</x:t>
   </x:si>
   <x:si>
+    <x:t>1507783</x:t>
+  </x:si>
+  <x:si>
     <x:t>RASEL C. FERRER</x:t>
   </x:si>
   <x:si>
@@ -136,6 +148,9 @@
     <x:t>43A-2-2026-1072-268</x:t>
   </x:si>
   <x:si>
+    <x:t>1507682</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROFIEN F. NUÑEZ</x:t>
   </x:si>
   <x:si>
@@ -148,6 +163,9 @@
     <x:t>43A-2-2026-1061-611</x:t>
   </x:si>
   <x:si>
+    <x:t>1507672</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -166,6 +184,9 @@
     <x:t>43A-2-2026-1080-857</x:t>
   </x:si>
   <x:si>
+    <x:t>1505803</x:t>
+  </x:si>
+  <x:si>
     <x:t>Deniel Puyo</x:t>
   </x:si>
   <x:si>
@@ -196,6 +217,9 @@
     <x:t>43A-2-2026-1078-427</x:t>
   </x:si>
   <x:si>
+    <x:t>1505804</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILETOOLS VENTURE INC</x:t>
   </x:si>
   <x:si>
@@ -208,6 +232,9 @@
     <x:t>43A-2-2026-1079-778</x:t>
   </x:si>
   <x:si>
+    <x:t>1505805</x:t>
+  </x:si>
+  <x:si>
     <x:t>STAR APPLIANCE CENTER, INC.</x:t>
   </x:si>
   <x:si>
@@ -220,6 +247,9 @@
     <x:t>43A-2-2026-1107-513</x:t>
   </x:si>
   <x:si>
+    <x:t>1507784</x:t>
+  </x:si>
+  <x:si>
     <x:t>STAR APPLIANCE CENTER, INC. - (BRANCH)</x:t>
   </x:si>
   <x:si>
@@ -232,6 +262,9 @@
     <x:t>43A-2-2026-1106-738</x:t>
   </x:si>
   <x:si>
+    <x:t>1507785</x:t>
+  </x:si>
+  <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
   </x:si>
   <x:si>
@@ -244,6 +277,9 @@
     <x:t>43A-2-2026-1070-812</x:t>
   </x:si>
   <x:si>
+    <x:t>1511010</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ceasar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -262,6 +298,9 @@
     <x:t>43A-2-2026-1114-391</x:t>
   </x:si>
   <x:si>
+    <x:t>1507791</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -277,6 +316,9 @@
     <x:t>43A-2-2026-1135-273</x:t>
   </x:si>
   <x:si>
+    <x:t>1511622</x:t>
+  </x:si>
+  <x:si>
     <x:t>Adora Mercado</x:t>
   </x:si>
   <x:si>
@@ -292,6 +334,9 @@
     <x:t>43A-2-2026-1134-784</x:t>
   </x:si>
   <x:si>
+    <x:t>1511627</x:t>
+  </x:si>
+  <x:si>
     <x:t>STAY YOUNG ONLINE TRADING OPC</x:t>
   </x:si>
   <x:si>
@@ -304,6 +349,9 @@
     <x:t>43A-2-2026-1059-113</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve"> 1507657</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -319,6 +367,9 @@
     <x:t>43A-2-2026-1104-763</x:t>
   </x:si>
   <x:si>
+    <x:t>1507790</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER</x:t>
   </x:si>
   <x:si>
@@ -331,6 +382,9 @@
     <x:t>43A-2-2026-1139-014</x:t>
   </x:si>
   <x:si>
+    <x:t>1511623</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER  (TECNO STORE)</x:t>
   </x:si>
   <x:si>
@@ -343,6 +397,9 @@
     <x:t>43A-2-2026-1129-801</x:t>
   </x:si>
   <x:si>
+    <x:t>1511631</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE AND ACCESSORIES CENTER (HONOR STORE )</x:t>
   </x:si>
   <x:si>
@@ -355,6 +412,9 @@
     <x:t>43A-2-2026-1128-999</x:t>
   </x:si>
   <x:si>
+    <x:t>1511630</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC.</x:t>
   </x:si>
   <x:si>
@@ -367,6 +427,9 @@
     <x:t>43A-2-2026-1136-850</x:t>
   </x:si>
   <x:si>
+    <x:t>1511626</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (GREENTELCOM STORE)</x:t>
   </x:si>
   <x:si>
@@ -379,6 +442,9 @@
     <x:t>43A-2-2026-1142-741</x:t>
   </x:si>
   <x:si>
+    <x:t>1511635</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HONOR STORE )</x:t>
   </x:si>
   <x:si>
@@ -418,6 +484,9 @@
     <x:t>43A-2-2026-1138-367</x:t>
   </x:si>
   <x:si>
+    <x:t>1511624</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC.(GREENTELCOM STORE)</x:t>
   </x:si>
   <x:si>
@@ -427,6 +496,9 @@
     <x:t>43A-2-2026-1137-243</x:t>
   </x:si>
   <x:si>
+    <x:t>1511625</x:t>
+  </x:si>
+  <x:si>
     <x:t>IT AVENUE GENERAL MERCHANDISE</x:t>
   </x:si>
   <x:si>
@@ -439,6 +511,9 @@
     <x:t>43A-2-2026-1121-512</x:t>
   </x:si>
   <x:si>
+    <x:t>1511576</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -454,6 +529,9 @@
     <x:t>43A-2-2026-1067-112</x:t>
   </x:si>
   <x:si>
+    <x:t>1510925</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -469,6 +547,9 @@
     <x:t>43A-2-2026-1074-021</x:t>
   </x:si>
   <x:si>
+    <x:t>1507743</x:t>
+  </x:si>
+  <x:si>
     <x:t>GIZMOTECH CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -481,6 +562,9 @@
     <x:t>43A-2-2026-1099-127</x:t>
   </x:si>
   <x:si>
+    <x:t>1511502</x:t>
+  </x:si>
+  <x:si>
     <x:t>GIZMOTECH CORPORATION - GAMES AND GADGETS</x:t>
   </x:si>
   <x:si>
@@ -493,6 +577,9 @@
     <x:t>43A-2-2026-1075-295</x:t>
   </x:si>
   <x:si>
+    <x:t>1507742</x:t>
+  </x:si>
+  <x:si>
     <x:t>MUNERIS INCORPORATED (SST LAPTOP)</x:t>
   </x:si>
   <x:si>
@@ -505,6 +592,9 @@
     <x:t>43A-2-2026-1123-290</x:t>
   </x:si>
   <x:si>
+    <x:t>1507839</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station Permit to PURCHASE/POSSESS (DOMESTIC Trade)</x:t>
   </x:si>
   <x:si>
@@ -520,6 +610,9 @@
     <x:t>43A-2-2026-1140-568</x:t>
   </x:si>
   <x:si>
+    <x:t>1507884</x:t>
+  </x:si>
+  <x:si>
     <x:t>RODOLFO C. ABAD JR.</x:t>
   </x:si>
   <x:si>
@@ -532,6 +625,9 @@
     <x:t>43A-2-2026-1141-720</x:t>
   </x:si>
   <x:si>
+    <x:t>1507883</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -559,6 +655,9 @@
     <x:t>43A-3-2026-1207-652</x:t>
   </x:si>
   <x:si>
+    <x:t>1511906</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHRISTOPHER I. PALLESCO</x:t>
   </x:si>
   <x:si>
@@ -571,12 +670,18 @@
     <x:t>43A-3-2026-1210-786</x:t>
   </x:si>
   <x:si>
+    <x:t>1529812</x:t>
+  </x:si>
+  <x:si>
     <x:t>DD-AT-02054C-2026</x:t>
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1209-851</x:t>
   </x:si>
   <x:si>
+    <x:t>1529809</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -589,6 +694,9 @@
     <x:t>43A-3-2026-1189-403</x:t>
   </x:si>
   <x:si>
+    <x:t>1511778</x:t>
+  </x:si>
+  <x:si>
     <x:t>JAKE C. PASILAN</x:t>
   </x:si>
   <x:si>
@@ -601,6 +709,9 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>1511815</x:t>
+  </x:si>
+  <x:si>
     <x:t>RUBEN C. SESCON</x:t>
   </x:si>
   <x:si>
@@ -613,6 +724,9 @@
     <x:t>43A-3-2026-1203-366</x:t>
   </x:si>
   <x:si>
+    <x:t>1529776</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
@@ -625,6 +739,9 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve"> 1511203</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -637,6 +754,9 @@
     <x:t>43A-3-2026-1179-857</x:t>
   </x:si>
   <x:si>
+    <x:t>1511203</x:t>
+  </x:si>
+  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -649,6 +769,9 @@
     <x:t>43A-3-2026-1177-099</x:t>
   </x:si>
   <x:si>
+    <x:t>1511204</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -661,6 +784,9 @@
     <x:t>43A-3-2026-1151-716</x:t>
   </x:si>
   <x:si>
+    <x:t>1511234</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -670,6 +796,9 @@
     <x:t>43A-3-2026-1150-325</x:t>
   </x:si>
   <x:si>
+    <x:t>1511233</x:t>
+  </x:si>
+  <x:si>
     <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
   </x:si>
   <x:si>
@@ -679,6 +808,9 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
+    <x:t>1511232</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -691,6 +823,9 @@
     <x:t>43A-3-2026-1154-964</x:t>
   </x:si>
   <x:si>
+    <x:t>1511237</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -703,6 +838,9 @@
     <x:t>43A-2-2026-1089-192</x:t>
   </x:si>
   <x:si>
+    <x:t>1511276</x:t>
+  </x:si>
+  <x:si>
     <x:t>Caesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -715,6 +853,9 @@
     <x:t>43A-2-2026-1095-163</x:t>
   </x:si>
   <x:si>
+    <x:t>1511194</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
@@ -727,6 +868,9 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
+    <x:t>1511225</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -736,6 +880,9 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
+    <x:t>1511192</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -748,6 +895,9 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
+    <x:t>1511193</x:t>
+  </x:si>
+  <x:si>
     <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
   </x:si>
   <x:si>
@@ -757,6 +907,9 @@
     <x:t>43A-2-2026-1085-453</x:t>
   </x:si>
   <x:si>
+    <x:t>1511206</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
   </x:si>
   <x:si>
@@ -766,6 +919,9 @@
     <x:t>43A-2-2026-1111-408</x:t>
   </x:si>
   <x:si>
+    <x:t>1511278</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -775,6 +931,9 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
+    <x:t>1511223</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -784,6 +943,9 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
+    <x:t>1511224</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -796,6 +958,9 @@
     <x:t>43A-2-2026-1086-471</x:t>
   </x:si>
   <x:si>
+    <x:t>1511196</x:t>
+  </x:si>
+  <x:si>
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
@@ -808,6 +973,9 @@
     <x:t>43A-2-2026-1097-702</x:t>
   </x:si>
   <x:si>
+    <x:t>1511274</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -817,6 +985,9 @@
     <x:t>43A-2-2026-1109-317</x:t>
   </x:si>
   <x:si>
+    <x:t>1511246</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
   </x:si>
   <x:si>
@@ -829,6 +1000,9 @@
     <x:t>43A-3-2026-1152-831</x:t>
   </x:si>
   <x:si>
+    <x:t>1511235</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILECRAZE TELECOM INC</x:t>
   </x:si>
   <x:si>
@@ -841,6 +1015,9 @@
     <x:t>43A-3-2026-1159-651</x:t>
   </x:si>
   <x:si>
+    <x:t>1511242</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILECRAZE TELECOM INC.</x:t>
   </x:si>
   <x:si>
@@ -853,6 +1030,9 @@
     <x:t>43A-2-2026-1113-757</x:t>
   </x:si>
   <x:si>
+    <x:t>1511248</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -865,6 +1045,9 @@
     <x:t>43A-3-2026-1153-796</x:t>
   </x:si>
   <x:si>
+    <x:t>1511236</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHONEVILLE MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -877,6 +1060,9 @@
     <x:t>43A-3-2026-1202-217</x:t>
   </x:si>
   <x:si>
+    <x:t>1511271</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -889,6 +1075,9 @@
     <x:t>43A-2-2026-1094-777</x:t>
   </x:si>
   <x:si>
+    <x:t>1511195</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC</x:t>
   </x:si>
   <x:si>
@@ -898,6 +1087,9 @@
     <x:t>43A-3-2026-1161-717</x:t>
   </x:si>
   <x:si>
+    <x:t>1511211</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -910,6 +1102,9 @@
     <x:t>43A-2-2026-1108-762</x:t>
   </x:si>
   <x:si>
+    <x:t>1511213</x:t>
+  </x:si>
+  <x:si>
     <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -919,6 +1114,9 @@
     <x:t>43A-2-2026-1083-282</x:t>
   </x:si>
   <x:si>
+    <x:t>1511241</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -928,6 +1126,9 @@
     <x:t>43A-3-2026-1168-173</x:t>
   </x:si>
   <x:si>
+    <x:t>1511222</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
   </x:si>
   <x:si>
@@ -937,6 +1138,9 @@
     <x:t>43A-3-2026-1201-204</x:t>
   </x:si>
   <x:si>
+    <x:t>1511270</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -946,6 +1150,9 @@
     <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
+    <x:t>1511231</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -958,6 +1165,9 @@
     <x:t>43A-2-2026-1084-395</x:t>
   </x:si>
   <x:si>
+    <x:t>1511240</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -967,6 +1177,9 @@
     <x:t>43A-2-2026-1087-228</x:t>
   </x:si>
   <x:si>
+    <x:t>1511275</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -979,6 +1192,9 @@
     <x:t>43A-3-2026-1174-419</x:t>
   </x:si>
   <x:si>
+    <x:t>1511761</x:t>
+  </x:si>
+  <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -991,6 +1207,9 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
+    <x:t>1507967</x:t>
+  </x:si>
+  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -1000,6 +1219,9 @@
     <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
+    <x:t>1507966</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -1018,6 +1240,9 @@
     <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
+    <x:t>1507965</x:t>
+  </x:si>
+  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -1030,6 +1255,9 @@
     <x:t>43A-3-2026-1162-745</x:t>
   </x:si>
   <x:si>
+    <x:t>1511226</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
   </x:si>
   <x:si>
@@ -1039,6 +1267,9 @@
     <x:t>43A-3-2026-1157-256</x:t>
   </x:si>
   <x:si>
+    <x:t>1511208</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -1051,6 +1282,9 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>1511639</x:t>
+  </x:si>
+  <x:si>
     <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -1060,6 +1294,9 @@
     <x:t>43A-3-2026-1163-392</x:t>
   </x:si>
   <x:si>
+    <x:t>1511277</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -1069,6 +1306,9 @@
     <x:t>43A-3-2026-1175-710</x:t>
   </x:si>
   <x:si>
+    <x:t>1511759</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -1078,6 +1318,9 @@
     <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
+    <x:t>1511760</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -1087,6 +1330,9 @@
     <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
+    <x:t>1511758</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBOY INC.</x:t>
   </x:si>
   <x:si>
@@ -1099,6 +1345,9 @@
     <x:t>43A-3-2026-1205-403</x:t>
   </x:si>
   <x:si>
+    <x:t>1511858</x:t>
+  </x:si>
+  <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -1111,6 +1360,9 @@
     <x:t>43A-3-2026-1194-347</x:t>
   </x:si>
   <x:si>
+    <x:t>1511219</x:t>
+  </x:si>
+  <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -1121,6 +1373,9 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1147-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507892</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1132,7 +1387,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1186,13 +1441,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -1451,7 +1699,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1489,50 +1737,41 @@
     <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1576,6 +1815,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1587,71 +1830,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2018,7 +2245,7 @@
       <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s"/>
+      <x:c r="D8" s="14" t="s"/>
       <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
@@ -2028,23 +2255,23 @@
       <x:c r="G8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="14">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J8" s="13" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="H8" s="15">
+        <x:v>46069.0835222569</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46069.1006819792</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="14">
-        <x:v>46069.1133333333</x:v>
+      <x:c r="L8" s="17">
+        <x:v>46069.1133347338</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -2052,1444 +2279,1444 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46066.3145039236</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="17">
+        <x:v>46066.3194256134</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s"/>
+      <x:c r="E10" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="15">
+        <x:v>46069.0835757523</x:v>
+      </x:c>
+      <x:c r="I10" s="15">
+        <x:v>46069.1000300231</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="17">
+        <x:v>46069.1128697454</x:v>
+      </x:c>
+      <x:c r="M10" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F9" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="14">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J9" s="13" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="s"/>
+      <x:c r="E11" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="15">
+        <x:v>46072.1720853819</x:v>
+      </x:c>
+      <x:c r="I11" s="15">
+        <x:v>46072.2351628009</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K11" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="14">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M9" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
+      <x:c r="L11" s="17">
+        <x:v>46073.1890290625</x:v>
+      </x:c>
+      <x:c r="M11" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s"/>
-      <x:c r="E10" s="16" t="s">
+      <x:c r="C12" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="s"/>
+      <x:c r="E12" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="15">
+        <x:v>46063.2819612616</x:v>
+      </x:c>
+      <x:c r="I12" s="15">
+        <x:v>46063.2922791319</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K12" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L12" s="17">
+        <x:v>46063.2957673958</x:v>
+      </x:c>
+      <x:c r="M12" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="s"/>
+      <x:c r="E13" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H13" s="15">
+        <x:v>46058.4859935069</x:v>
+      </x:c>
+      <x:c r="I13" s="15">
+        <x:v>46062.1570258102</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K13" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="20">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="16" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="L13" s="17">
+        <x:v>46062.1882026968</x:v>
+      </x:c>
+      <x:c r="M13" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H14" s="15">
+        <x:v>46067.3600302778</x:v>
+      </x:c>
+      <x:c r="I14" s="15">
+        <x:v>46067.3600485417</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K14" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="17">
+        <x:v>46079.273015787</x:v>
+      </x:c>
+      <x:c r="M14" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H15" s="15">
+        <x:v>46072.3184291551</x:v>
+      </x:c>
+      <x:c r="I15" s="15">
+        <x:v>46072.3184479745</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="17">
+        <x:v>46079.269710081</x:v>
+      </x:c>
+      <x:c r="M15" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H16" s="15">
+        <x:v>46067.1596693866</x:v>
+      </x:c>
+      <x:c r="I16" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K16" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="17">
+        <x:v>46079.277259919</x:v>
+      </x:c>
+      <x:c r="M16" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H17" s="15">
+        <x:v>46067.222213287</x:v>
+      </x:c>
+      <x:c r="I17" s="15">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K17" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="17">
+        <x:v>46079.2763165278</x:v>
+      </x:c>
+      <x:c r="M17" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H18" s="15">
+        <x:v>46072.3605633333</x:v>
+      </x:c>
+      <x:c r="I18" s="15">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="K18" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="17">
+        <x:v>46073.2285051968</x:v>
+      </x:c>
+      <x:c r="M18" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H19" s="15">
+        <x:v>46072.352960787</x:v>
+      </x:c>
+      <x:c r="I19" s="15">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K19" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="17">
+        <x:v>46073.2314433796</x:v>
+      </x:c>
+      <x:c r="M19" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H20" s="15">
+        <x:v>46063.1352781944</x:v>
+      </x:c>
+      <x:c r="I20" s="15">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K20" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="17">
+        <x:v>46063.2367775347</x:v>
+      </x:c>
+      <x:c r="M20" s="13" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="13" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="s"/>
+      <x:c r="E21" s="13" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H21" s="15">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="I21" s="15">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="J21" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K21" s="16" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L21" s="17">
+        <x:v>46073.3142477315</x:v>
+      </x:c>
+      <x:c r="M21" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="13" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H22" s="15">
+        <x:v>46079.3584810995</x:v>
+      </x:c>
+      <x:c r="I22" s="15">
+        <x:v>46079.3584983796</x:v>
+      </x:c>
+      <x:c r="J22" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K22" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="17">
+        <x:v>46080.2311256134</x:v>
+      </x:c>
+      <x:c r="M22" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="13" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G23" s="13" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H23" s="15">
+        <x:v>46079.3539738194</x:v>
+      </x:c>
+      <x:c r="I23" s="15">
+        <x:v>46079.3539910417</x:v>
+      </x:c>
+      <x:c r="J23" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K23" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="17">
+        <x:v>46080.244091956</x:v>
+      </x:c>
+      <x:c r="M23" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="13" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H24" s="15">
+        <x:v>46058.1529325347</x:v>
+      </x:c>
+      <x:c r="I24" s="15">
+        <x:v>46058.1529476968</x:v>
+      </x:c>
+      <x:c r="J24" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K24" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="17">
+        <x:v>46058.2410705671</x:v>
+      </x:c>
+      <x:c r="M24" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G25" s="13" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H25" s="15">
+        <x:v>46072.2635348032</x:v>
+      </x:c>
+      <x:c r="I25" s="15">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J25" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="K25" s="16" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="17">
+        <x:v>46073.3091133681</x:v>
+      </x:c>
+      <x:c r="M25" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H26" s="15">
+        <x:v>46079.3873177662</x:v>
+      </x:c>
+      <x:c r="I26" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K26" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="17">
+        <x:v>46080.2360791898</x:v>
+      </x:c>
+      <x:c r="M26" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G27" s="13" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H27" s="15">
+        <x:v>46079.2523059375</x:v>
+      </x:c>
+      <x:c r="I27" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="K27" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="17">
+        <x:v>46080.2925916204</x:v>
+      </x:c>
+      <x:c r="M27" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G28" s="13" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H28" s="15">
+        <x:v>46079.2430618866</x:v>
+      </x:c>
+      <x:c r="I28" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="K28" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="17">
+        <x:v>46080.2801283218</x:v>
+      </x:c>
+      <x:c r="M28" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="20">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="16" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I13" s="18">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="20">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="20">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
+      <x:c r="D29" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G29" s="13" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H29" s="15">
+        <x:v>46079.3652018403</x:v>
+      </x:c>
+      <x:c r="I29" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K29" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="17">
+        <x:v>46080.2425555208</x:v>
+      </x:c>
+      <x:c r="M29" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G30" s="13" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H30" s="15">
+        <x:v>46080.2923673264</x:v>
+      </x:c>
+      <x:c r="I30" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K30" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="17">
+        <x:v>46080.3208568171</x:v>
+      </x:c>
+      <x:c r="M30" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G31" s="13" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H31" s="15">
+        <x:v>46079.3162545833</x:v>
+      </x:c>
+      <x:c r="I31" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="K31" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="17">
+        <x:v>46080.2883729977</x:v>
+      </x:c>
+      <x:c r="M31" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G32" s="13" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H32" s="15">
+        <x:v>46079.3059443634</x:v>
+      </x:c>
+      <x:c r="I32" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="K32" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="17">
+        <x:v>46080.2896890278</x:v>
+      </x:c>
+      <x:c r="M32" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C33" s="13" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F33" s="13" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G33" s="13" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H33" s="15">
+        <x:v>46079.2943998843</x:v>
+      </x:c>
+      <x:c r="I33" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="K33" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="17">
+        <x:v>46080.2916823611</x:v>
+      </x:c>
+      <x:c r="M33" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F34" s="13" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G34" s="13" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H34" s="15">
+        <x:v>46079.3789042361</x:v>
+      </x:c>
+      <x:c r="I34" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="K34" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="17">
+        <x:v>46080.2376106713</x:v>
+      </x:c>
+      <x:c r="M34" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F35" s="13" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G35" s="13" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H35" s="15">
+        <x:v>46079.3728295139</x:v>
+      </x:c>
+      <x:c r="I35" s="15">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K35" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="17">
+        <x:v>46080.2394384722</x:v>
+      </x:c>
+      <x:c r="M35" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F36" s="13" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G36" s="13" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H36" s="15">
+        <x:v>46077.0697396412</x:v>
+      </x:c>
+      <x:c r="I36" s="15">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J36" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="K36" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="17">
+        <x:v>46077.1078903704</x:v>
+      </x:c>
+      <x:c r="M36" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="13" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C37" s="13" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="20">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E16" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E17" s="16" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
+      <x:c r="E37" s="13" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F37" s="13" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G37" s="13" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H37" s="15">
+        <x:v>46062.159017581</x:v>
+      </x:c>
+      <x:c r="I37" s="15">
+        <x:v>46062.1590321875</x:v>
+      </x:c>
+      <x:c r="J37" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="K37" s="16" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L37" s="17">
+        <x:v>46062.1863264931</x:v>
+      </x:c>
+      <x:c r="M37" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C38" s="13" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D38" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H17" s="18">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I17" s="18">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I18" s="18">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I19" s="18">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="20">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I20" s="18">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s"/>
-      <x:c r="E21" s="16" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I21" s="18">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L21" s="20">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C22" s="16" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D22" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E22" s="16" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F22" s="16" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H22" s="18">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I22" s="18">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J22" s="17" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K22" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="20">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M22" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C23" s="16" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D23" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E23" s="16" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F23" s="16" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H23" s="18">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I23" s="18">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J23" s="17" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K23" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="20">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M23" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C24" s="16" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D24" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E24" s="16" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F24" s="16" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G24" s="16" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H24" s="18">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I24" s="18">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J24" s="17" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K24" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="20">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M24" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C25" s="16" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D25" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E25" s="16" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F25" s="16" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G25" s="16" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H25" s="18">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I25" s="18">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J25" s="17" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K25" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="20">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M25" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C26" s="16" t="s">
+      <x:c r="E38" s="13" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F38" s="13" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G38" s="13" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H38" s="15">
+        <x:v>46066.2180240509</x:v>
+      </x:c>
+      <x:c r="I38" s="15">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J38" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K38" s="16" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L38" s="17">
+        <x:v>46066.2724449537</x:v>
+      </x:c>
+      <x:c r="M38" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C39" s="13" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D39" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E39" s="13" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F39" s="13" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G39" s="13" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H39" s="15">
+        <x:v>46071.0492490046</x:v>
+      </x:c>
+      <x:c r="I39" s="15">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J39" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="K39" s="16" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L39" s="17">
+        <x:v>46071.0606162616</x:v>
+      </x:c>
+      <x:c r="M39" s="13" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D26" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E26" s="16" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F26" s="16" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G26" s="16" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H26" s="18">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I26" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="17" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K26" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="20">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M26" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C27" s="16" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D27" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E27" s="16" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F27" s="16" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G27" s="16" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H27" s="18">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I27" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="17" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K27" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="20">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M27" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C28" s="16" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D28" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E28" s="16" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F28" s="16" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G28" s="16" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H28" s="18">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I28" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K28" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="20">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M28" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C29" s="16" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D29" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E29" s="16" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F29" s="16" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G29" s="16" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H29" s="18">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I29" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="17" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K29" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="20">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M29" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C30" s="16" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D30" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E30" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F30" s="16" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G30" s="16" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H30" s="18">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I30" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="17" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K30" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="20">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M30" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C31" s="16" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D31" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E31" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F31" s="16" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G31" s="16" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H31" s="18">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I31" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="20">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M31" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C32" s="16" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D32" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E32" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F32" s="16" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H32" s="18">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I32" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K32" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="20">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M32" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C33" s="16" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D33" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E33" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F33" s="16" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G33" s="16" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H33" s="18">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I33" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="17" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K33" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="20">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M33" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C34" s="16" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D34" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E34" s="16" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F34" s="16" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G34" s="16" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H34" s="18">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I34" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="17" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K34" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="20">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M34" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C35" s="16" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D35" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E35" s="16" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F35" s="16" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G35" s="16" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H35" s="18">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I35" s="18">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J35" s="17" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K35" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="20">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M35" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C36" s="16" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D36" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E36" s="16" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F36" s="16" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G36" s="16" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H36" s="18">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I36" s="18">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J36" s="17" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K36" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="20">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M36" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="16" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C37" s="16" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D37" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E37" s="16" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F37" s="16" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G37" s="16" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H37" s="18">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I37" s="18">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J37" s="17" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K37" s="19" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L37" s="20">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M37" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C38" s="16" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D38" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E38" s="16" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F38" s="16" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G38" s="16" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H38" s="18">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I38" s="18">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J38" s="17" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K38" s="19" t="n">
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C40" s="13" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E40" s="13" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F40" s="13" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G40" s="13" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H40" s="15">
+        <x:v>46066.2275385417</x:v>
+      </x:c>
+      <x:c r="I40" s="15">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J40" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="K40" s="16" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="20">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M38" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C39" s="16" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D39" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E39" s="16" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F39" s="16" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G39" s="16" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H39" s="18">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I39" s="18">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J39" s="17" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K39" s="19" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L39" s="20">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M39" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C40" s="16" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D40" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E40" s="16" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F40" s="16" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G40" s="16" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H40" s="18">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I40" s="18">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J40" s="17" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K40" s="19" t="n">
+      <x:c r="L40" s="17">
+        <x:v>46066.2701807986</x:v>
+      </x:c>
+      <x:c r="M40" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C41" s="13" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E41" s="13" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F41" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G41" s="13" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H41" s="15">
+        <x:v>46078.2436305208</x:v>
+      </x:c>
+      <x:c r="I41" s="15">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J41" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="K41" s="16" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L40" s="20">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M40" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C41" s="16" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D41" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E41" s="16" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F41" s="16" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="G41" s="16" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H41" s="18">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I41" s="18">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J41" s="17" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K41" s="19" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L41" s="20">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M41" s="16" t="s">
-        <x:v>24</x:v>
+      <x:c r="L41" s="17">
+        <x:v>46078.3266231366</x:v>
+      </x:c>
+      <x:c r="M41" s="13" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="16" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C42" s="16" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D42" s="17" t="s"/>
-      <x:c r="E42" s="16" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F42" s="16" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G42" s="16" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H42" s="18">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I42" s="18">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J42" s="17" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K42" s="19" t="n">
+      <x:c r="B42" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C42" s="13" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D42" s="14" t="s"/>
+      <x:c r="E42" s="13" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F42" s="13" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G42" s="13" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H42" s="15">
+        <x:v>46080.2342400116</x:v>
+      </x:c>
+      <x:c r="I42" s="15">
+        <x:v>46080.2342615972</x:v>
+      </x:c>
+      <x:c r="J42" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="K42" s="16" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L42" s="20">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M42" s="16" t="s">
-        <x:v>24</x:v>
+      <x:c r="L42" s="17">
+        <x:v>46080.3353454745</x:v>
+      </x:c>
+      <x:c r="M42" s="13" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="16" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C43" s="16" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D43" s="17" t="s"/>
-      <x:c r="E43" s="16" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F43" s="16" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="G43" s="16" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H43" s="18">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I43" s="18">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J43" s="17" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K43" s="19" t="n">
+      <x:c r="B43" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C43" s="13" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D43" s="14" t="s"/>
+      <x:c r="E43" s="13" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F43" s="13" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G43" s="13" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H43" s="15">
+        <x:v>46080.272270544</x:v>
+      </x:c>
+      <x:c r="I43" s="15">
+        <x:v>46080.2722898495</x:v>
+      </x:c>
+      <x:c r="J43" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K43" s="16" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L43" s="20">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M43" s="16" t="s">
-        <x:v>24</x:v>
+      <x:c r="L43" s="17">
+        <x:v>46080.3345804745</x:v>
+      </x:c>
+      <x:c r="M43" s="13" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="21" t="s">
+      <x:c r="B46" s="18" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C46" s="19" t="s"/>
+      <x:c r="D46" s="19" t="s"/>
+      <x:c r="E46" s="20" t="s"/>
+      <x:c r="F46" s="20" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B47" s="21" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C47" s="22" t="s"/>
+      <x:c r="D47" s="22" t="s"/>
+      <x:c r="E47" s="22" t="s"/>
+      <x:c r="F47" s="23" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C48" s="25" t="s"/>
+      <x:c r="D48" s="25" t="s"/>
+      <x:c r="E48" s="25" t="s"/>
+      <x:c r="F48" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="24" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C49" s="25" t="s"/>
+      <x:c r="D49" s="25" t="s"/>
+      <x:c r="E49" s="25" t="s"/>
+      <x:c r="F49" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C50" s="25" t="s"/>
+      <x:c r="D50" s="25" t="s"/>
+      <x:c r="E50" s="25" t="s"/>
+      <x:c r="F50" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="24" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C51" s="25" t="s"/>
+      <x:c r="D51" s="25" t="s"/>
+      <x:c r="E51" s="25" t="s"/>
+      <x:c r="F51" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="24" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C52" s="25" t="s"/>
+      <x:c r="D52" s="25" t="s"/>
+      <x:c r="E52" s="25" t="s"/>
+      <x:c r="F52" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="24" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C53" s="25" t="s"/>
+      <x:c r="D53" s="25" t="s"/>
+      <x:c r="E53" s="25" t="s"/>
+      <x:c r="F53" s="26" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="24" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C54" s="25" t="s"/>
+      <x:c r="D54" s="25" t="s"/>
+      <x:c r="E54" s="25" t="s"/>
+      <x:c r="F54" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="24" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C46" s="22" t="s"/>
-      <x:c r="D46" s="22" t="s"/>
-      <x:c r="E46" s="23" t="s"/>
-      <x:c r="F46" s="23" t="s"/>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="24" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C47" s="25" t="s"/>
-      <x:c r="D47" s="25" t="s"/>
-      <x:c r="E47" s="25" t="s"/>
-      <x:c r="F47" s="26" t="s">
-        <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C48" s="28" t="s"/>
-      <x:c r="D48" s="28" t="s"/>
-      <x:c r="E48" s="28" t="s"/>
-      <x:c r="F48" s="29" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C49" s="28" t="s"/>
-      <x:c r="D49" s="28" t="s"/>
-      <x:c r="E49" s="28" t="s"/>
-      <x:c r="F49" s="29" t="n">
+      <x:c r="C55" s="25" t="s"/>
+      <x:c r="D55" s="25" t="s"/>
+      <x:c r="E55" s="25" t="s"/>
+      <x:c r="F55" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="24" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C56" s="25" t="s"/>
+      <x:c r="D56" s="25" t="s"/>
+      <x:c r="E56" s="25" t="s"/>
+      <x:c r="F56" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="27" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C50" s="28" t="s"/>
-      <x:c r="D50" s="28" t="s"/>
-      <x:c r="E50" s="28" t="s"/>
-      <x:c r="F50" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="27" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C51" s="28" t="s"/>
-      <x:c r="D51" s="28" t="s"/>
-      <x:c r="E51" s="28" t="s"/>
-      <x:c r="F51" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="27" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C52" s="28" t="s"/>
-      <x:c r="D52" s="28" t="s"/>
-      <x:c r="E52" s="28" t="s"/>
-      <x:c r="F52" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="27" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="27" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="27" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C55" s="28" t="s"/>
-      <x:c r="D55" s="28" t="s"/>
-      <x:c r="E55" s="28" t="s"/>
-      <x:c r="F55" s="29" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="27" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C56" s="28" t="s"/>
-      <x:c r="D56" s="28" t="s"/>
-      <x:c r="E56" s="28" t="s"/>
-      <x:c r="F56" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="30" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C57" s="31" t="s"/>
-      <x:c r="D57" s="31" t="s"/>
-      <x:c r="E57" s="31" t="s"/>
-      <x:c r="F57" s="32" t="n">
+      <x:c r="B57" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C57" s="28" t="s"/>
+      <x:c r="D57" s="28" t="s"/>
+      <x:c r="E57" s="28" t="s"/>
+      <x:c r="F57" s="29" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
@@ -4539,7 +4766,7 @@
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
       <x:c r="B4" s="11" t="s">
-        <x:v>173</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -4622,35 +4849,35 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="13" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D8" s="13" t="s"/>
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
       <x:c r="E8" s="13" t="s">
-        <x:v>175</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F8" s="13" t="s">
-        <x:v>176</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G8" s="13" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H8" s="14">
-        <x:v>46100.1144675926</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>46100.1505092593</x:v>
-      </x:c>
-      <x:c r="J8" s="13" t="n">
-        <x:v>1511906</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46100.1144765394</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46100.1505107292</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="14">
-        <x:v>46100.1652777778</x:v>
+      <x:c r="L8" s="17">
+        <x:v>46100.1652817245</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>84</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -4658,2101 +4885,2101 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s"/>
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
       <x:c r="E9" s="13" t="s">
-        <x:v>179</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F9" s="13" t="s">
-        <x:v>180</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G9" s="13" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H9" s="14">
-        <x:v>46100.3734490741</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46100.388599537</x:v>
-      </x:c>
-      <x:c r="J9" s="13" t="n">
-        <x:v>1529812</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46100.3734511921</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46100.3886071759</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="14">
-        <x:v>46100.3957175926</x:v>
+      <x:c r="L9" s="17">
+        <x:v>46100.3957177662</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
+      <x:c r="B10" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s"/>
-      <x:c r="E10" s="16" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
-        <x:v>46100.365787037</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>46100.3731712963</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1529809</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="C10" s="13" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s"/>
+      <x:c r="E10" s="13" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H10" s="15">
+        <x:v>46100.3657890856</x:v>
+      </x:c>
+      <x:c r="I10" s="15">
+        <x:v>46100.3731746412</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="20">
-        <x:v>46100.3868981482</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>24</x:v>
+      <x:c r="L10" s="17">
+        <x:v>46100.3869012616</x:v>
+      </x:c>
+      <x:c r="M10" s="13" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
+      <x:c r="B11" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="16" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="C11" s="13" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="s"/>
+      <x:c r="E11" s="13" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H11" s="15">
+        <x:v>46091.3061033796</x:v>
+      </x:c>
+      <x:c r="I11" s="15">
+        <x:v>46091.3108077083</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="K11" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L11" s="20">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>84</x:v>
+      <x:c r="L11" s="17">
+        <x:v>46091.3131892477</x:v>
+      </x:c>
+      <x:c r="M11" s="13" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
+      <x:c r="B12" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="16" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="C12" s="13" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="s"/>
+      <x:c r="E12" s="13" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H12" s="15">
+        <x:v>46093.1459465972</x:v>
+      </x:c>
+      <x:c r="I12" s="15">
+        <x:v>46093.1585187731</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="K12" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L12" s="20">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>84</x:v>
+      <x:c r="L12" s="17">
+        <x:v>46093.1595409143</x:v>
+      </x:c>
+      <x:c r="M12" s="13" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
+      <x:c r="B13" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="16" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I13" s="18">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="C13" s="13" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="s"/>
+      <x:c r="E13" s="13" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H13" s="15">
+        <x:v>46098.0792632986</x:v>
+      </x:c>
+      <x:c r="I13" s="15">
+        <x:v>46098.0878978819</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="K13" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="20">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>24</x:v>
+      <x:c r="L13" s="17">
+        <x:v>46098.0997679745</x:v>
+      </x:c>
+      <x:c r="M13" s="13" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="B14" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H14" s="15">
+        <x:v>46090.2418365857</x:v>
+      </x:c>
+      <x:c r="I14" s="15">
+        <x:v>46090.2418534606</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="K14" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="20">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L14" s="17">
+        <x:v>46093.3049920255</x:v>
+      </x:c>
+      <x:c r="M14" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="B15" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H15" s="15">
+        <x:v>46090.2558238542</x:v>
+      </x:c>
+      <x:c r="I15" s="15">
+        <x:v>46090.2558400116</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="20">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L15" s="17">
+        <x:v>46097.2890797917</x:v>
+      </x:c>
+      <x:c r="M15" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E16" s="16" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
+      <x:c r="B16" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H16" s="15">
+        <x:v>46090.210999456</x:v>
+      </x:c>
+      <x:c r="I16" s="15">
+        <x:v>46090.211015162</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="K16" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L16" s="20">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L16" s="17">
+        <x:v>46093.3080127546</x:v>
+      </x:c>
+      <x:c r="M16" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E17" s="16" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I17" s="18">
+      <x:c r="B17" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H17" s="15">
+        <x:v>46083.2380494329</x:v>
+      </x:c>
+      <x:c r="I17" s="15">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
+      <x:c r="J17" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="K17" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="20">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L17" s="17">
+        <x:v>46097.1564439468</x:v>
+      </x:c>
+      <x:c r="M17" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I18" s="18">
+      <x:c r="B18" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H18" s="15">
+        <x:v>46083.2322339931</x:v>
+      </x:c>
+      <x:c r="I18" s="15">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
+      <x:c r="J18" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="K18" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="20">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L18" s="17">
+        <x:v>46097.1495293519</x:v>
+      </x:c>
+      <x:c r="M18" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I19" s="18">
+      <x:c r="B19" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H19" s="15">
+        <x:v>46080.4532551852</x:v>
+      </x:c>
+      <x:c r="I19" s="15">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
+      <x:c r="J19" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="K19" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="20">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L19" s="17">
+        <x:v>46097.1461728357</x:v>
+      </x:c>
+      <x:c r="M19" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I20" s="18">
+      <x:c r="B20" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H20" s="15">
+        <x:v>46083.2599218056</x:v>
+      </x:c>
+      <x:c r="I20" s="15">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
+      <x:c r="J20" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K20" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="20">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L20" s="17">
+        <x:v>46097.1652390856</x:v>
+      </x:c>
+      <x:c r="M20" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E21" s="16" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>46069.2785648148</x:v>
-      </x:c>
-      <x:c r="I21" s="18">
+      <x:c r="B21" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H21" s="15">
+        <x:v>46069.278571956</x:v>
+      </x:c>
+      <x:c r="I21" s="15">
         <x:v>46067</x:v>
       </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1511276</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
+      <x:c r="J21" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="K21" s="16" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L21" s="20">
-        <x:v>46100.3884027778</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>226</x:v>
+      <x:c r="L21" s="17">
+        <x:v>46100.3884108912</x:v>
+      </x:c>
+      <x:c r="M21" s="13" t="s">
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C22" s="16" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D22" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E22" s="16" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F22" s="16" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H22" s="18">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I22" s="18">
+      <x:c r="B22" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H22" s="15">
+        <x:v>46069.3514850347</x:v>
+      </x:c>
+      <x:c r="I22" s="15">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J22" s="17" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K22" s="19" t="n">
+      <x:c r="J22" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="K22" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="20">
+      <x:c r="L22" s="17">
         <x:v>46097.2437384259</x:v>
       </x:c>
-      <x:c r="M22" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="M22" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C23" s="16" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D23" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E23" s="16" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F23" s="16" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H23" s="18">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I23" s="18">
+      <x:c r="B23" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="G23" s="13" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="H23" s="15">
+        <x:v>46084.0854516898</x:v>
+      </x:c>
+      <x:c r="I23" s="15">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J23" s="17" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K23" s="19" t="n">
+      <x:c r="J23" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="K23" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="20">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M23" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L23" s="17">
+        <x:v>46093.3956400694</x:v>
+      </x:c>
+      <x:c r="M23" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C24" s="16" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D24" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E24" s="16" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="F24" s="16" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="G24" s="16" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="H24" s="18">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I24" s="18">
+      <x:c r="B24" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H24" s="15">
+        <x:v>46084.0996762384</x:v>
+      </x:c>
+      <x:c r="I24" s="15">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J24" s="17" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K24" s="19" t="n">
+      <x:c r="J24" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="K24" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="20">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M24" s="16" t="s">
-        <x:v>200</x:v>
+      <x:c r="L24" s="17">
+        <x:v>46097.241468588</x:v>
+      </x:c>
+      <x:c r="M24" s="13" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C25" s="16" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D25" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E25" s="16" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="F25" s="16" t="s">
+      <x:c r="B25" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G25" s="13" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H25" s="15">
+        <x:v>46069.3573124306</x:v>
+      </x:c>
+      <x:c r="I25" s="15">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="K25" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="17">
+        <x:v>46097.2426396643</x:v>
+      </x:c>
+      <x:c r="M25" s="13" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G25" s="16" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H25" s="18">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I25" s="18">
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H26" s="15">
+        <x:v>46069.1542109954</x:v>
+      </x:c>
+      <x:c r="I26" s="15">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J26" s="14" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="K26" s="16" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L26" s="17">
+        <x:v>46097.2466610301</x:v>
+      </x:c>
+      <x:c r="M26" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G27" s="13" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H27" s="15">
+        <x:v>46073.1441202083</x:v>
+      </x:c>
+      <x:c r="I27" s="15">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J27" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="K27" s="16" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L27" s="17">
+        <x:v>46100.4005466667</x:v>
+      </x:c>
+      <x:c r="M27" s="13" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G28" s="13" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="H28" s="15">
+        <x:v>46084.2189288542</x:v>
+      </x:c>
+      <x:c r="I28" s="15">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J28" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="K28" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="17">
+        <x:v>46093.3723926852</x:v>
+      </x:c>
+      <x:c r="M28" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G29" s="13" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H29" s="15">
+        <x:v>46084.2250188542</x:v>
+      </x:c>
+      <x:c r="I29" s="15">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J29" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="K29" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="17">
+        <x:v>46093.3804507639</x:v>
+      </x:c>
+      <x:c r="M29" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G30" s="13" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="H30" s="15">
+        <x:v>46069.2178798032</x:v>
+      </x:c>
+      <x:c r="I30" s="15">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J30" s="14" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="K30" s="16" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L30" s="17">
+        <x:v>46097.2456397685</x:v>
+      </x:c>
+      <x:c r="M30" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="G31" s="13" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="H31" s="15">
+        <x:v>46069.3717699074</x:v>
+      </x:c>
+      <x:c r="I31" s="15">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="K31" s="16" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L31" s="17">
+        <x:v>46100.3754893056</x:v>
+      </x:c>
+      <x:c r="M31" s="13" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="G32" s="13" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="H32" s="15">
+        <x:v>46073.1251625463</x:v>
+      </x:c>
+      <x:c r="I32" s="15">
+        <x:v>45619</x:v>
+      </x:c>
+      <x:c r="J32" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="K32" s="16" t="n">
+        <x:v>11280</x:v>
+      </x:c>
+      <x:c r="L32" s="17">
+        <x:v>46099.1200232986</x:v>
+      </x:c>
+      <x:c r="M32" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C33" s="13" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F33" s="13" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="G33" s="13" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="H33" s="15">
+        <x:v>46083.2443981019</x:v>
+      </x:c>
+      <x:c r="I33" s="15">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J25" s="17" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K25" s="19" t="n">
+      <x:c r="J33" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="K33" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="20">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M25" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C26" s="16" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D26" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E26" s="16" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F26" s="16" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G26" s="16" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H26" s="18">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I26" s="18">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J26" s="17" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K26" s="19" t="n">
+      <x:c r="L33" s="17">
+        <x:v>46097.1600206018</x:v>
+      </x:c>
+      <x:c r="M33" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="F34" s="13" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="G34" s="13" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="H34" s="15">
+        <x:v>46084.1225139699</x:v>
+      </x:c>
+      <x:c r="I34" s="15">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J34" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="K34" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="17">
+        <x:v>46097.3505144329</x:v>
+      </x:c>
+      <x:c r="M34" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="F35" s="13" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="G35" s="13" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="H35" s="15">
+        <x:v>46073.1541139005</x:v>
+      </x:c>
+      <x:c r="I35" s="15">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="K35" s="16" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L26" s="20">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M26" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C27" s="16" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D27" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E27" s="16" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F27" s="16" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G27" s="16" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H27" s="18">
-        <x:v>46073.1441087963</x:v>
-      </x:c>
-      <x:c r="I27" s="18">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J27" s="17" t="n">
-        <x:v>1511278</x:v>
-      </x:c>
-      <x:c r="K27" s="19" t="n">
+      <x:c r="L35" s="17">
+        <x:v>46099.1584012616</x:v>
+      </x:c>
+      <x:c r="M35" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="F36" s="13" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="G36" s="13" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="H36" s="15">
+        <x:v>46083.252116412</x:v>
+      </x:c>
+      <x:c r="I36" s="15">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J36" s="14" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="K36" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="17">
+        <x:v>46097.1628986343</x:v>
+      </x:c>
+      <x:c r="M36" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C37" s="13" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="F37" s="13" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="G37" s="13" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="H37" s="15">
+        <x:v>46097.4788515162</x:v>
+      </x:c>
+      <x:c r="I37" s="15">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J37" s="14" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="K37" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="17">
+        <x:v>46100.2987549074</x:v>
+      </x:c>
+      <x:c r="M37" s="13" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C38" s="13" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="D38" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E38" s="13" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="F38" s="13" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="G38" s="13" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="H38" s="15">
+        <x:v>46069.3341180556</x:v>
+      </x:c>
+      <x:c r="I38" s="15">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J38" s="14" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="K38" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="17">
+        <x:v>46097.244735544</x:v>
+      </x:c>
+      <x:c r="M38" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C39" s="13" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="D39" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E39" s="13" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="F39" s="13" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="G39" s="13" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="H39" s="15">
+        <x:v>46084.1513040509</x:v>
+      </x:c>
+      <x:c r="I39" s="15">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J39" s="14" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="K39" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L39" s="17">
+        <x:v>46097.2494578472</x:v>
+      </x:c>
+      <x:c r="M39" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C40" s="13" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E40" s="13" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="F40" s="13" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="G40" s="13" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="H40" s="15">
+        <x:v>46073.1135088426</x:v>
+      </x:c>
+      <x:c r="I40" s="15">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J40" s="14" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="K40" s="16" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L40" s="17">
+        <x:v>46097.2511403241</x:v>
+      </x:c>
+      <x:c r="M40" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C41" s="13" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E41" s="13" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F41" s="13" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="G41" s="13" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="H41" s="15">
+        <x:v>46069.1151616435</x:v>
+      </x:c>
+      <x:c r="I41" s="15">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J41" s="14" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="K41" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="17">
+        <x:v>46097.343386956</x:v>
+      </x:c>
+      <x:c r="M41" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C42" s="13" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="D42" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="F42" s="13" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="G42" s="13" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="H42" s="15">
+        <x:v>46084.3311976389</x:v>
+      </x:c>
+      <x:c r="I42" s="15">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J42" s="14" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="K42" s="16" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L27" s="20">
-        <x:v>46100.4005439815</x:v>
-      </x:c>
-      <x:c r="M27" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C28" s="16" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D28" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E28" s="16" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F28" s="16" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G28" s="16" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H28" s="18">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I28" s="18">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J28" s="17" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K28" s="19" t="n">
+      <x:c r="L42" s="17">
+        <x:v>46093.3668852546</x:v>
+      </x:c>
+      <x:c r="M42" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C43" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D43" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E43" s="13" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="F43" s="13" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="G43" s="13" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="H43" s="15">
+        <x:v>46097.4214954398</x:v>
+      </x:c>
+      <x:c r="I43" s="15">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J43" s="14" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="K43" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="20">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M28" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C29" s="16" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D29" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E29" s="16" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="F29" s="16" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G29" s="16" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="H29" s="18">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I29" s="18">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J29" s="17" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K29" s="19" t="n">
+      <x:c r="L43" s="17">
+        <x:v>46100.2966699421</x:v>
+      </x:c>
+      <x:c r="M43" s="13" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C44" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D44" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E44" s="13" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="F44" s="13" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="G44" s="13" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="H44" s="15">
+        <x:v>46092.1012814815</x:v>
+      </x:c>
+      <x:c r="I44" s="15">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J44" s="14" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="K44" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="20">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M29" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C30" s="16" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D30" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E30" s="16" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="F30" s="16" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="G30" s="16" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="H30" s="18">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I30" s="18">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J30" s="17" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K30" s="19" t="n">
+      <x:c r="L44" s="17">
+        <x:v>46097.1408234491</x:v>
+      </x:c>
+      <x:c r="M44" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C45" s="13" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D45" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E45" s="13" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="F45" s="13" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="G45" s="13" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H45" s="15">
+        <x:v>46069.1217257292</x:v>
+      </x:c>
+      <x:c r="I45" s="15">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J45" s="14" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="K45" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="17">
+        <x:v>46097.3375062153</x:v>
+      </x:c>
+      <x:c r="M45" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C46" s="13" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D46" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E46" s="13" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="F46" s="13" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="G46" s="13" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="H46" s="15">
+        <x:v>46069.2327997454</x:v>
+      </x:c>
+      <x:c r="I46" s="15">
+        <x:v>46049</x:v>
+      </x:c>
+      <x:c r="J46" s="14" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="K46" s="16" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L30" s="20">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M30" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C31" s="16" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D31" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E31" s="16" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="F31" s="16" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="G31" s="16" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="H31" s="18">
-        <x:v>46069.3717592593</x:v>
-      </x:c>
-      <x:c r="I31" s="18">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J31" s="17" t="n">
-        <x:v>1511274</x:v>
-      </x:c>
-      <x:c r="K31" s="19" t="n">
+      <x:c r="L46" s="17">
+        <x:v>46100.3816829514</x:v>
+      </x:c>
+      <x:c r="M46" s="13" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C47" s="13" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="D47" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E47" s="13" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="F47" s="13" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="G47" s="13" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="H47" s="15">
+        <x:v>46086.106481875</x:v>
+      </x:c>
+      <x:c r="I47" s="15">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J47" s="14" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="K47" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L47" s="17">
+        <x:v>46090.2765830324</x:v>
+      </x:c>
+      <x:c r="M47" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="13" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C48" s="13" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E48" s="13" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="F48" s="13" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="G48" s="13" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="H48" s="15">
+        <x:v>46084.3419451968</x:v>
+      </x:c>
+      <x:c r="I48" s="15">
+        <x:v>46084.3419617014</x:v>
+      </x:c>
+      <x:c r="J48" s="14" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="K48" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L48" s="17">
+        <x:v>46090.3480933681</x:v>
+      </x:c>
+      <x:c r="M48" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B49" s="13" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C49" s="13" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E49" s="13" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="F49" s="13" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="G49" s="13" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="H49" s="15">
+        <x:v>46085.1627479398</x:v>
+      </x:c>
+      <x:c r="I49" s="15">
+        <x:v>46085.1627651505</x:v>
+      </x:c>
+      <x:c r="J49" s="14" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="K49" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L49" s="17">
+        <x:v>46090.3453534259</x:v>
+      </x:c>
+      <x:c r="M49" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B50" s="13" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C50" s="13" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E50" s="13" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="F50" s="13" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G50" s="13" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="H50" s="15">
+        <x:v>46085.1662527662</x:v>
+      </x:c>
+      <x:c r="I50" s="15">
+        <x:v>46085.1662689699</x:v>
+      </x:c>
+      <x:c r="J50" s="14" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="K50" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L50" s="17">
+        <x:v>46090.3437343634</x:v>
+      </x:c>
+      <x:c r="M50" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B51" s="13" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C51" s="13" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E51" s="13" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F51" s="13" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="G51" s="13" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="H51" s="15">
+        <x:v>46085.1709247338</x:v>
+      </x:c>
+      <x:c r="I51" s="15">
+        <x:v>46085.1709419676</x:v>
+      </x:c>
+      <x:c r="J51" s="14" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="K51" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L51" s="17">
+        <x:v>46090.3337014815</x:v>
+      </x:c>
+      <x:c r="M51" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B52" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C52" s="13" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E52" s="13" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="F52" s="13" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="G52" s="13" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="H52" s="15">
+        <x:v>46084.1579541898</x:v>
+      </x:c>
+      <x:c r="I52" s="15">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J52" s="14" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="K52" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L52" s="17">
+        <x:v>46093.4169326042</x:v>
+      </x:c>
+      <x:c r="M52" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B53" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C53" s="13" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E53" s="13" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="F53" s="13" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="G53" s="13" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="H53" s="15">
+        <x:v>46084.1080380324</x:v>
+      </x:c>
+      <x:c r="I53" s="15">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J53" s="14" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="K53" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L53" s="17">
+        <x:v>46097.2478153472</x:v>
+      </x:c>
+      <x:c r="M53" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B54" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C54" s="13" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E54" s="13" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="F54" s="13" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="G54" s="13" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="H54" s="15">
+        <x:v>46083.0788057755</x:v>
+      </x:c>
+      <x:c r="I54" s="15">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J54" s="14" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="K54" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L54" s="17">
+        <x:v>46083.1042250116</x:v>
+      </x:c>
+      <x:c r="M54" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B55" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C55" s="13" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E55" s="13" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="F55" s="13" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="G55" s="13" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="H55" s="15">
+        <x:v>46084.1627466204</x:v>
+      </x:c>
+      <x:c r="I55" s="15">
+        <x:v>46060</x:v>
+      </x:c>
+      <x:c r="J55" s="14" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="K55" s="16" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L31" s="20">
-        <x:v>46100.3754861111</x:v>
-      </x:c>
-      <x:c r="M31" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C32" s="16" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D32" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E32" s="16" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="F32" s="16" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="H32" s="18">
-        <x:v>46073.125162037</x:v>
-      </x:c>
-      <x:c r="I32" s="18">
-        <x:v>45619</x:v>
-      </x:c>
-      <x:c r="J32" s="17" t="n">
-        <x:v>1511246</x:v>
-      </x:c>
-      <x:c r="K32" s="19" t="n">
-        <x:v>11280</x:v>
-      </x:c>
-      <x:c r="L32" s="20">
-        <x:v>46099.1200231481</x:v>
-      </x:c>
-      <x:c r="M32" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C33" s="16" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="D33" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E33" s="16" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="F33" s="16" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="G33" s="16" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="H33" s="18">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I33" s="18">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J33" s="17" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K33" s="19" t="n">
+      <x:c r="L55" s="17">
+        <x:v>46100.392939537</x:v>
+      </x:c>
+      <x:c r="M55" s="13" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B56" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C56" s="13" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E56" s="13" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="F56" s="13" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="G56" s="13" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="H56" s="15">
+        <x:v>46086.1144463079</x:v>
+      </x:c>
+      <x:c r="I56" s="15">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J56" s="14" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="K56" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L33" s="20">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M33" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C34" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D34" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E34" s="16" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F34" s="16" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G34" s="16" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H34" s="18">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I34" s="18">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J34" s="17" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K34" s="19" t="n">
+      <x:c r="L56" s="17">
+        <x:v>46090.2703739352</x:v>
+      </x:c>
+      <x:c r="M56" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B57" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C57" s="13" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E57" s="13" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="F57" s="13" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="G57" s="13" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="H57" s="15">
+        <x:v>46087.1643336806</x:v>
+      </x:c>
+      <x:c r="I57" s="15">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J57" s="14" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="K57" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L34" s="20">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M34" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C35" s="16" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="D35" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E35" s="16" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="F35" s="16" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="G35" s="16" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H35" s="18">
-        <x:v>46073.1541087963</x:v>
-      </x:c>
-      <x:c r="I35" s="18">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J35" s="17" t="n">
-        <x:v>1511248</x:v>
-      </x:c>
-      <x:c r="K35" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L35" s="20">
-        <x:v>46099.1583912037</x:v>
-      </x:c>
-      <x:c r="M35" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C36" s="16" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D36" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E36" s="16" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F36" s="16" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G36" s="16" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H36" s="18">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I36" s="18">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J36" s="17" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K36" s="19" t="n">
+      <x:c r="L57" s="17">
+        <x:v>46090.2727784143</x:v>
+      </x:c>
+      <x:c r="M57" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B58" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C58" s="13" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E58" s="13" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="F58" s="13" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="G58" s="13" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="H58" s="15">
+        <x:v>46086.099798588</x:v>
+      </x:c>
+      <x:c r="I58" s="15">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J58" s="14" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="K58" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L36" s="20">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M36" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C37" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D37" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E37" s="16" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F37" s="16" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G37" s="16" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H37" s="18">
-        <x:v>46097.4788425926</x:v>
-      </x:c>
-      <x:c r="I37" s="18">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J37" s="17" t="n">
-        <x:v>1511271</x:v>
-      </x:c>
-      <x:c r="K37" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="20">
-        <x:v>46100.29875</x:v>
-      </x:c>
-      <x:c r="M37" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C38" s="16" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D38" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E38" s="16" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F38" s="16" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G38" s="16" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H38" s="18">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I38" s="18">
+      <x:c r="L58" s="17">
+        <x:v>46090.2691152778</x:v>
+      </x:c>
+      <x:c r="M58" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B59" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C59" s="13" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E59" s="13" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="F59" s="13" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="G59" s="13" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="H59" s="15">
+        <x:v>46098.290884375</x:v>
+      </x:c>
+      <x:c r="I59" s="15">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J59" s="14" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="K59" s="16" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L59" s="17">
+        <x:v>46098.3188767824</x:v>
+      </x:c>
+      <x:c r="M59" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B60" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C60" s="13" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="D60" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E60" s="13" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="F60" s="13" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="G60" s="13" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="H60" s="15">
+        <x:v>46092.9637875116</x:v>
+      </x:c>
+      <x:c r="I60" s="15">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J38" s="17" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K38" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="20">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M38" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C39" s="16" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D39" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E39" s="16" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F39" s="16" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G39" s="16" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H39" s="18">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I39" s="18">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J39" s="17" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K39" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L39" s="20">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M39" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C40" s="16" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="D40" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E40" s="16" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="F40" s="16" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="G40" s="16" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="H40" s="18">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I40" s="18">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J40" s="17" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K40" s="19" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L40" s="20">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M40" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C41" s="16" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="D41" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E41" s="16" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="F41" s="16" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="G41" s="16" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="H41" s="18">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I41" s="18">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J41" s="17" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K41" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="20">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M41" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C42" s="16" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="D42" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E42" s="16" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="F42" s="16" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="G42" s="16" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="H42" s="18">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I42" s="18">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J42" s="17" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K42" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L42" s="20">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M42" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C43" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D43" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E43" s="16" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="F43" s="16" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="G43" s="16" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="H43" s="18">
-        <x:v>46097.4214930556</x:v>
-      </x:c>
-      <x:c r="I43" s="18">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J43" s="17" t="n">
-        <x:v>1511270</x:v>
-      </x:c>
-      <x:c r="K43" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="20">
-        <x:v>46100.2966666667</x:v>
-      </x:c>
-      <x:c r="M43" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C44" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D44" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E44" s="16" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F44" s="16" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G44" s="16" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="H44" s="18">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I44" s="18">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J44" s="17" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K44" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="20">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M44" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C45" s="16" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D45" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E45" s="16" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="F45" s="16" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="G45" s="16" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="H45" s="18">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I45" s="18">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J45" s="17" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K45" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="20">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M45" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C46" s="16" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D46" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E46" s="16" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="F46" s="16" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="G46" s="16" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="H46" s="18">
-        <x:v>46069.2327893519</x:v>
-      </x:c>
-      <x:c r="I46" s="18">
-        <x:v>46049</x:v>
-      </x:c>
-      <x:c r="J46" s="17" t="n">
-        <x:v>1511275</x:v>
-      </x:c>
-      <x:c r="K46" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L46" s="20">
-        <x:v>46100.3816782407</x:v>
-      </x:c>
-      <x:c r="M46" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C47" s="16" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="D47" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E47" s="16" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="F47" s="16" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="G47" s="16" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="H47" s="18">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I47" s="18">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J47" s="17" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K47" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L47" s="20">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M47" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C48" s="16" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="D48" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E48" s="16" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="F48" s="16" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="G48" s="16" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="H48" s="18">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I48" s="18">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J48" s="17" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K48" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L48" s="20">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M48" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B49" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C49" s="16" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="D49" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E49" s="16" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="F49" s="16" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="G49" s="16" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="H49" s="18">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I49" s="18">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J49" s="17" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K49" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L49" s="20">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M49" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B50" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C50" s="16" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="D50" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E50" s="16" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="F50" s="16" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="G50" s="16" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="H50" s="18">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I50" s="18">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J50" s="17" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K50" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L50" s="20">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M50" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B51" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C51" s="16" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="D51" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E51" s="16" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="F51" s="16" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="G51" s="16" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="H51" s="18">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I51" s="18">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J51" s="17" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K51" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L51" s="20">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M51" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B52" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C52" s="16" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="D52" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E52" s="16" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="F52" s="16" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="G52" s="16" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="H52" s="18">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I52" s="18">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J52" s="17" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K52" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L52" s="20">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M52" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B53" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C53" s="16" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D53" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E53" s="16" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="F53" s="16" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="G53" s="16" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="H53" s="18">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I53" s="18">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J53" s="17" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K53" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L53" s="20">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M53" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B54" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C54" s="16" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="D54" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E54" s="16" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="F54" s="16" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="G54" s="16" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="H54" s="18">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I54" s="18">
+      <x:c r="J60" s="14" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="K60" s="16" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L60" s="17">
+        <x:v>46093.3109466551</x:v>
+      </x:c>
+      <x:c r="M60" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B61" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C61" s="13" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E61" s="13" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="F61" s="13" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="G61" s="13" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="H61" s="15">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I61" s="15">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J54" s="17" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K54" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L54" s="20">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M54" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B55" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C55" s="16" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D55" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E55" s="16" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="F55" s="16" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="G55" s="16" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="H55" s="18">
-        <x:v>46084.1627430556</x:v>
-      </x:c>
-      <x:c r="I55" s="18">
-        <x:v>46060</x:v>
-      </x:c>
-      <x:c r="J55" s="17" t="n">
-        <x:v>1511277</x:v>
-      </x:c>
-      <x:c r="K55" s="19" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L55" s="20">
-        <x:v>46100.3929282407</x:v>
-      </x:c>
-      <x:c r="M55" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B56" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C56" s="16" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="D56" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E56" s="16" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="F56" s="16" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="G56" s="16" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="H56" s="18">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I56" s="18">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J56" s="17" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K56" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L56" s="20">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M56" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B57" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C57" s="16" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="D57" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E57" s="16" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="F57" s="16" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="G57" s="16" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="H57" s="18">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I57" s="18">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J57" s="17" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K57" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L57" s="20">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M57" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B58" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C58" s="16" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="D58" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E58" s="16" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="F58" s="16" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="G58" s="16" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="H58" s="18">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I58" s="18">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J58" s="17" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K58" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L58" s="20">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M58" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B59" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C59" s="16" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="D59" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E59" s="16" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="F59" s="16" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="G59" s="16" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="H59" s="18">
-        <x:v>46098.2908796296</x:v>
-      </x:c>
-      <x:c r="I59" s="18">
-        <x:v>45997</x:v>
-      </x:c>
-      <x:c r="J59" s="17" t="n">
-        <x:v>1511858</x:v>
-      </x:c>
-      <x:c r="K59" s="19" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L59" s="20">
-        <x:v>46098.3188657407</x:v>
-      </x:c>
-      <x:c r="M59" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B60" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C60" s="16" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="D60" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E60" s="16" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="F60" s="16" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="G60" s="16" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="H60" s="18">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I60" s="18">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J60" s="17" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K60" s="19" t="n">
+      <x:c r="J61" s="14" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="K61" s="16" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L60" s="20">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M60" s="16" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B61" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C61" s="16" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="D61" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E61" s="16" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="F61" s="16" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="G61" s="16" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="H61" s="18">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I61" s="18">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J61" s="17" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K61" s="19" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L61" s="20">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M61" s="16" t="s">
-        <x:v>24</x:v>
+      <x:c r="L61" s="17">
+        <x:v>46083.1543707755</x:v>
+      </x:c>
+      <x:c r="M61" s="13" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="21" t="s">
+      <x:c r="B64" s="18" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C64" s="19" t="s"/>
+      <x:c r="D64" s="19" t="s"/>
+      <x:c r="E64" s="20" t="s"/>
+      <x:c r="F64" s="20" t="s"/>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B65" s="21" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C65" s="22" t="s"/>
+      <x:c r="D65" s="22" t="s"/>
+      <x:c r="E65" s="22" t="s"/>
+      <x:c r="F65" s="23" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C66" s="25" t="s"/>
+      <x:c r="D66" s="25" t="s"/>
+      <x:c r="E66" s="25" t="s"/>
+      <x:c r="F66" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="24" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C67" s="25" t="s"/>
+      <x:c r="D67" s="25" t="s"/>
+      <x:c r="E67" s="25" t="s"/>
+      <x:c r="F67" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B68" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C68" s="25" t="s"/>
+      <x:c r="D68" s="25" t="s"/>
+      <x:c r="E68" s="25" t="s"/>
+      <x:c r="F68" s="26" t="n">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B69" s="24" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C69" s="25" t="s"/>
+      <x:c r="D69" s="25" t="s"/>
+      <x:c r="E69" s="25" t="s"/>
+      <x:c r="F69" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B70" s="24" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C70" s="25" t="s"/>
+      <x:c r="D70" s="25" t="s"/>
+      <x:c r="E70" s="25" t="s"/>
+      <x:c r="F70" s="26" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B71" s="24" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C64" s="22" t="s"/>
-      <x:c r="D64" s="22" t="s"/>
-      <x:c r="E64" s="23" t="s"/>
-      <x:c r="F64" s="23" t="s"/>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B65" s="24" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C65" s="25" t="s"/>
-      <x:c r="D65" s="25" t="s"/>
-      <x:c r="E65" s="25" t="s"/>
-      <x:c r="F65" s="26" t="s">
-        <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C66" s="28" t="s"/>
-      <x:c r="D66" s="28" t="s"/>
-      <x:c r="E66" s="28" t="s"/>
-      <x:c r="F66" s="29" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C67" s="28" t="s"/>
-      <x:c r="D67" s="28" t="s"/>
-      <x:c r="E67" s="28" t="s"/>
-      <x:c r="F67" s="29" t="n">
+      <x:c r="C71" s="25" t="s"/>
+      <x:c r="D71" s="25" t="s"/>
+      <x:c r="E71" s="25" t="s"/>
+      <x:c r="F71" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B68" s="27" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C68" s="28" t="s"/>
-      <x:c r="D68" s="28" t="s"/>
-      <x:c r="E68" s="28" t="s"/>
-      <x:c r="F68" s="29" t="n">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B69" s="27" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C69" s="28" t="s"/>
-      <x:c r="D69" s="28" t="s"/>
-      <x:c r="E69" s="28" t="s"/>
-      <x:c r="F69" s="29" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B70" s="27" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C70" s="28" t="s"/>
-      <x:c r="D70" s="28" t="s"/>
-      <x:c r="E70" s="28" t="s"/>
-      <x:c r="F70" s="29" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B71" s="27" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C71" s="28" t="s"/>
-      <x:c r="D71" s="28" t="s"/>
-      <x:c r="E71" s="28" t="s"/>
-      <x:c r="F71" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
     <x:row r="72" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B72" s="30" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C72" s="31" t="s"/>
-      <x:c r="D72" s="31" t="s"/>
-      <x:c r="E72" s="31" t="s"/>
-      <x:c r="F72" s="32" t="n">
+      <x:c r="B72" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C72" s="28" t="s"/>
+      <x:c r="D72" s="28" t="s"/>
+      <x:c r="E72" s="28" t="s"/>
+      <x:c r="F72" s="29" t="n">
         <x:v>54</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="451">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="456">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -712,6 +712,21 @@
     <x:t>1511815</x:t>
   </x:si>
   <x:si>
+    <x:t>ROBERT O. DELA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phase 1A Blk 3 Lot 3 RCD Royale Homes, Kalubkob, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03514-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1220-726</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1506181</x:t>
+  </x:si>
+  <x:si>
     <x:t>RUBEN C. SESCON</x:t>
   </x:si>
   <x:si>
@@ -886,6 +901,42 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511224</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -898,18 +949,6 @@
     <x:t>1511193</x:t>
   </x:si>
   <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511206</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
   </x:si>
   <x:si>
@@ -922,30 +961,6 @@
     <x:t>1511278</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511224</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -964,6 +979,18 @@
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-17-11-0683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1109-317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511246</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CENTER ILLUSTRE AVE, DISTRICT IV, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -974,18 +1001,6 @@
   </x:si>
   <x:si>
     <x:t>1511274</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-17-11-0683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1109-317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511246</x:t>
   </x:si>
   <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
@@ -5042,10 +5057,10 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H13" s="15">
-        <x:v>46098.0792632986</x:v>
+        <x:v>46104.2283957986</x:v>
       </x:c>
       <x:c r="I13" s="15">
-        <x:v>46098.0878978819</x:v>
+        <x:v>46104.2427159028</x:v>
       </x:c>
       <x:c r="J13" s="14" t="s">
         <x:v>233</x:v>
@@ -5054,22 +5069,20 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L13" s="17">
-        <x:v>46098.0997679745</x:v>
+        <x:v>46104.2658305093</x:v>
       </x:c>
       <x:c r="M13" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="13" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
+      <x:c r="D14" s="14" t="s"/>
       <x:c r="E14" s="13" t="s">
         <x:v>235</x:v>
       </x:c>
@@ -5080,22 +5093,22 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H14" s="15">
-        <x:v>46090.2418365857</x:v>
+        <x:v>46098.0792632986</x:v>
       </x:c>
       <x:c r="I14" s="15">
-        <x:v>46090.2418534606</x:v>
+        <x:v>46098.0878978819</x:v>
       </x:c>
       <x:c r="J14" s="14" t="s">
         <x:v>238</x:v>
       </x:c>
       <x:c r="K14" s="16" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L14" s="17">
-        <x:v>46093.3049920255</x:v>
+        <x:v>46098.0997679745</x:v>
       </x:c>
       <x:c r="M14" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -5103,7 +5116,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="13" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D15" s="14" t="s">
         <x:v>49</x:v>
@@ -5118,10 +5131,10 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="H15" s="15">
-        <x:v>46090.2558238542</x:v>
+        <x:v>46090.2418365857</x:v>
       </x:c>
       <x:c r="I15" s="15">
-        <x:v>46090.2558400116</x:v>
+        <x:v>46090.2418534606</x:v>
       </x:c>
       <x:c r="J15" s="14" t="s">
         <x:v>243</x:v>
@@ -5130,10 +5143,10 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="17">
-        <x:v>46097.2890797917</x:v>
+        <x:v>46093.3049920255</x:v>
       </x:c>
       <x:c r="M15" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -5141,7 +5154,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C16" s="13" t="s">
-        <x:v>244</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D16" s="14" t="s">
         <x:v>49</x:v>
@@ -5156,10 +5169,10 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H16" s="15">
-        <x:v>46090.210999456</x:v>
+        <x:v>46090.2558238542</x:v>
       </x:c>
       <x:c r="I16" s="15">
-        <x:v>46090.211015162</x:v>
+        <x:v>46090.2558400116</x:v>
       </x:c>
       <x:c r="J16" s="14" t="s">
         <x:v>248</x:v>
@@ -5168,21 +5181,21 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="17">
-        <x:v>46093.3080127546</x:v>
+        <x:v>46097.2890797917</x:v>
       </x:c>
       <x:c r="M16" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="13" t="s">
         <x:v>249</x:v>
       </x:c>
       <x:c r="D17" s="14" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E17" s="13" t="s">
         <x:v>250</x:v>
@@ -5194,22 +5207,22 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="H17" s="15">
-        <x:v>46083.2380494329</x:v>
+        <x:v>46090.210999456</x:v>
       </x:c>
       <x:c r="I17" s="15">
-        <x:v>46100</x:v>
+        <x:v>46090.211015162</x:v>
       </x:c>
       <x:c r="J17" s="14" t="s">
         <x:v>253</x:v>
       </x:c>
       <x:c r="K17" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="17">
-        <x:v>46097.1564439468</x:v>
+        <x:v>46093.3080127546</x:v>
       </x:c>
       <x:c r="M17" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -5217,37 +5230,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C18" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D18" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E18" s="13" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F18" s="13" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G18" s="13" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H18" s="15">
-        <x:v>46083.2322339931</x:v>
+        <x:v>46083.2380494329</x:v>
       </x:c>
       <x:c r="I18" s="15">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J18" s="14" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K18" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="17">
-        <x:v>46097.1495293519</x:v>
+        <x:v>46097.1564439468</x:v>
       </x:c>
       <x:c r="M18" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -5255,37 +5268,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C19" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D19" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E19" s="13" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F19" s="13" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G19" s="13" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H19" s="15">
-        <x:v>46080.4532551852</x:v>
+        <x:v>46083.2322339931</x:v>
       </x:c>
       <x:c r="I19" s="15">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J19" s="14" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="K19" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="17">
-        <x:v>46097.1461728357</x:v>
+        <x:v>46097.1495293519</x:v>
       </x:c>
       <x:c r="M19" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -5293,7 +5306,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C20" s="13" t="s">
-        <x:v>262</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D20" s="14" t="s">
         <x:v>60</x:v>
@@ -5308,10 +5321,10 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="H20" s="15">
-        <x:v>46083.2599218056</x:v>
+        <x:v>46080.4532551852</x:v>
       </x:c>
       <x:c r="I20" s="15">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J20" s="14" t="s">
         <x:v>266</x:v>
@@ -5320,10 +5333,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="17">
-        <x:v>46097.1652390856</x:v>
+        <x:v>46097.1461728357</x:v>
       </x:c>
       <x:c r="M20" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -5346,22 +5359,22 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="H21" s="15">
-        <x:v>46069.278571956</x:v>
+        <x:v>46083.2599218056</x:v>
       </x:c>
       <x:c r="I21" s="15">
-        <x:v>46067</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J21" s="14" t="s">
         <x:v>271</x:v>
       </x:c>
       <x:c r="K21" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="17">
-        <x:v>46100.3884108912</x:v>
+        <x:v>46097.1652390856</x:v>
       </x:c>
       <x:c r="M21" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5369,7 +5382,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D22" s="14" t="s">
         <x:v>60</x:v>
@@ -5384,22 +5397,22 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="H22" s="15">
-        <x:v>46069.3514850347</x:v>
+        <x:v>46069.278571956</x:v>
       </x:c>
       <x:c r="I22" s="15">
-        <x:v>46094</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J22" s="14" t="s">
         <x:v>276</x:v>
       </x:c>
       <x:c r="K22" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L22" s="17">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46100.3884108912</x:v>
       </x:c>
       <x:c r="M22" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5407,7 +5420,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C23" s="13" t="s">
-        <x:v>277</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D23" s="14" t="s">
         <x:v>60</x:v>
@@ -5422,10 +5435,10 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="H23" s="15">
-        <x:v>46084.0854516898</x:v>
+        <x:v>46069.3514850347</x:v>
       </x:c>
       <x:c r="I23" s="15">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J23" s="14" t="s">
         <x:v>281</x:v>
@@ -5434,10 +5447,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="17">
-        <x:v>46093.3956400694</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M23" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5445,37 +5458,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="13" t="s">
-        <x:v>277</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D24" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E24" s="13" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="F24" s="13" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G24" s="13" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H24" s="15">
-        <x:v>46084.0996762384</x:v>
+        <x:v>46084.0854516898</x:v>
       </x:c>
       <x:c r="I24" s="15">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J24" s="14" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="K24" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="17">
-        <x:v>46097.241468588</x:v>
+        <x:v>46093.3956400694</x:v>
       </x:c>
       <x:c r="M24" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5483,7 +5496,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C25" s="13" t="s">
-        <x:v>286</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D25" s="14" t="s">
         <x:v>60</x:v>
@@ -5498,10 +5511,10 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="H25" s="15">
-        <x:v>46069.3573124306</x:v>
+        <x:v>46084.0996762384</x:v>
       </x:c>
       <x:c r="I25" s="15">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J25" s="14" t="s">
         <x:v>290</x:v>
@@ -5510,10 +5523,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="17">
-        <x:v>46097.2426396643</x:v>
+        <x:v>46097.241468588</x:v>
       </x:c>
       <x:c r="M25" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5521,19 +5534,19 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C26" s="13" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D26" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E26" s="13" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F26" s="13" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G26" s="13" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H26" s="15">
         <x:v>46069.1542109954</x:v>
@@ -5542,7 +5555,7 @@
         <x:v>46035</x:v>
       </x:c>
       <x:c r="J26" s="14" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K26" s="16" t="n">
         <x:v>3780</x:v>
@@ -5551,7 +5564,7 @@
         <x:v>46097.2466610301</x:v>
       </x:c>
       <x:c r="M26" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5559,37 +5572,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C27" s="13" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D27" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E27" s="13" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F27" s="13" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G27" s="13" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="H27" s="15">
-        <x:v>46073.1441202083</x:v>
+        <x:v>46084.2189288542</x:v>
       </x:c>
       <x:c r="I27" s="15">
-        <x:v>46030</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J27" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="K27" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="17">
-        <x:v>46100.4005466667</x:v>
+        <x:v>46093.3723926852</x:v>
       </x:c>
       <x:c r="M27" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5597,37 +5610,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C28" s="13" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D28" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E28" s="13" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F28" s="13" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="G28" s="13" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="H28" s="15">
-        <x:v>46084.2189288542</x:v>
+        <x:v>46084.2250188542</x:v>
       </x:c>
       <x:c r="I28" s="15">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J28" s="14" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="K28" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="17">
-        <x:v>46093.3723926852</x:v>
+        <x:v>46093.3804507639</x:v>
       </x:c>
       <x:c r="M28" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5635,37 +5648,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C29" s="13" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D29" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E29" s="13" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F29" s="13" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G29" s="13" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H29" s="15">
-        <x:v>46084.2250188542</x:v>
+        <x:v>46069.3573124306</x:v>
       </x:c>
       <x:c r="I29" s="15">
-        <x:v>46144</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J29" s="14" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="K29" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="17">
-        <x:v>46093.3804507639</x:v>
+        <x:v>46097.2426396643</x:v>
       </x:c>
       <x:c r="M29" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5673,7 +5686,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C30" s="13" t="s">
-        <x:v>307</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D30" s="14" t="s">
         <x:v>60</x:v>
@@ -5688,10 +5701,10 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="H30" s="15">
-        <x:v>46069.2178798032</x:v>
+        <x:v>46073.1441202083</x:v>
       </x:c>
       <x:c r="I30" s="15">
-        <x:v>46051</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J30" s="14" t="s">
         <x:v>311</x:v>
@@ -5700,10 +5713,10 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L30" s="17">
-        <x:v>46097.2456397685</x:v>
+        <x:v>46100.4005466667</x:v>
       </x:c>
       <x:c r="M30" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5726,10 +5739,10 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="H31" s="15">
-        <x:v>46069.3717699074</x:v>
+        <x:v>46069.2178798032</x:v>
       </x:c>
       <x:c r="I31" s="15">
-        <x:v>46066</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J31" s="14" t="s">
         <x:v>316</x:v>
@@ -5738,10 +5751,10 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L31" s="17">
-        <x:v>46100.3754893056</x:v>
+        <x:v>46097.2456397685</x:v>
       </x:c>
       <x:c r="M31" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5749,19 +5762,19 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C32" s="13" t="s">
-        <x:v>312</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D32" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E32" s="13" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F32" s="13" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="G32" s="13" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="H32" s="15">
         <x:v>46073.1251625463</x:v>
@@ -5770,7 +5783,7 @@
         <x:v>45619</x:v>
       </x:c>
       <x:c r="J32" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="K32" s="16" t="n">
         <x:v>11280</x:v>
@@ -5779,7 +5792,7 @@
         <x:v>46099.1200232986</x:v>
       </x:c>
       <x:c r="M32" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5787,7 +5800,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C33" s="13" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D33" s="14" t="s">
         <x:v>60</x:v>
@@ -5802,22 +5815,22 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="H33" s="15">
-        <x:v>46083.2443981019</x:v>
+        <x:v>46069.3717699074</x:v>
       </x:c>
       <x:c r="I33" s="15">
-        <x:v>46100</x:v>
+        <x:v>46066</x:v>
       </x:c>
       <x:c r="J33" s="14" t="s">
         <x:v>325</x:v>
       </x:c>
       <x:c r="K33" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L33" s="17">
-        <x:v>46097.1600206018</x:v>
+        <x:v>46100.3754893056</x:v>
       </x:c>
       <x:c r="M33" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5840,10 +5853,10 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="H34" s="15">
-        <x:v>46084.1225139699</x:v>
+        <x:v>46083.2443981019</x:v>
       </x:c>
       <x:c r="I34" s="15">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J34" s="14" t="s">
         <x:v>330</x:v>
@@ -5852,10 +5865,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="17">
-        <x:v>46097.3505144329</x:v>
+        <x:v>46097.1600206018</x:v>
       </x:c>
       <x:c r="M34" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5878,22 +5891,22 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="H35" s="15">
-        <x:v>46073.1541139005</x:v>
+        <x:v>46084.1225139699</x:v>
       </x:c>
       <x:c r="I35" s="15">
-        <x:v>46030</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J35" s="14" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="K35" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="17">
-        <x:v>46099.1584012616</x:v>
+        <x:v>46097.3505144329</x:v>
       </x:c>
       <x:c r="M35" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -5916,22 +5929,22 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="H36" s="15">
-        <x:v>46083.252116412</x:v>
+        <x:v>46073.1541139005</x:v>
       </x:c>
       <x:c r="I36" s="15">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J36" s="14" t="s">
         <x:v>340</x:v>
       </x:c>
       <x:c r="K36" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L36" s="17">
-        <x:v>46097.1628986343</x:v>
+        <x:v>46099.1584012616</x:v>
       </x:c>
       <x:c r="M36" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -5954,7 +5967,7 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="H37" s="15">
-        <x:v>46097.4788515162</x:v>
+        <x:v>46083.252116412</x:v>
       </x:c>
       <x:c r="I37" s="15">
         <x:v>46100</x:v>
@@ -5966,10 +5979,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="17">
-        <x:v>46100.2987549074</x:v>
+        <x:v>46097.1628986343</x:v>
       </x:c>
       <x:c r="M37" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5992,10 +6005,10 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="H38" s="15">
-        <x:v>46069.3341180556</x:v>
+        <x:v>46097.4788515162</x:v>
       </x:c>
       <x:c r="I38" s="15">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J38" s="14" t="s">
         <x:v>350</x:v>
@@ -6004,10 +6017,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="17">
-        <x:v>46097.244735544</x:v>
+        <x:v>46100.2987549074</x:v>
       </x:c>
       <x:c r="M38" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -6021,31 +6034,31 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="E39" s="13" t="s">
-        <x:v>327</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F39" s="13" t="s">
-        <x:v>352</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="G39" s="13" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="H39" s="15">
-        <x:v>46084.1513040509</x:v>
+        <x:v>46069.3341180556</x:v>
       </x:c>
       <x:c r="I39" s="15">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J39" s="14" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="K39" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="17">
-        <x:v>46097.2494578472</x:v>
+        <x:v>46097.244735544</x:v>
       </x:c>
       <x:c r="M39" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
@@ -6053,13 +6066,13 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C40" s="13" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="D40" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E40" s="13" t="s">
-        <x:v>356</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F40" s="13" t="s">
         <x:v>357</x:v>
@@ -6068,22 +6081,22 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="H40" s="15">
-        <x:v>46073.1135088426</x:v>
+        <x:v>46084.1513040509</x:v>
       </x:c>
       <x:c r="I40" s="15">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J40" s="14" t="s">
         <x:v>359</x:v>
       </x:c>
       <x:c r="K40" s="16" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="17">
-        <x:v>46097.2511403241</x:v>
+        <x:v>46097.2494578472</x:v>
       </x:c>
       <x:c r="M40" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
@@ -6091,37 +6104,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C41" s="13" t="s">
-        <x:v>355</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D41" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E41" s="13" t="s">
-        <x:v>360</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F41" s="13" t="s">
-        <x:v>361</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="G41" s="13" t="s">
-        <x:v>362</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="H41" s="15">
-        <x:v>46069.1151616435</x:v>
+        <x:v>46073.1135088426</x:v>
       </x:c>
       <x:c r="I41" s="15">
-        <x:v>46172</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J41" s="14" t="s">
-        <x:v>363</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="K41" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L41" s="17">
-        <x:v>46097.343386956</x:v>
+        <x:v>46097.2511403241</x:v>
       </x:c>
       <x:c r="M41" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
@@ -6129,37 +6142,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C42" s="13" t="s">
-        <x:v>355</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D42" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E42" s="13" t="s">
-        <x:v>364</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F42" s="13" t="s">
-        <x:v>365</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="G42" s="13" t="s">
-        <x:v>366</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="H42" s="15">
-        <x:v>46084.3311976389</x:v>
+        <x:v>46069.1151616435</x:v>
       </x:c>
       <x:c r="I42" s="15">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J42" s="14" t="s">
-        <x:v>367</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="K42" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L42" s="17">
-        <x:v>46093.3668852546</x:v>
+        <x:v>46097.343386956</x:v>
       </x:c>
       <x:c r="M42" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
@@ -6167,37 +6180,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C43" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D43" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E43" s="13" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F43" s="13" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="G43" s="13" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="H43" s="15">
-        <x:v>46097.4214954398</x:v>
+        <x:v>46084.3311976389</x:v>
       </x:c>
       <x:c r="I43" s="15">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J43" s="14" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="K43" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L43" s="17">
-        <x:v>46100.2966699421</x:v>
+        <x:v>46093.3668852546</x:v>
       </x:c>
       <x:c r="M43" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
@@ -6211,31 +6224,31 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="E44" s="13" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F44" s="13" t="s">
-        <x:v>373</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G44" s="13" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="H44" s="15">
-        <x:v>46092.1012814815</x:v>
+        <x:v>46097.4214954398</x:v>
       </x:c>
       <x:c r="I44" s="15">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J44" s="14" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="K44" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="17">
-        <x:v>46097.1408234491</x:v>
+        <x:v>46100.2966699421</x:v>
       </x:c>
       <x:c r="M44" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -6243,7 +6256,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C45" s="13" t="s">
-        <x:v>376</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D45" s="14" t="s">
         <x:v>60</x:v>
@@ -6258,10 +6271,10 @@
         <x:v>379</x:v>
       </x:c>
       <x:c r="H45" s="15">
-        <x:v>46069.1217257292</x:v>
+        <x:v>46092.1012814815</x:v>
       </x:c>
       <x:c r="I45" s="15">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J45" s="14" t="s">
         <x:v>380</x:v>
@@ -6270,10 +6283,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="17">
-        <x:v>46097.3375062153</x:v>
+        <x:v>46097.1408234491</x:v>
       </x:c>
       <x:c r="M45" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
@@ -6281,37 +6294,37 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C46" s="13" t="s">
-        <x:v>376</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="D46" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E46" s="13" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F46" s="13" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="G46" s="13" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="H46" s="15">
-        <x:v>46069.2327997454</x:v>
+        <x:v>46069.1217257292</x:v>
       </x:c>
       <x:c r="I46" s="15">
-        <x:v>46049</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J46" s="14" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K46" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="17">
-        <x:v>46100.3816829514</x:v>
+        <x:v>46097.3375062153</x:v>
       </x:c>
       <x:c r="M46" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
@@ -6319,7 +6332,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C47" s="13" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="D47" s="14" t="s">
         <x:v>60</x:v>
@@ -6334,33 +6347,33 @@
         <x:v>388</x:v>
       </x:c>
       <x:c r="H47" s="15">
-        <x:v>46086.106481875</x:v>
+        <x:v>46069.2327997454</x:v>
       </x:c>
       <x:c r="I47" s="15">
-        <x:v>46095</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J47" s="14" t="s">
         <x:v>389</x:v>
       </x:c>
       <x:c r="K47" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L47" s="17">
-        <x:v>46090.2765830324</x:v>
+        <x:v>46100.3816829514</x:v>
       </x:c>
       <x:c r="M47" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="13" t="s">
-        <x:v>92</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C48" s="13" t="s">
         <x:v>390</x:v>
       </x:c>
       <x:c r="D48" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E48" s="13" t="s">
         <x:v>391</x:v>
@@ -6372,22 +6385,22 @@
         <x:v>393</x:v>
       </x:c>
       <x:c r="H48" s="15">
-        <x:v>46084.3419451968</x:v>
+        <x:v>46086.106481875</x:v>
       </x:c>
       <x:c r="I48" s="15">
-        <x:v>46084.3419617014</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J48" s="14" t="s">
         <x:v>394</x:v>
       </x:c>
       <x:c r="K48" s="16" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L48" s="17">
-        <x:v>46090.3480933681</x:v>
+        <x:v>46090.2765830324</x:v>
       </x:c>
       <x:c r="M48" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
@@ -6395,34 +6408,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C49" s="13" t="s">
-        <x:v>390</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="D49" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E49" s="13" t="s">
-        <x:v>395</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F49" s="13" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G49" s="13" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="H49" s="15">
-        <x:v>46085.1627479398</x:v>
+        <x:v>46084.3419451968</x:v>
       </x:c>
       <x:c r="I49" s="15">
-        <x:v>46085.1627651505</x:v>
+        <x:v>46084.3419617014</x:v>
       </x:c>
       <x:c r="J49" s="14" t="s">
-        <x:v>398</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="K49" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L49" s="17">
-        <x:v>46090.3453534259</x:v>
+        <x:v>46090.3480933681</x:v>
       </x:c>
       <x:c r="M49" s="13" t="s">
         <x:v>26</x:v>
@@ -6433,34 +6446,34 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C50" s="13" t="s">
-        <x:v>390</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="D50" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E50" s="13" t="s">
-        <x:v>399</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="F50" s="13" t="s">
-        <x:v>400</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="G50" s="13" t="s">
-        <x:v>401</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H50" s=